--- a/'What Percent Of Our Atmosphere Is CO2' Doug LaMalfa Stumps Entire Panel With Climate Questions.xlsx
+++ b/'What Percent Of Our Atmosphere Is CO2' Doug LaMalfa Stumps Entire Panel With Climate Questions.xlsx
@@ -461,12 +461,8 @@
 threads, typical woke pof. | For the right amount of money, they would push their own children into a volcano. | @gossumx  One of them claimed transportation is 49% of CO2...
 Completely absurd. | 49% of what, exactly?
 A % dangling without context is at most alarming.  But when the the context is shown wrt CO2 emissions, it is realized to be a nothing burger.  She only alluded to, without providing context.  That's known as talking out your azz. | @granolafunk6192  Air transport to be specific is the single biggest c02 generator since the fuel (kerosene) "cokes" and generates a lot of soot and C02.  Elon Musk's Falcon rockets also use a different form of kerosene (RP-4) that cokes so badly that the engines have to be cleaned after every flight.  When you look at how many flights per day are in the air (thanks to the wonders of ADS-B) it's pretty plausible.  I read somewhere that all the automobile traffic in the world doesn't add up to the CO2 generated by all the air traffic each day since even a gasoline powered klunker burns less fuel per trip and burns the gasoline cleaner than the jet engine does.  
-I'm waiting for Airforce 1 to go electric and then I'll think about it.  Until then I really think we should re-evaluate investing a lot more into nuclear power.  Zero emissions and you can avoid rolling blackouts.  The energy density is much higher than fossil fuels and solar/wind (with the latter just being unreliable if Newsome's California is any example). | @granolafunk6192  so what percent of the CO2 do you think comes from transportation. According to the reports that I have been seeing over the last fifty years 49% sounds about right. | @2000sborton  ...
-Approximately 3% of atmospheric CO2 is anthropogenic. | @2000sborton  Stop reading biased sources of news or something. | @jamesforbes2871  you are correct. Approximately 3% of total atmospheric CO2 is anthropogenic. The 49% refers to the percentage of anthropogenic CO2 from transportation. 
-  This is why a youtube comments section is not the best place to find accurate information about a life changing matter. It is far too easy to get confused in the details. 
-  No wonder the vast majority of the population has been so easily led astray by the people who have a major stake in this. That is the petrochemical industry who have TRILLIONS of dollars in this game. | My plants love CO² | "Hi I work for the govt.  I'm here to help... just kidding... we both know that I don't care about doing anything to help.  In fact, I don't even know wtf I am doing and tbh what I do is probably harming the country and the economy but this is the only job where I can make this much money without putting much effort in.  The free market is much to demanding.  No one would pay me half of what I am making in this cushy govt job.   Just please don't ask me to be accountable.  We both know that's not going to get us anywhere." | They aren't just ignorant they are evil. And exposing does no good for anyone. It's not as if justice exists. | Yes the mythbuster experiment is flawed - those were sealed boxes with non-equalised pressure stopping convection and no water evaporation (the primary roots of energy transfer from the surface to the upper atmosphere).  The earth is not a box and uses a lot of energy in the hydrological cycle. | These sick people MUST BE EXPOSED WORLDWIDE and most of all stopped. | @gossumx  that mythbuster clip showed only a 3% rise in temperature using more than 10,000 times the concentration of manmade Co2 that exists in the atmosphere. Also that's without any of the many climate feedbacks that help moderate Earth temperature. So that temp rise was also hugely exaggerated. That clip pretty much debunks the alarmist viewpoint. | @gossumx  that clip showed that Mythbusters filled those tiny greenhouses with 70,000ppm!
-Do you really think that 7% is comparable to todays 0.040% co2 levels? | @Malpriorvids  Does it show 70,000 ppm? I hadn't seen what their settings were for it.  Where did it show?  That being said, our atmosphere is a much thicker blanket than those small greenhouses.  It really just illustrates the concept.  But I'd be happy to look into it more and maybe learn a thing or two. | ​ @gossumx  yes. It is inconsequencial | @gossumx  That is a demonstration, not an experiment. The levels of CO2 and CH4 used would themselves be lethal regardless of the observed one degree rise in temperature. It does demonstrate that exceptionally high concentrations of these gases can effect temperature. | @gossumx  (methane isn’t co2) | @bujkaizack  I’m sorry if I didn’t describe it well. They used 4 separate test chambers. 1 with CO2, 1 with methane, and 2 controls with atmospheric air. | Cars make carbon monoxide NOT CO2 carbon dioxide!!! | @troyfrei2962  Eh? Internal combustion engines produce approx 20 times CO2 to CO. Do a little research anywhere to confirm. | @troyfrei2962  They make both. CO is much lower amount. | @troyfrei2962  that is so wrong its not even funny. cars do in fact produce small amounts of carbon monoxide (CO) but they also produce very large amounts of carbon dioxide (CO2) it is a biproduct of burning hydrocarbons in the presence of oxygen 
-(C-H + O2 = CO2 + H2O) so maybe if you listened in chemistry you would know that. | Because they get $$$$$$ to do it, say it, push it...</v>
+I'm waiting for Airforce 1 to go electric and then I'll think about it.  Until then I really think we should re-evaluate investing a lot more into nuclear power.  Zero emissions and you can avoid rolling blackouts.  The energy density is much higher than fossil fuels and solar/wind (with the latter just being unreliable if Newsome's California is any example). | @Snuffitology  The volcano Katla alone does more. | @granolafunk6192  Nonsense. Volcanic CO2 emissions are one one hundredth of anthropogenic CO2 emissions according to the United Geological Survey. | @jamesmorrow1646  Not according to Katla. | @jamesmorrow1646  What is nonsense, is claiming that you know how much is emitted by volcanoes we do not know about. | @granolafunk6192  so what percent of the CO2 do you think comes from transportation. According to the reports that I have been seeing over the last fifty years 49% sounds about right. | @granolafunk6192  they drinketh the kool aid with much abundance and ferver | @granolafunk6192  Of the emissions, not that it was the composition. She said 5% too. | @Braiam  No, she wasn't. He asked her what is the composition of CO2 in the atmosphere. She answered by saying transportation is 49% of that.
+So she thinks humans have created more CO2 than exists on the f n planet... | My plants love CO² | "Hi I work for the govt.  I'm here to help... just kidding... we both know that I don't care about doing anything to help.  In fact, I don't even know wtf I am doing and tbh what I do is probably harming the country and the economy but this is the only job where I can make this much money without putting much effort in.  The free market is much to demanding.  No one would pay me half of what I am making in this cushy govt job.   Just please don't ask me to be accountable.  We both know that's not going to get us anywhere."</v>
       </c>
     </row>
     <row r="4">
@@ -518,7 +514,7 @@
       </c>
       <c r="E6" t="str" xml:space="preserve">
         <v xml:space="preserve">They are wrong only by 20000%, so there is still a very small chance they are not going to deliver well planned disaster | @Dmitry Shultz  I can see you are a optimistic person!!! | Welcome to politics haha | When have you ever known our government to know what they're doing? | ​ @woodrowmagnus2535  I believe that people saying this needs to think a bit  more. | Baseline at 0.03%, stated that falling to 0.02% would be catastrophic but that rising to 0.04% is a tiny number we shouldn't worry about.  _x000d_
-DO YOU TRUST A FARMER TO UNDERSTAND CLIMATE SCIENCE IF THEY DON'T UNDERSTAND THE FLAWS IN THEIR OWN ARGUMENT? | Imagine a world where this isn't the case. Reminds me of where I work also. | ​ @jessicaandtrains7768  I think we still have some countries with knowledgeable n educated n capable/qualified or experts/professional ones. Unfortunately those countries are in so called "global south" or countries your politicians are "bad mouthings" in your msms... | They'll "do" what they were bribed to do,, regardless of relative skills. Unfortunately, most people in authority are. | Sounds like the Soviet Union</v>
+DO YOU TRUST A FARMER TO UNDERSTAND CLIMATE SCIENCE IF THEY DON'T UNDERSTAND THE FLAWS IN THEIR OWN ARGUMENT? | Imagine a world where this isn't the case. Reminds me of where I work also. | ​ @jessicaandtrains7768  I think we still have some countries with knowledgeable n educated n capable/qualified or experts/professional ones. Unfortunately those countries are in so called "global south" or countries your politicians are "bad mouthings" in your msms... | They'll "do" what they were bribed to do,, regardless of relative skills. Unfortunately, most people in authority are. | Sounds like the Soviet Union | For "non-technical" read "uneducated"... | Snafu.  Situation Normal all fuc#ed up | This is a 5th class, middle school question. People in charge with "climate change" have no idea wtf they are doing? | Unfortunate? It should be criminal. | This is how Common Purpose train their students so they can function within society. | Or they are told to do it anyway and take the heat. | This describes 100% of our government now. | And get paid millions or steal it | Technical people also make bad decisions based on ideology. That whole alarmism on co2 is collective histeria mostly among graduated people. | It’s no different than insurance execs telling doctors what procedures/tests they can and cannot do. Insurance companies have been dictating the course of a patients medical care for decades, not the patient’s doctors.</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
@@ -535,8 +531,23 @@
       <c r="D7">
         <v>3400</v>
       </c>
-      <c r="E7" t="str">
-        <v>be executed you mean... | No, be removed feom their positions. They are either incompetent, or complicit liars...take your pick. | and they're chuckling about their ignorance. | Fired, they should be fired. | Honestly..you knew the answer...? I didn't. | @markneedham8726 what did you think “400 parts per million” worked out to…..?? | @markneedham8726  I did, yes. It’s a basic point. | ​ @markneedham8726  are you a politician waiting to pass multi-billion dollar laws? No? Ok.... yeah that's probably some knowledge they should be privy to. | Yeah, you'd think one of them would say less than 1%.  Embarrassing. | And who elects these people again? | @shacktime  Nobody, they are not government officials. They were called as independent witnesses, representing construction companies (National Stone, Sand &amp; Gravel Association, Associated Builders and Contractors,American Road &amp; Transportation Builders Association and American Association of State Highway and Transportation Officials). You've been tricked into believing that they were government climate specialists. Better check your facts first.</v>
+      <c r="E7" t="str" xml:space="preserve">
+        <v xml:space="preserve">be executed you mean... | No, be removed feom their positions. They are either incompetent, or complicit liars...take your pick. | and they're chuckling about their ignorance. | Fired, they should be fired. | Honestly..you knew the answer...? I didn't. | @markneedham8726 what did you think “400 parts per million” worked out to…..?? | @markneedham8726  I did, yes. It’s a basic point. | ​ @markneedham8726  are you a politician waiting to pass multi-billion dollar laws? No? Ok.... yeah that's probably some knowledge they should be privy to. | Yeah, you'd think one of them would say less than 1%.  Embarrassing. | And who elects these people again? | Jail sounds more acceptable. | If they actually resigned every time they made a mistake like this then there would be none left. | Mr. Marc D. Williams, Executive Director, Texas Department of Transportation, On Behalf of the American Association of State Highway and Transportation Officials; Mr. Dwayne Boyd, Regional President, CRH, On Behalf of the National Stone, Sand &amp; Gravel Association; Mr. Aric Dreher, Assistant General Manager, Cianbro, On Behalf of the Associated Builders and Contractors; Ms. Paula Hammond, Senior Vice President, WSP USA, On Behalf of the American Road &amp; Transportation Builders Association. The panelists are not politicians (bar the Executive Director of Transportation in the state of Texas), three are business members on behalf of professional organizations. Never mind, you are right, these are the EXACT people that want to impose multi-billion dollar laws....just so they can line their own pockets on the hard work of the low wage earners that work for them (but I don't think they have the political views you think they have). | Cheshire Red - Resign? Fire them. | No, they should all be sacked!!! | Panelists: "They aren't paying us to know what we're talking about"... | Amen! | Not resign but fired | AMEN! | The point is not the amount of CO2 in the atmosphere being apparently negligible, but that the average concentration has increased by a 50%, and now it is way higher than what it was before the Industrial Revolution, what has been measured in ice cores going as back as 10 thousand years. 
+That's the part it is always conveniently silenced, same as chemistry and physics demonstrating that air having more CO2 retains more heat, that almost all climatologists agree that greenhouse gases are causing the climate to change - and the evidence we watch every day in the news catastrophe after catastrophe: heat waves, floods, droughts, wildfires, hurricanes, and the breaking of temperature records month after month, year after year.
+That guy is lying in the slimiest way possible. He knows he is lying, and manipulates half-truths to confound people. That was what he did to you. | @MariaMartinez-researcher  So now every weather event and anomaly is attributed to climate change now, huh?
+In 2019 and 2020, Arizona and the southwest hardly had any monsoon rains. That was attributed to climate change.
+In 2022, Arizona and the southwest had near record monsoon rains. In a few places, it did set records. That was also attributed to climate change.
+Right after Katrina hit New Orleans in 2005, scientists kept telling us we would have more and greater hurricanes. That was immediately followed by the 2006 - 2016 lull in hurricane activity, the longest period of hurricane inactivity since the 1860s. Scientists were initially puzzled by the lull in hurricane activity, but then finally attributed it to climate change.
+And why do climate scientists get so many predictions wrong, like "more and greater hurricane activity"?
+In 1988, NASA's Dr. James Hansen told Congress that Manhattan's West Side Highway would be completely under water because of climate change. That would take a sea level rise of roughly 15 ft. 
+Why does "no arctic sea ice" keep getting pushed back? And occasionally, there is bear record sea ice. A few years back, there was so much sea ice flowing out of the arctic ocean that practically every boat in the Alaskan commercial fishing fleet sustained damage.
+Takes of little or no sea ice go back centuries. That is what European explorers learned from Aleuts and Eskimos over 400 years ago, which prompted the search for the fabled northwest passage. And that would have been during the coldest period of the Little Ice Age.
+And how do you account for the stomach contents of the 3 Wooly Mammoths found in Siberia? Scientists discovered grasses and plants that no longer grow at the latitudes where the mammoths were found, because it is now too cold.
+How do you account for the fact that Danish scientists discovered that roughly half of Greenland was once forested, and most of the rest of Greenland had ground cover plants of the types found in northern Alaska and Canada?
+It was obviously much warmer in the past, so was all of the calamity? Why wasnt there an "existential threat" to life on Earth when it was obviously warmer. Some people actually think that the Earth burst into flames and explode because of climate change.
+And why do greenhouse farmers use CO2 generators? They raise CO2 levels 2-3+ times current atmospheric levels to greatly increase plant growth and crop yield? | @MariaMartinez-researcher  
+Also, why did Michael Mann completely omit the Medieval Warm Period and the Little Ice Age from his infamous hockey stick graph? 
+Why did Michael Mann message Dr. David Deming that "We have got to get rid of the Medieval Warm Period."</v>
       </c>
     </row>
     <row r="8">
@@ -570,10 +581,10 @@
         <v>147</v>
       </c>
       <c r="E9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
+        <v>I would propose them to breathe 5% CO2 air for half an hour. Just as an experiment. | Meh. Not knowing the percentage isn’t as malinformed as is believing that the fact it’s a small percentage means that isn’t a problem | @SigFigNewton  you might want to look up "the carbon cycle" before you put more shame on sir issac newton's name "sigfignewton" then you might want to realise that carbon dioxide is n odorless colorless gas and by its very nature does not contribute to trapping heat in our atmosphere due to the "greenhouse effect" (because it doesnt reflect energy/light) or whatever sham you have bought into. clouds make up far more of the heat trapping effect of the earth than any "emissions". there is real pollution and we have addressed that through technology like putting scrubbers and filtration systems on power station exhausts but by and large the green movement was just about selling people things. just like all capitalist movements are about SELLING YOU THINGS | its gonna be really great when you realise caring about the environment doesnt actually give you the knowledge to fix anything. co2 does not matter</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="str">
         <v>@philipdevonald1273</v>
       </c>
@@ -586,9 +597,8 @@
       <c r="D10">
         <v>1000</v>
       </c>
-      <c r="E10" t="str" xml:space="preserve">
-        <v xml:space="preserve">@Alexander Everhart  the government exists to infringe on your God-given rights to life, liberty, and the pursuit of happiness. | As too Here in Australia! | @williambyast7791  if the concentration of CO2 in the atmosphere was measured as seats at the Melbourne Cricket Ground, it would be 41 seats. In the 1900s it would have been just 27 seats, making the increase over approximately 120 years a measly 14 seats. There are approximately 100,000 seats at the Melbourne Cricket Ground. Just imagine going to the MCG with a school group of 41 students, on a week day, when no-one else is there, and have them sit down in the bleachers in the Southern Stand. It kind of puts it into perspective doesn't it? | @peterslocomb152   Your analogy is not focusing the issue. For your analogy to work you might compare consumption of snacks by the increase in people which would be a 51.8% increase in snacks. Again it only took .03% of atmospheric CO2 to keep the earth warm enough for life. If we had 100% CO2 all life that needed oxygen would be dead. This is 100 year old science, not some myth. | ​ @williambyast7791  
-Yeah a fellow Aussie here too, our government is a complete clown show, Danger Dan makes it bearable. | I haven't been to California since the early part of '99, and from the sound of it, I don't think I've missed much. | Not just America, you have to include the rest of the western democracies. | ....and ready for the oven. SMH | the people on the panel are the US congress... | It's shameful that they don't know this key fact. | @shaneanderson7757  it real doesn’t work that way. Some of it is that way but not even close to all. It’s a perfect storm of the greedy, ideological, and psychotic. We have bureaucrats with power you couldn’t imagine and they answer to no one.</v>
+      <c r="E10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -605,10 +615,10 @@
         <v>1200</v>
       </c>
       <c r="E11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
+        <v>That's what happens when Congress is only the first step to the big money with lobbyists and govt/private partnership. Follow the money. | @torylynne I have . The money is called oil investors. | Politics as usual | At best it makes them easily manipulatable. | Remember their chant "Follow the science!"  Pretty sure science could bite them on the @$$ and they wouldn't recognize it. | LOL and just what exactly is it that a climate denier knows about the SCIENCE of climate change | they know, and they also know the profit, both monetary and socially (as they impose their derranged will onto people) | The absolute number doesn’t matter, what matters is the change and the effect of the change. If it’s 5% or 0.5% or 50%. It’s quite irrelevant. The problem is, it shifts. | Panel is National Stone, Sand &amp; Gravel Association, NOT climate scientists. | Strange how your comment  has 678 likes in 2 months but the one I see above has none in a 10 month period? Is it being shadow banned ?  All it is saying is expanding on the comments of the panel and giving an opinion on the fact that the levels expressed would still be acceptable levels ! Then pointing out that those in power should look closer at the reality of CO2! &amp; its benefits to the planet.</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
       <c r="A12" t="str">
         <v>@GModBMXer</v>
       </c>
@@ -621,8 +631,10 @@
       <c r="D12">
         <v>843</v>
       </c>
-      <c r="E12" t="str">
-        <v/>
+      <c r="E12" t="str" xml:space="preserve">
+        <v xml:space="preserve">CO2 feeds the precious plants we need for living. 
+kind regards Legends | ​ @ordinarybear7037 too much CO2 disrupts agricolture, you know the thing we need to live | @MrJohnL21  Only when this country self destructs and/or is destroyed by external forces. It appears to be terminal. | Representatives instead of leaders. | here we go again with the empty demands. Like you or anyone else is gonna do anything about it LOL. You have no leverage just face up to the reality, stock your house for anarchy. Forget the "future" of the "country" | Too late. They already did | These people? Mr. Marc D. Williams, Executive Director, Texas Department of Transportation, On Behalf of the American Association of State Highway and Transportation Officials; Mr. Dwayne Boyd, Regional President, CRH, On Behalf of the National Stone, Sand &amp; Gravel Association; Mr. Aric Dreher, Assistant General Manager, Cianbro, On Behalf of the Associated Builders and Contractors; Ms. Paula Hammond, Senior Vice President, WSP USA, On Behalf of the American Road &amp; Transportation Builders Association. Look up who people are before making assumptions. | When he asked the question I thought "0.5%" and I'm glad it was close. Interesting how random sceptics seem to know a lot more about this than the policy makers and alleged experts. Bit troubling actually. | Vote them out.... | They don't, the banking cartel that funds government &amp; the so called opposition do. 
+Taxes don't fund government, see Grace Commission.</v>
       </c>
     </row>
     <row r="13" xml:space="preserve">
@@ -639,12 +651,8 @@
       <c r="D13">
         <v>49</v>
       </c>
-      <c r="E13" t="str" xml:space="preserve">
-        <v xml:space="preserve">As a result, CO2 is still not regulated.  428 ppm and rising. | @UnknownPascal-sc2nk  what's the rate of rise per year or decade? | @Intricacy9490 : How many different gases have they describing as being CO2 since Al Gore?
-What ever happened to CO Carbon Monoxide?
-It didn't just suddenly disappear as if never existed. 
-Everything organic which decays emits CH4 Methane. Chemically combine with ultrafine H2O water vapour &amp; after a number of years you are left with CO + H.
-Everything organic which is burned emits CO Carbon Monoxide. Chemically combine with ultrafine H2O water vapour &amp; after a number of years you are left with CO2 + H. | @alancharlton3867  I don't understand you. Why would anyone describe another gas as CO2? A CO molecule (carbon monoxide) has a much shorter lifetime in the atmosphere (months vs. centuries). As a result CO is not as significant as CO2. Moreover, when we combust fossil fuels a much higher quantity of CO2 results compared to CO. | The man who was speaking was as ignorant of science as the panelists.</v>
+      <c r="E13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14" xml:space="preserve">
@@ -665,7 +673,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" xml:space="preserve">
       <c r="A15" t="str">
         <v>@zakmartin</v>
       </c>
@@ -678,8 +686,14 @@
       <c r="D15">
         <v>954</v>
       </c>
-      <c r="E15" t="str">
-        <v/>
+      <c r="E15" t="str" xml:space="preserve">
+        <v xml:space="preserve">I think you are being generous | You are overestimating! | IQ of room temperature. | @LDU2U  In Celsius. | @LDU2U  IQ of room temperature makes no grammatical sense.    Room temperature IQ i think is what you were trying to say.   Saying something dumb while trying to call a bunch of people dumb is funny but really dumb | 100% of the grift. | As there are 4 panelist and the PPM is 440 witch would mean an average of 110, I reject this proposal.
+ppm is a term used in science to help idiots read numbers, but these idiots clearly know neither what % means or how to extract a % from a number.
+Which is astounding if they are US citizens as the Union has more than 300million citizens.
+meaning 3'000'000 is 1%,- 30'000 is 0.01%,-- 300 is 0.0001%.
+Which should not be hard to do, and is quite the necessary ability should you look at any statistics that informs you of WTF is actually going on.
+This means that back in the day when they said one in a million, it meant that a 747 fell out of the sky every other month. | ​ @torgrimhanssen5100  *which
+Also ppm just means, parts per million. | That high? | IQ is not measured as a percentage but I understand what your saying</v>
       </c>
     </row>
     <row r="16" xml:space="preserve">
@@ -714,10 +728,10 @@
         <v>119</v>
       </c>
       <c r="E17" t="str">
-        <v>But many of them are known by the DOJ, and the DOJ has shown how they protect those that are implicated in the globalist human trafficking networks.</v>
-      </c>
-    </row>
-    <row r="18">
+        <v/>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
       <c r="A18" t="str">
         <v>@pulltheotherone5035</v>
       </c>
@@ -730,8 +744,10 @@
       <c r="D18">
         <v>619</v>
       </c>
-      <c r="E18" t="str">
-        <v/>
+      <c r="E18" t="str" xml:space="preserve">
+        <v xml:space="preserve">They play dumb but they know it's a scam. | No one ever accused liberals of being bright. | Exactly  watch the documentary The Dimming | @lisacarden1309  thanks | @lisacarden1309  no!...don't! waste of time | It’s a grift | I mean, we can play the common denominator game if people want? Particularly when it comes to "the earth heats and cools on its own over time. This is natural solar/global behavior" type comments. In the past 140 or so years, what is the only consistent change in global/animal behavior? Humans, over time, increasing their rate of consumption of coal and hydrocarbons to generate energy. Another thing to look at is, the earth was about 5°C (10°F) cooler, 20,000 years ago. Let that sink in, if you factor in the 1.1°C (1.9°F) increase since 1880, that means 20% of the entire global tempature increase has happened in 120 years, while the other 80% took almost 20,000 years. Oh, and it just so happens that we have happened to also increase our carbon emissions from fossil fuels by about 10 fold since 1900.
+Don't get me wrong, I'm not advocating for an immediate switch to EVs or even solar. I get that the technology isn't fully there yet. That being said, it's getting there and we need to start making that transition now. Many people look at it as something that we can push off for the next generation. So they won't feel the impact of the change, but that helps no one and is particularly damaging to your, sons/daughters, grandchildren, neices/nefews, baby cousins, etc. Who will have to eventually deal with it, but with drastically less time to work with. This isn't something we can just wait for technology to catch up with. We need to invest and push it forward. | They're executives from transportation industries like railroad and trucking. It's not their job to know. Usually when you want to know something about the climate, you ask a climate scientist, not a 70 year old transportation executive. | @tripe2237  Yeah but they are the ones implementing the "solutions". 
+That is the issue. Is like going to a mechanic and the mechanic evaluates your car and then leaves it to the guy hanging around the garage selling sandwiches to decide what to do and how to fix it. | @tripe2237  He already knows, the point is to educate</v>
       </c>
     </row>
     <row r="19" xml:space="preserve">
@@ -748,15 +764,13 @@
         <v>536</v>
       </c>
       <c r="E19" t="str" xml:space="preserve">
-        <v xml:space="preserve">Let's you know it's not about the carbon dioxide and all about the power over the people. | @harrylazard805  So it's not about the carbon dioxide because it's such a tiny amount? Am I getting the argument here right? | ​ @Wolf-ln1ml  I think that's the argument, but he's also digging at them for not knowing (people don't know how to convert ppm to % as well, 10000 ppm is 1%).
-I'll note that at 0.1%/1000 ppm (a 0.06%/600 ppm increase) you can measure cognitive decline, we've gone from 280 ppm to 420 ppm since the industrial revolution, and higher ambient CO2 makes it harder to keep indoor spaces below that (see doi: 10.1289/ehp.1104789). A very small increase here is a huge deal, and at planetary scales you can't realistically undo emissions. | @reddragonflyxx  Yeah, I'll happily admit that them not knowing such basic stuff is pretty bad, but it's also all too common among politicians that I see it as a lesser evil. As long as they listen to the actual scientists and do their best to make policies based on that, I don't give a damn whether they know the terminology or numbers, or even whether they have half a dozen lovers in appartments or whatever (as long as it's not an abuse of power). I don't ask my plumber or tax accountant about their moral standards either, I just want them to do their job properly.
-As for the actual numbers, yep, that's my point. If that's indeed his argument, which I'm pretty sure it is, then he should have zero objections to me increasing the percentage of something in his body by a far smaller amount, say, 0.0001% - it's such a tiny amount afterall, it can't have any effect, so just let me get the cyanide... | @reddragonflyxx Yes and by his own admission dropping to 200ppm will start killing plant life. He’s trying to play tricks with people’s common perception that small numbers are insignificant. | WITH OUR MONEY! | @MichaelSmith-jj3pz 
+        <v xml:space="preserve">Let's you know it's not about the carbon dioxide and all about the power over the people. | @harrylazard805  So it's not about the carbon dioxide because it's such a tiny amount? Am I getting the argument here right? | WITH OUR MONEY! | @MichaelSmith-jj3pz 
 And our livestock, our lands, our supply chains, our vehicles, and our properties, and our freedom, etc. | Bingo patriot ,see you in the trenches just like Ukraine | THEE INTIRE WORLD..ISNT THAT GODSJOB | It definitely will not end well. | This is industry being ignorant genius
 The people who didn't know shit were the industry, they're not government environmental regulators, that is construction etc industry leaders. The government guy knew the numbers, they didn't | This is industry being ignorant genius
 The people who didn't know shit were the industry, they're not government environmental regulators, that is construction etc industry leaders. The government guy knew the numbers, they didn't</v>
       </c>
     </row>
-    <row r="20" xml:space="preserve">
+    <row r="20">
       <c r="A20" t="str">
         <v>@nmgn</v>
       </c>
@@ -769,9 +783,8 @@
       <c r="D20">
         <v>1000</v>
       </c>
-      <c r="E20" t="str" xml:space="preserve">
-        <v xml:space="preserve">Leave it to the liberals.... | Living and seeing the disaster every day. | And people want Gavin Newsome to run for president.  He might be the worst governor of all time. | @chadwendt8702  
-Close.  Newsom and Cuomo from New York are among the worst. | @chadwendt8702  You mean.... Mr. Gruesome Nuisance? That sorry excuse is my Governor, too! | I moved away from California!! The 80's &amp; Early 90's Was Fantastic! Fantastic Time's! | Gretchin Whitmer is the worst, hands down. | @acutler4745  so glad I moved 9 yr ago and missed Witchner! | Thanks to woke democrats | ​ @Carlos.Rivera  R are not much better !</v>
+      <c r="E20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -808,7 +821,7 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" xml:space="preserve">
       <c r="A23" t="str">
         <v>@Dn1sdr</v>
       </c>
@@ -821,8 +834,18 @@
       <c r="D23">
         <v>469</v>
       </c>
-      <c r="E23" t="str">
-        <v/>
+      <c r="E23" t="str" xml:space="preserve">
+        <v xml:space="preserve">Did you like how giddy they were about the question? 8%! | The dishonesty of the entire Republican Party is a disgrace
+SEE: Statista, Lobbying spending of oil &amp; gas companies in the United States during election cycles from 1990 to 2024, by receiving political party | @@MorganBucks80 I mentioned cooled by 1 billions years mark , check the relevant literature for a closer estimate | I knew the answer when I was in Grade 8. (1958)   What happened??  We got dumber | This is what happens when industry representatives are in charge. There were no experts present in this video. | the best one I've heard is during a house committee investigation , an oil CEO asking the head of the Environment Protection Agency 
+"how come there is crude oil in the Arctic "...the guy shrugged and answered it must have migrated there " ......the oil man smiled and said nothing ,
+he knew the oil was formed some millions years ago when the north pole was ice free and full of vegetation | @sparkyfromel  That was 50,000,000 to 30,000,000 years ago.  Definitely before the enormous effects of human energy use during and now following the industrial age.  
+How many millions of years did the process of warming and subsequent cooling take?  We are seeing dramatic increases in less than 100 years with no real attempts at reversing the trend.  Life can adapt but change must be slow enough to allow adaptation lest extinction.
+Since you are informed perhaps you might also consider that over 10's of millions of years our sun's output becomes hotter (heats up because the percent of hydrogen fusion decreases as hydrogen is converted into higher molecular weight elements) during it's life (see Betelgeuse).  The sun bombards the earth with more energy now than 30,000,000 years ago.  Another factor in considering decision making based on reality rather than cherry picking or profound ignorance (see video). | @wallyhunt  since 1 billions years the earth has been cooling substantially ,
+for 2.5 millions years we are locked in an unstable serie of cycles called the Quaternary glaciation , there were several episodes of global cooling previously but this time it's different , some speak of Milankovitch cycles but they always were there , some presume it's due to the Antarctic current establishing a block around the newly frozen Antarctic pole 
+I've seen this kind of thing at work with industrial process control systems , it's a critical instability which is increasing  , 
+the feed-backs are over-correcting , a bit like loosing control of a car at high speed , and trying to steer back straight .
+the Ice ages get deeper each times , 
+now we are at the very narrow warm peak | @sparkyfromel  Are we talking the formation of crude oil or coal?</v>
       </c>
     </row>
     <row r="24">
@@ -856,10 +879,10 @@
         <v>789</v>
       </c>
       <c r="E25" t="str">
-        <v>I'd say it's 5?! | No, it's more like asking them what the air/fuel ratio is in an internal combustion engine.  I'd be will to bet, they wouldn't know either. | It's five, hence the 'V' | @ricardotorres9342 | Lol. He could have just asked, "What's a V8?" They'd probably say, "It's a vegetable drink." lol. | Lol. | "at least 20, im going for the high end here!" | To be honest, I don't think the executives at Ford would know that either. They seem to think a 4 door crossover is a Mustang. | Nah. More like asking them what correct MAF sensor reading is on lates test Diesel engine. | I think if you buy a case of V8, the number of cans in the case would technically be cylinders, but I can't drink that stuff.  I'm not sure why Ford would know about a vegetable drink though? | "It's 1 right?? One engine, one cylinder?" Lmfao! | no that would be asking hoe much CO2 it emits at 72,4 km/h | These are car manufacturers not climate scientists | No, it's more like asking someone who is in the roads/bridge building/infrastructure industry (as these people are) what is the ratio of air to fuel in a direct injection system vs a 4 bbl carburator in a V8 at idle. The answer is, "I don't know, I build roads, you idiot." He should have answered the original question, "Neither we nor you are a climate scientist." | @OneCalledChuck  I agree. But annoyed at Forbes for posting this. | @OneCalledChuck  Except the panel was lecturing everyone on CO² | Anytime you try to explain it to some rando tho they say but we have so many cars how can we not be effecting it.... | @firebush1343  when you say over you're making a values statement. | @firebush1343  affecting | ​ @firebush1343  well to be fair you do have an over reliance on cars there in the US, a problem that won't be solved with EVs either (at least not with electric cars). | Not really a good example since you could anyone even with zero knowledge of what an engines is and chances are they would get that question correct | Worse, they insist there must be less cylinders, and you ask how they reached that conclusion - and they just look blank and say "no idea, we're just paid to say this" | That's the difference between a corporation that develops and manufactures products to a government that regulates what the product is.  Any dummy can pass regulations and stay in business, even get elected as president of the US, as we have seen. | The guy in the center is a lobbyist for the sand/gravel (concrete aggregate) industry trying to get them to pass exemptions to build more roads. He dgaf</v>
-      </c>
-    </row>
-    <row r="26" xml:space="preserve">
+        <v>I'd say it's 5?! | No, it's more like asking them what the air/fuel ratio is in an internal combustion engine.  I'd be will to bet, they wouldn't know either. | It's five, hence the 'V' | @ricardotorres9342 | Lol. He could have just asked, "What's a V8?" They'd probably say, "It's a vegetable drink." lol. | Lol. | "at least 20, im going for the high end here!" | To be honest, I don't think the executives at Ford would know that either. They seem to think a 4 door crossover is a Mustang. | Nah. More like asking them what correct MAF sensor reading is on lates test Diesel engine.</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" t="str">
         <v>@scottjohnson7780</v>
       </c>
@@ -872,13 +895,8 @@
       <c r="D26">
         <v>487</v>
       </c>
-      <c r="E26" t="str" xml:space="preserve">
-        <v xml:space="preserve">I knock JK Rolling's writing a lot, but that line about "The Ministry must be seen doing Something!" rings true to this day globally. | Its a grift. | And also to make it seem like they're doing something to tey and justify their jobs - bit like Local Councils. | This is an example of government being industry.
-Would be nice if they understood how damaging CO2’s warming will be | ​​ @SigFigNewton : CO2 &amp; SO2 are actually coolants, sitting relatively low in the atmosphere.
-H2O sits at all levels in the atmosphere.
-CH4, H2O &amp; H on the other hand, are high up in the atmosphere concentrating the heat  like when you hold a magnifying glass to concentrate the Suns rays on a particular spot, in their case from a wider diameter above down to the smaller diameter of the Earths surface. | This is industry being incapable 
-The people who didn't know shit were the industry, they're not government environmental regulators, that is construction etc industry leaders. The government guy knew the numbers, they didn't | This is industry being incapable 
-The people who didn't know shit were the industry, they're not government environmental regulators, that is construction etc industry leaders. The government guy knew the numbers, they didn't | The “just do something” attitude exists because companies already do nothing. Did you know, that the single largest producer of CFCs intended to oppose the Montreal protocol and only got on board when they realized it would give them a competitive advantage in the European market? They were willing to sacrifice the literal OZONE LAYER, perhaps the most important part of our planet’s atmosphere (if you like living anyways) for their profits, and only got on board when they figured out it could be profitable. So yeah, politicians, representing the people don’t know the science, but they at the very least know the policy recommendations. | You’re confusing what scientists actually say with what climate deniers claim that they say. | "jesus is coming. Look busy."</v>
+      <c r="E26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -929,7 +947,7 @@
         <v>561</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>He, too, is a fool cuz he doesn’t understand it himself. | No, he only exposed himself as not having even a surface level understanding of physics | these are people making equipment not policy wonks, so they are not to blame | @samthing4thetrack806  Yet, they promote the fallacy, take the subsidies, and don't question it.. yeah, totally unrelated, its not their fault.. | @yeost187  yes they are daft | @samthing4thetrack806  They are part of the policy process and yet they know nothing.</v>
       </c>
     </row>
     <row r="30" xml:space="preserve">
@@ -960,10 +978,10 @@
 Yea but you do know we're surrounded by mostly water.. 
 Trees on land don't even come anywhere close to the oxygen released by the life we don't see under the sea.. 
 You need to be more worried about cleaning up our oceans.. 
-Rather than some guys truck..</v>
-      </c>
-    </row>
-    <row r="31" xml:space="preserve">
+Rather than some guys truck.. | Sir LaMafa stands up for the people he is a great representative for rural America 🇺🇸.....</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" t="str">
         <v>@JoeBlowUK</v>
       </c>
@@ -976,18 +994,8 @@
       <c r="D31">
         <v>1200</v>
       </c>
-      <c r="E31" t="str" xml:space="preserve">
-        <v xml:space="preserve">I pump my aquariums FULL of CO2, what I get from doing that is very fast lush plant growth. | @xisotopex  and if you lived in a hot country you would need a chiller BECAUSE THE FUCKING TEMPERATURE WOULD GO UP | @xisotopex  
-Do you kill the fish? | @neilkurzman4907  no it doesnt kill the fish lol. | @xisotopex  
-If you were actually blowing CO2 into the water, it would. | @neilkurzman4907  no it wouldnt, and no, it doesnt. and yes actual CO2 is being injected into the water column. most people use compressed CO2 some people use a liquid form of CO2 which is not quite the same thing and not quite as effective... | @xisotopex  
-And how do you regulate the CO2 so that it doesn’t affect the fish?
-So it requires an electronic control system to keep the level safe.
-Either way, I don’t think your fish tank it’s affected by climate. | @neilkurzman4907  if the fish are at the surface gulping air, you have gone too far...  JK. you can use some sort of electronic monitoring but not necessary...  a few chemical tests to establish a baseline... the point is that CO2 is not the bugbear people think it is... the natural; process for glbal warming and cooling is NOT understood completely, and is certainly far more complex than a relative few data points from some ice cores. | @xisotopex  Last time I checked, humans are not plants. | Idiocracy | and if you ban plant food then you pretty much ban all food since everything we eat is either plants, eats plants or eats animals that eat eat plants lol. their argument is utter stupidity | humans can easily breathe in an atmosphere with 1000+ ppm co2. actually in homes co2 levels can go up to 3000 ppm. | Using word "green" for this movement is even worse than ridiculous. The Earth would get greener if CO2 concentration gets higher instead lower. | @wanglimr That depends on the level of CO2
-1. There is a maximum that plants can use.
-2. More CO2 also means a higher average temperature. The same structure that takes CO2 from the air (Stoma) also loses a lot of water. So while the plants have more CO2 they dont have enough water to photosythesise. 
-(Sorry for making some mistakes- I'm from Germany and only learned English in school)
-Now I study Biology and Classical Philology at the University. 
-Have a nice day | ​ @wanglimr  it already has, green areas are expanding worldwide. Thar never gets mentioned though for some reason</v>
+      <c r="E31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1024,7 +1032,7 @@
         <v/>
       </c>
     </row>
-    <row r="34">
+    <row r="34" xml:space="preserve">
       <c r="A34" t="str">
         <v>@KinuGrove</v>
       </c>
@@ -1037,8 +1045,9 @@
       <c r="D34">
         <v>663</v>
       </c>
-      <c r="E34" t="str">
-        <v/>
+      <c r="E34" t="str" xml:space="preserve">
+        <v xml:space="preserve">it's like When Elon simply asked questions back to the BBC "reporter" James Clayton. The other side simply talk out of their behinds | @luigivincenz3843  Na Elon was much more childish than that, he didn't even have any figure's of his own. But I guess both of them asked a very stupid question and made themselves look stupid though so maybe it is. | These are your rulers. Enjoy! | They put the EV Cart before the horse Infrastructure  meanwhile, plug your EV into your gas &amp; oil supplies getting your electricity. | Don't let human rights get in the way of government business | ​ @StartabusinesswithJustin  And elite individuals. | Exactly,  don't confuse me with facts.
+BTW Elon rules! | The statistic isn’t relevant to climate change, 99% of the atmosphere is nitrogen and oxygen but neither of those are greenhouse gases like CO2, they don’t trap heat in the planet. CO2 is still the most important greenhouse gas that humans are changing the concentration of. | @bdog734  wow so you're saying my intellect is just under genius? Well thanks pal</v>
       </c>
     </row>
     <row r="35" xml:space="preserve">
@@ -1082,7 +1091,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" xml:space="preserve">
+    <row r="37">
       <c r="A37" t="str">
         <v>@dkvikingkd233</v>
       </c>
@@ -1095,10 +1104,8 @@
       <c r="D37">
         <v>953</v>
       </c>
-      <c r="E37" t="str" xml:space="preserve">
-        <v xml:space="preserve">The people who would vote emotionally will accept it, or he knows the truth but he's on some external payroll | @wizardoffrobozz  "The people who would vote emotionally will accept it..."
-Exactly, EMOTIONALLY, not LOGICALLY, and yet fail to comprehend why their "logic" fails. | The last three years have demonstrated that ignorance is no barrier to making decisions about how we should live. | @darylfoster7944  "The last three years have demonstrated that ignorance is no barrier to making decisions..."
-We can call that BIDENISM. | In fairness, if you asked them how many parts per million of the atmosphere were CO2 as measured at Mauna Loa, they might actually be able to tell you, since that is a publicly known number which does indeed translate into 0.04(23) percent. But it does show how unfamiliar many policymakers are with actually crunching ANY numbers. | It's not ignorance, it's a play to gain power. | what you say is so important. Here in France same problem, our leaders are so ignorants, it is scary. | If you're a statistician don't ask your doctor about epidemiological statistics. | ​@Chris Jones because a large part of their agenda to change our daily lives is based on this.  Maybe they should know about the things they give as a reason for what they are doing. | ​@@chrisjones5215because they are law makers?</v>
+      <c r="E37" t="str">
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -1118,7 +1125,7 @@
         <v/>
       </c>
     </row>
-    <row r="39">
+    <row r="39" xml:space="preserve">
       <c r="A39" t="str">
         <v>@LS-lb7pw</v>
       </c>
@@ -1131,8 +1138,10 @@
       <c r="D39">
         <v>461</v>
       </c>
-      <c r="E39" t="str">
-        <v/>
+      <c r="E39" t="str" xml:space="preserve">
+        <v xml:space="preserve">L S, We're lucky up here in his district. Northern California. | @larsord9139  That explains his sanity and common sense.  Nice to see my home state still has some sane people and politicians there. | And yet you still elect people like Gavin Newsome and Nancy Pelosi . | @spedoclctr  not me, ever | @spedoclctr  And we are glad we did ! | @spedoclctr  the cities do not the whole state.
+The problem is you have San Francisco, San Jose, LA, outnumber the entire population of Northern California almost 2 to 1. Why do you think Northern California wanted to split off? | Just love his name | I could not agree more | It's to late goodbye Commiefornia | ​ @larryzach7880  
+Yeah the whole of the US is screwed.</v>
       </c>
     </row>
     <row r="40">
@@ -1169,7 +1178,7 @@
         <v>Oil and water, oil and water. | Oil and cents do | Democrats are at least smart enough to know that an increase from 300 too 400 PPM over such a short time is not a small increase, as LaMalfa describes it, that's a massive increase. | @simonharris4873  Can you tell me any scientific or sound basis as to why EVs should be forced on everyone as the only solution, or as a solution at all? | @simonharris4873  have you read anything about the increase of plant growth which is helping the carbon situation?  More food for the plants means they are growing faster and are capturing more carbon.  You have to at least understand that scary = money and loss of freedom.   Should we do something? Sure, but at least attempt to bring a balanced approach. | @MJ T  Plant growth was never a problem during the many 1000s of years when we were at 275 PPM.</v>
       </c>
     </row>
-    <row r="42" xml:space="preserve">
+    <row r="42">
       <c r="A42" t="str">
         <v>@MrSaemichlaus</v>
       </c>
@@ -1182,11 +1191,8 @@
       <c r="D42">
         <v>553</v>
       </c>
-      <c r="E42" t="str" xml:space="preserve">
-        <v xml:space="preserve">The more educated one becomes the more compartmentalised they become, and follow the money, this is how higher education rumbles. Mattias Desmet has explained it quite nicely and how higher does not always mean wiser. | @MotorcycleEngineering101  If you will use that argument we may as well use snail races to determine politics. Having a basic respectable education would be a start in giving a nation a flying chance of collective success. | if it's increasing at the same rate, every politician will be a climate expert soon. | yep | 0.04% is generous. | and the people believe them without questioning anything | Depends how you measure it. The 0.04% is by molecule... in every million molecules, around 420 are CO2 molecules, up from 350 not too long ago. It is a bigger molecule than the oxygen and nitrogen molecules, you only get 0.04% if you ignore its bigger size and weight. However, it is the total amount that matters... like, a thick warm blanket on your bed will be mostly air, but if you get completely underneath it, the small amount of heat that it traps starts to add up. If the amount that it traps is not enough, on a cold night, then adding another blanket, that is also mostly air, will trap a bit more..… you won't be hotter straight away, but as the trapped heat adds up, you will slowly warm up to a higher temperature. If you are out lying in the hot sun, like our planet is, wrapping yourself in a blanket of billions of tonnes of carbon, even if that blanket is mostly just air, will get you warmer. The historical 0.035% of CO2 meant that we were warming up very slowly. The current 0.042% is billions of tonnes of extra blanket that means we are warming up a lot quicker now. We are still adding more blanket, and we have no way to simply remove a blanket when we get too hot. | @annoloki  Good anology, Co2 is also heavier than air and sinks into the soil once it it cultivated, we did an experiment for several years where we added carbon from our log burner, pure charcoals into the soil and the results were bigger and better vedge than areas where we left it unfertilised, the carbon in the soil sequesters Co2 and holds it there, once we reach a certain level like during the Medieval Warming Period we will have much more food growth and need less additives to force feed the crops, like we witnessed in Europe when the biggest and best cathedrals were built from the fat of the land and great summers for growing food.
-If you take Russia for instance they still have much of their vast forest which will grow into a fruit basket in time, areas now under the frost will come online and we will have to move in order to survive, it will come to pass one day, watch this space. | @annoloki  You just forgot to mention two very important things. The first one is that the Sun plays a role much more important then ourselves. Historicaly, it's not the levels of CO2 that drives the temperatures of the Earth, but other way around. It's the temperature that drives the CO2 levels. The second one is that Earth itself has developed a series of mechanisms to compensate these things for billions of years. For instance, a warmer Earth has more water vapor in the air, which creates more clouds, which reflects more sunlight, helping it to cool it down. There is absolutely no factual reason regarding climate to this CO2 madness. The reasons are exclusively politics and control. When you create an common enemy, it is much easier to lead people believing that it is a good thing to let go their natural 1st gen human rights. | @annoloki  as co2 rises vegetation increases absorbing more heat, nitrogen and oxygen make up most of the atmosphere and weights are very close co2 is approximately 3 times as heavy. But is more of a net than a blanket at this point. Being that heavy many other things are a bigger problem than co2. | ​ @dpirkl4560  yea u think vegetation grows better with drought with storms and more extreme weather's ? | @faikerdogan2802  doesn't mean co2 is the primary culprit of disasters, that's like saying co2 causes every disaster on earth.
-There are also many other factors such as environmental damage and pollution. There's no mastermind to the problem at large, that's a stupid way of thinking. | @Elka_Sir  what are u talking about?? This specific problem has this specific reason. No one is saying CO2 causes earthquakes or some stuff. It effects the climate. Drought and storm is apart of climate. No one is also saying every storm is because of that. | ​ @faikerdogan2802  where is this extreme weather, of which you speak. We have had forest fires, Tornadoes,  floods, heat waves from time immemorial. | @faikerdogan2802  no, vegetation likes co2, many studies look it up js. | @faikerdogan2802  if co2 is the only problem, why did we have the Montreal protocol, why are refrigerants regulated. Countries like China and US have been trying to manipulate weather for years. We have had droughts, floods, hotter and colder periods of weather. We really don't have a long accurate history of data to look at. Yes we can see swings but accurate data is very recent especially globally in real time. | @dpirkl4560  If China is trying to manipulate the weather why are they building an average of 2 coal plants a week | @faikerdogan2802  you fully ignore, technology what can change weather, and keep blaming co2 or methane for it.
-UNO forbid weather war-fare in 1977. now try to debunk other views what not suits your agenda or belief. think</v>
+      <c r="E42" t="str">
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -1223,7 +1229,7 @@
         <v/>
       </c>
     </row>
-    <row r="45">
+    <row r="45" xml:space="preserve">
       <c r="A45" t="str">
         <v>@EyeExcelThenPrevail</v>
       </c>
@@ -1236,8 +1242,9 @@
       <c r="D45">
         <v>423</v>
       </c>
-      <c r="E45" t="str">
-        <v/>
+      <c r="E45" t="str" xml:space="preserve">
+        <v xml:space="preserve">Yes, quite agree how calm and collected this Representative is but one feels that instead he should actually be calling for all these illiterate tyrants to be tarred and feathered prior to having all their funds sequestered and then jailed for a considerable period. Thanks for listening. | @MickeyMouse-ul2zs  Or they could be educated! | Well then his common sense is wrong because he is trying to say that the fact that CO2 is in small concentrations in the atmosphere the effects will be negligible. That is not necessarily the case. There are many examples in nature of substances in small quantities that can have noticeable effects. | It's true, climate change science is not commonly understood, which is why ignoramus politicians like this man get away with saying $#@! like this and you guys all fall for it. | Another interesting question would have been, "Since America is 4.25 per cent of the population of the planet, how much effect does destroying our way of live have on the other 95 per cent of the planets CO2 production? | @ralphholiman7401  The united states is 15% of the world emissions so it would affect 15%. Obviously the data should not be about world population. Also if u want factory jobs and the automotive industry thriving in the USA invest in electric vehicles. It is most obviously the easiest. | Pretending that the % of CO2 in the atmosphere is in any way relevant or a number ur supposed to know if u claim to be an expert on the topic is not common sense. It is showing that you are staggeringly ignorant on the theory. | @beertje6394  Maybe you should consider spending more energy on becoming the best person you can be and serving your community instead of trying to play God.  Let's start there before we go trying to control minute changes in the earth's atmosphere, as if you even know how.  There always seems to be a big group of "expert scientists" at the centre of every calamity. Strange how that works, isn't it. | @beertje6394  yes, the ones complaining about CO2 not knowing the % of CO2 is not relevant at all...
+Who’s staggeringly ignorant again? | @360lootgoon3  Correct the % of CO2 in the atmosphere is entirely irrelevant to climate change. It is about the increase in CO2 in ppm and how this inhibits the earth from regulating its temperature. | Gavin Meinzer - Can you point out to me one time in the earth's entire history where detrimental and beneficial climate change didn't occur simultaneously? | @beertje6394  The increase of CO2 in PPM is and increase in %! | @beertje6394  People tend to theorize themselves straight out of reality. You haven't noticed that? Common sense has always been the best barometer of truth (no pun intended).</v>
       </c>
     </row>
     <row r="46">
@@ -1254,7 +1261,7 @@
         <v>445</v>
       </c>
       <c r="E46" t="str">
-        <v>Clown world what a ridiculous decade we live in | Like klaus Schwab and his cronies over in Davos, Switzerland. Sorry Klaus won’t comply | There is a "protest". Every four years, and every adult can participate. | Yes. | Omg not WOKEAPHOBIA!  I needed a good laugh today and that one did for me! | @amiehulscher7156  Wokeaphobia is just as dumb as any of those "phobia" words people use not having any idea what Phobia even means. | @amiehulscher7156 help mommy the woke is coming for me! But they still can’t define woke ️ | @jeremys6747  If you have no idea what woke means then why should we define it for you troll boy?</v>
+        <v>Clown world what a ridiculous decade we live in | Like klaus Schwab and his cronies over in Davos, Switzerland. Sorry Klaus won’t comply | There is a "protest". Every four years, and every adult can participate. | Yes. | Omg not WOKEAPHOBIA!  I needed a good laugh today and that one did for me! | @amiehulscher7156  Wokeaphobia is just as dumb as any of those "phobia" words people use not having any idea what Phobia even means. | @sam-psonsmith9951  nope, I'm 100% positive that I understand the meanings of both those words that's why I put them together and even though wokeaphobia, I will admit is not a word in the dictionary,  that does not mean that  it doesn't apply in context with the OP's comment.  Stop trying to be the wokeass meaning police!  You don't even own a woke flag but maybe you should?I'd rather be a woke person then be ASLEEP because I care about other people who are not like me and I don't even know. I care about other people's feelings about stuff before my own. I'm not underprivileged but I have the capacity to empathize with and understand those whose journey may not have been as easy as my own and I can admire and aspire to be as strong as those you'd rather not think about, let alone show any tolerance or humanity to! I'm not afraid or ashamed of who I am OR WHO KNOWS what I think but I am afraid and ashamed of so many WHO LOOK LIKE ME BUT THINK LIKE YOU! | @amiehulscher7156 You may know the definition of "phobia" but it seems that you don't because you are misapplying it. The majority of those people are not afraid of wokeness, they are repulsed by it, just as a person biting into their sandwich and finding out that it's rotten. | @amiehulscher7156 help mommy the woke is coming for me! But they still can’t define woke ️</v>
       </c>
     </row>
     <row r="47">
@@ -1271,7 +1278,7 @@
         <v>365</v>
       </c>
       <c r="E47" t="str">
-        <v>I’m Bigly, and I approve this message!  In all seriousness… WTF. | Bigly | You are mistaken. Their plan is much bigger. 40 Percent of the world population will never see this Green transformation. Basically starvation for the rest. | ​ @richardv9648  how come? | Then they wouldn't have any power if it failed | What job? He showed that 99% of the population didn't know this number. Do you know what temperature would have earth without any CO2 on the atmosphere? | Bigly | Another  for bigly!!</v>
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -1305,7 +1312,7 @@
         <v>7</v>
       </c>
       <c r="E49" t="str">
-        <v/>
+        <v>Yes. Thank God. This isn't by accident, This is what our Educational system has produced,  we need to clean house.</v>
       </c>
     </row>
     <row r="50" xml:space="preserve">
@@ -1323,7 +1330,7 @@
       </c>
       <c r="E50" t="str" xml:space="preserve">
         <v xml:space="preserve">We will stop Northstream. | My butts been wiped. | The only truth Brandon ever told. | Bumbels actually said that. | " I don't need your vote to get into the office I need you after I get in the office "
-Joe Biden | You seem to be on the wrong thread; this one is talking about infrastructure. | @grahamhodge8313  yet it is a wonderful reminder isn’t it?   Hope it didn’t cause any damage…. the time and effort of responding and so forth.    You could have just moved along to NPR or whatnot. | It's in China.People work for the government by passing examinations and accumulating experience from the work practices of grass-roots civil servants.And the west depends on who is more eye-catching to work for the government. | But we can’t prove it so we just repeat this until all smooth brains agree | @jeremys6747  More like all the smooth brains deny it, don't you? | @DevilsAdvocate43  y’all so talkative online yet seem to be mute when in court. Sad. | @DevilsAdvocate43  Lah lah lah climate change.   Good lord, is your entire world directed by emotionalism, or is there any objective measure involved, like, a checkbook or a property line (Oops, you probably don’t own property… terribly sorry).    See the history of Scotland as one of many examples.   Well documented periods of NO crops due to cold, and GREAT crops due to heat.  Honestly, it’s tiresome having to continuously educate you people.</v>
+Joe Biden | You seem to be on the wrong thread; this one is talking about infrastructure. | @grahamhodge8313  yet it is a wonderful reminder isn’t it?   Hope it didn’t cause any damage…. the time and effort of responding and so forth.    You could have just moved along to NPR or whatnot. | @samseven5260  It is tiresome correcting people who should know better.  I could move along to many places but sometimes one has to try and overcome the idiocy that is so prevalent in America, much of it promoted by people like you. | It's in China.People work for the government by passing examinations and accumulating experience from the work practices of grass-roots civil servants.And the west depends on who is more eye-catching to work for the government. | But we can’t prove it so we just repeat this until all smooth brains agree | @jeremys6747  More like all the smooth brains deny it, don't you?</v>
       </c>
     </row>
     <row r="51">
@@ -1340,10 +1347,10 @@
         <v>243</v>
       </c>
       <c r="E51" t="str">
-        <v>100% | The burning of fossil fuels affects the concentration of CO2 in the atmosphere. Before the industrial revolution, the amount of CO2 in the atmosphere was about 288 ppm. We have now reached about 414 ppm, so we are on the way to doubling the amount of CO2 in the atmosphere by the end of this century. Scientists say that if CO2 doubles, it could raise the average global temperature of the Earth between two and five degrees Celsius | @MikeAIright  and? what do you not care about the trees? why you soo adamant on suffocating the trees? you do know that tree's don't inhale oxygen, right? | you fall for it didn’t you?</v>
-      </c>
-    </row>
-    <row r="52">
+        <v/>
+      </c>
+    </row>
+    <row r="52" xml:space="preserve">
       <c r="A52" t="str">
         <v>@Crowbar11115</v>
       </c>
@@ -1356,8 +1363,9 @@
       <c r="D52">
         <v>301</v>
       </c>
-      <c r="E52" t="str">
-        <v/>
+      <c r="E52" t="str" xml:space="preserve">
+        <v xml:space="preserve">And below .02 plants die. | the next question after that is now much does man contribute to CO2 levels, hint, it's insignificant. | @axeman2638  whats even more hilarious is that all the cars, buses, trucks, etc we see account for less then 1% of all emissions from internal combustion engines worldwide yearly. Shipping industry is 70% but they can continue to burn the dirtiest fuels of all | @axeman2638  `if we could calculate the number of people needed to significantly alter that balance we could figure out de designed limits  of the planet ,that would be a good number to have . | @rovidius2006  anyone that thinks the earth is over populated needs to lead by example.
+Man's CO2 emissions are a net benefit to the planet, a small one , but still a net benefit. | @axeman2638  Little studies done in 80s show increase plant life due to elevated Co2 levels by similar amounts ,0.4 % may be a failsafe value . | Exactly right. | It is now above 0.04% so you expected the wrong answer from them.  We are at 429 PPM according to numbers I could find.  BTW: In 1998 it was about 330PPM. | @kensmith5694  thats an avg concentration. Most of the year it sits much lower then that. Essentially the concentration lvls are dominated by the northern hemisphere due to the majority of carbon based life existing there. So as we enter the growing season our co2 concentrations are at the highest and they immediately drop off a cliff as biomass strips it out of the atmosphere. For the rest of the growing season it will sit at ots lowest lvls until fall comes and all of that organic matter that is carbon based begins decaying and releasing the co2 back into the atmosphere. It will rise steadily until it reaches its peak as the growing season starts and the cycle begins again. The main things are that we are at the extreme low end of the scale for co2 concentrations in earths atmosphere over the last billion years and all life is carbon based and we get that carbon from Co2. Its what makes life possible | @kensmith5694  PPM means Parts Per Million. You convert to percent by dividing by 10,000. Guess what 429 PPM is? 0.0429%. It rounds down to 0.04. | @jmerced  I know what 400PPM means.  Look at what I was responding to.  0.03%-0.04% doesn't include 0.0429%.  0.0429^ is in the range 0.04%-0.05%.  What I said was 100% correct.  You had no reason to be insulting when you mistakenly thought you were correcting me. | @kensmith5694  How much better do you think it will get? Does the Russian volcano help increase much? | Research is hard for the fear mongers.</v>
       </c>
     </row>
     <row r="53">
@@ -1393,8 +1401,28 @@
       <c r="D54">
         <v>495</v>
       </c>
-      <c r="E54" t="str">
-        <v>kun gf lu d eaths would also be an acceptable answer. | lol that's a funny one haha | Alex: Sorry, the adjudicator says you're wrong! Your answer was technically right but 'coronavirus' is more right, so you lose points. | Alex is dead? RIP Mr Trebek we love and  miss you except for this guy He doesn't respect you AT ALL! | @amiehulscher7156  just because you dont understand a joke doesnt mean it isnt funny. | @amiehulscher7156  lighten up Francis | Just because you don't understand something doesn't make it a hoax. | @GeoRyukaiser   just because you hoax something doesn't make it a fact either. | @GeoRyukaiser  Bwahaha..... | @GeoRyukaiser  if the energy industry was nationalised (gov ceasing the means of production) global warming would never be brought up again. As if that was the goal the whole time. | @GeoRyukaiser  no one understands truly understands it, that is why perdition after perdition falls.</v>
+      <c r="E54" t="str" xml:space="preserve">
+        <v xml:space="preserve">kun gf lu d eaths would also be an acceptable answer. | lol that's a funny one haha | Alex: Sorry, the adjudicator says you're wrong! Your answer was technically right but 'coronavirus' is more right, so you lose points. | Alex is dead? RIP Mr Trebek we love and  miss you except for this guy He doesn't respect you AT ALL! | @amiehulscher7156  just because you dont understand a joke doesnt mean it isnt funny. | @amiehulscher7156  lighten up Francis | Just because you don't understand something doesn't make it a hoax. | @GeoRyukaiser   just because you hoax something doesn't make it a fact either. | @GeoRyukaiser  Bwahaha..... | @GeoRyukaiser  if the energy industry was nationalised (gov ceasing the means of production) global warming would never be brought up again. As if that was the goal the whole time. | @guillermoelnino  No, it would still be brought up. Why? Because the fossil fuels would still be releasing more CO2 then the natural CO2 flow can process. Which means it would continue to concentrate and cause problems.
+Personally I have no idea why the energy industry is dragging its feet since smaller companies are raking in profits from non-fossil fuel energy production. | @GeoRyukaiser  so, is it ok for an unelected panel of people (like the ones here) that help create laws and enforce compliance to said laws, that affects everyone but they haven't a single clue what they are talking about nor a shred of evidence or data to support their ideas? Is it ok for them to force changes simply based upon imagination and mindless guessing? 
+If a financial guru or company of gurus were to take people's money and promise positive results but offered only imaginary unsubstantiated information on the processes, then they, through the pulling of yours and other people's resources made them self or selves very rich and left you poorer than before with no positive results as they move on to do the same to others.....wouldn't that person or group of people be considered fraudsters??? 
+They disseminate fraudulent information, use unwarranted fear tactics to take people's money and force major changes, than as they reap the rewards as you are left with the mess and the bills! Sound like a fair deal? | ​ @damieno3470  Being underprepared and being caught off guard by an older man asking something a high schooler or first year physics student should know does not invalidate any of the research. Given how little these people know I doubt any of them are researchers in the field, or done those early classes, thus I consider their opinions irrelevant in regards to the facts.
+And the facts remain that every single claim that anthropogenic climate change isn't happening fails immediately upon exposure to the data. It is happening and at rates not seen since massive catastrophic events like the time of Siberian Flood-Basalt event... when all of Siberia was covered in lava by the eruption of a super volcano. No such natural event has happened to cause the levels of CO2 and temperature rise in the time frame observed to explain away present trends.
+Moreover we are already observing the beginnings of ecological collapse as plant and animal life is unable to adapt quickly enough to changes that are happening. Hundreds of species you have never heard of are already extinct entirely due to the climate changing.
+Cry all you want, but those are the facts. Climate change is happening, it will not be a good thing and there is NO natural explanation. | ​@GeoRyukaiser  what studies? What data? I can just as easily say all the data points to (insert my political point here), all of the studies agree. The trends all show that I am correct
+ I do this without pointing to anything. See how that works? Have you read a study yourself? Understand the test methods used? Sample sizes? Reviewed the data yourself? Of course not. You were told something in school and believe it because you get to feel smarter than others | @slipperysteve8  Every study from every reputable source. At the ones I've read. And yes, I've read them. I'm skeptical in that I don't blindly believe, so I check every claim made, by both sides. And it's the denial side that comes up short every single time. | @damieno3470  No, colleges where not seriously teaching Al Gore's stuff in 80s/90s or whenever. Maybe at entry level, first year, first semester, when students where still not ready to go indepth with data, but courses after that would have been with the data itself. Even then, while Gore did exagerate things, he wasn't entirely baseless. Acid rain is a thing and does happen in places with high enough polution (beijing for example). The reason America didn't really suffer from it was because of changes to environmental practices.
+As for the claims about the equator, coffee and caps melting. I've never seen Gore's claims and never intend to. All I can say is the papers did make those predictions, though the time frame was over a hundred or so years and that current trends are within predicted parameters.
+Also in the 70s they didn't teach that. The coming ice age was a minority opinion within the scientific community at the time which, while backed by historical data, largely ignored atmospheric data of the time. The majority of papers on the climate in the 70s all agreed that warming was coming in the 80s. The TIME article was based on those minority opinions and is full of uncredited quotes and media spin. I've seen it, it reads like a modern article about republicans from the MSM.
+No one in the scientifically literate side of the community wants to eliminate CO2 entirely, only the amount produced by human industry. Why? Because the natural processes that eliminate natural sources of CO2 (including human breath) aren't able to process all the extra we are producing. And too much CO2 is also bad, as of 2010-2012 plants already hit peak greening from extra CO2 and have since started to suffer negative effects and browning from there being more CO2 then they can process. | @damieno3470  What's even worse, they put this crap in the youth who have minds full of mush that is formed into lunacy. | @GeoRyukaiser  no one understands truly understands it, that is why perdition after perdition falls. | kun gf lu d eaths would also be an acceptable answer. | lol that's a funny one haha | Alex: Sorry, the adjudicator says you're wrong! Your answer was technically right but 'coronavirus' is more right, so you lose points. | Alex is dead? RIP Mr Trebek we love and  miss you except for this guy He doesn't respect you AT ALL! | @amiehulscher7156  just because you dont understand a joke doesnt mean it isnt funny. | @amiehulscher7156  lighten up Francis | Just because you don't understand something doesn't make it a hoax. | @GeoRyukaiser   just because you hoax something doesn't make it a fact either. | @GeoRyukaiser  Bwahaha..... | @GeoRyukaiser  if the energy industry was nationalised (gov ceasing the means of production) global warming would never be brought up again. As if that was the goal the whole time. | @guillermoelnino  No, it would still be brought up. Why? Because the fossil fuels would still be releasing more CO2 then the natural CO2 flow can process. Which means it would continue to concentrate and cause problems.
+Personally I have no idea why the energy industry is dragging its feet since smaller companies are raking in profits from non-fossil fuel energy production. | @GeoRyukaiser  so, is it ok for an unelected panel of people (like the ones here) that help create laws and enforce compliance to said laws, that affects everyone but they haven't a single clue what they are talking about nor a shred of evidence or data to support their ideas? Is it ok for them to force changes simply based upon imagination and mindless guessing? 
+If a financial guru or company of gurus were to take people's money and promise positive results but offered only imaginary unsubstantiated information on the processes, then they, through the pulling of yours and other people's resources made them self or selves very rich and left you poorer than before with no positive results as they move on to do the same to others.....wouldn't that person or group of people be considered fraudsters??? 
+They disseminate fraudulent information, use unwarranted fear tactics to take people's money and force major changes, than as they reap the rewards as you are left with the mess and the bills! Sound like a fair deal? | ​ @damieno3470  Being underprepared and being caught off guard by an older man asking something a high schooler or first year physics student should know does not invalidate any of the research. Given how little these people know I doubt any of them are researchers in the field, or done those early classes, thus I consider their opinions irrelevant in regards to the facts.
+And the facts remain that every single claim that anthropogenic climate change isn't happening fails immediately upon exposure to the data. It is happening and at rates not seen since massive catastrophic events like the time of Siberian Flood-Basalt event... when all of Siberia was covered in lava by the eruption of a super volcano. No such natural event has happened to cause the levels of CO2 and temperature rise in the time frame observed to explain away present trends.
+Moreover we are already observing the beginnings of ecological collapse as plant and animal life is unable to adapt quickly enough to changes that are happening. Hundreds of species you have never heard of are already extinct entirely due to the climate changing.
+Cry all you want, but those are the facts. Climate change is happening, it will not be a good thing and there is NO natural explanation. | ​@GeoRyukaiser  what studies? What data? I can just as easily say all the data points to (insert my political point here), all of the studies agree. The trends all show that I am correct
+ I do this without pointing to anything. See how that works? Have you read a study yourself? Understand the test methods used? Sample sizes? Reviewed the data yourself? Of course not. You were told something in school and believe it because you get to feel smarter than others | @slipperysteve8  Every study from every reputable source. At the ones I've read. And yes, I've read them. I'm skeptical in that I don't blindly believe, so I check every claim made, by both sides. And it's the denial side that comes up short every single time. | @damieno3470  No, colleges where not seriously teaching Al Gore's stuff in 80s/90s or whenever. Maybe at entry level, first year, first semester, when students where still not ready to go indepth with data, but courses after that would have been with the data itself. Even then, while Gore did exagerate things, he wasn't entirely baseless. Acid rain is a thing and does happen in places with high enough polution (beijing for example). The reason America didn't really suffer from it was because of changes to environmental practices.
+As for the claims about the equator, coffee and caps melting. I've never seen Gore's claims and never intend to. All I can say is the papers did make those predictions, though the time frame was over a hundred or so years and that current trends are within predicted parameters.
+Also in the 70s they didn't teach that. The coming ice age was a minority opinion within the scientific community at the time which, while backed by historical data, largely ignored atmospheric data of the time. The majority of papers on the climate in the 70s all agreed that warming was coming in the 80s. The TIME article was based on those minority opinions and is full of uncredited quotes and media spin. I've seen it, it reads like a modern article about republicans from the MSM.
+No one in the scientifically literate side of the community wants to eliminate CO2 entirely, only the amount produced by human industry. Why? Because the natural processes that eliminate natural sources of CO2 (including human breath) aren't able to process all the extra we are producing. And too much CO2 is also bad, as of 2010-2012 plants already hit peak greening from extra CO2 and have since started to suffer negative effects and browning from there being more CO2 then they can process. | @damieno3470  What's even worse, they put this crap in the youth who have minds full of mush that is formed into lunacy. | @GeoRyukaiser  no one understands truly understands it, that is why perdition after perdition falls.</v>
       </c>
     </row>
     <row r="55" xml:space="preserve">
@@ -1411,15 +1439,8 @@
       <c r="D55">
         <v>308</v>
       </c>
-      <c r="E55" t="str" xml:space="preserve">
-        <v xml:space="preserve">Didn't they try to scare you with acid rain as well, the rest of that list sounds so familiar... | ​ @unpaintedleadsyndrome  Acid rains were real. I guess you don't remember the L.A. smog problem from the 90s? 
-It was bad. Really bad. | @unpaintedleadsyndrome  Yes, and an incoming ice age. | ​ @michaellunney968  we're still coming out of the last ice age. Earth time is not like human time. It's literally glacial time. | I'm still waiting for the flying cars we were promised in the year 2000!!! | Steve, here in Australia back around 2010 we were told be a guy named Tim Flannery that if we didn’t tackle climate change our major dams would never be full again, children wouldn’t know what snow looks like and it would NEVER rain in the Australian outback. Well, well most major dams are full and Australia has had floods, the outback is lush and green, last winter the southern alps had record snowfall and it also snowed in the middle of summer in Tasmania. Also there have hardly been any major cyclones make landfall in tropical Australia but there has been flooding. | @dimitriosfreedom9282  I think we will have to accept a few oddities within the climate, we need to make the scientific breakthroughs to help us environmentally but our priority has to be human beings, all this  scaremongering and lies isn't helping anyone. | The Ozone one was actually true. But the thing is, all they had to do was eliminate highly toxic chemicals you wouldn't really want to use anyway and the ozone fixed itself. 
-Lighting "creates" ozone. | Tiger population has increased | That may have been somewhat true at the time, but technology has grown faster than those timeframes and we constantly find new ways and sources to obtain oil and gas.  It's happened many times in the past and will probably keep happening in the future.  (just my opinion) | ​ @ripvanrevs  no your wrong  they know where the oil was it was just too costly to extract vs the gaz price with the rapidly increasing gaz price these oil reserve becomes profitable to extract simple as that and we got better equipment so its even cheaper that it was beforehand | In 1978 I was in Lion's Club debate on energy when I was in high school. My claim was that oil was abundant and we had enough to last at least 100 years (this was based on actual scientific investigation of things like the Saudi oils fields). My opponent stressed how we must drastically reduce usage and wear sweaters and always cover our pots so heat wasn't wasted. Needless to say, my opponent was declared the winner. | Exactly right They would state that the club of rome which is supposed to be the greatest minds  of the world that we would run out of all fossil fuels years ago So much for great minds | Well… that’s because then, like now, people listened to the “news” in stead of listening to those actually doing the research. | All buildings would be eroded away by the acid rain, and we'd all die because the loss of the OZON layer | Since the times when you were a child additional fuel sources have been found. Consider the vast increase in the number of hydro-electric and nuclear facilities producing energy.  Vehicles have become more energy efficient and technologies such as solar and wind have become viable replacements, and have even overtaken the use of fossil fuels in some countries (such as Scotland).   Many sources of fossil fuels that were not viable 50 years ago can now be harvested such as shale and fracking, and due to the increasing value of fossil fuels known reservoirs of oil that would not have been used 50 years ago can now be utilised - thus the 50 year limit has extended.
-Tigers and Elephants remain on the brink of extinction with 3 tiger sub species having gone extinct since the 1970s, The Javan Tiger, The Caspian Tiger and the Bali Tiger - the South China Tiger is functionally extinct in the wild.  African forest elephants are critically endangered but conservation efforts have managed to stabilise other elephant species.
-Sea levels have risen - and while London remains above water (with very expensive upgrades to the Thames barrier), perhaps you could ask the people of Kiribati their opinion on this.
-Now, considering your stance of not doing anything, the prediction of complete destruction of the ozone layer within 100 years WOULD have been correct, however governments decided that rather than allowing us to cause significant damage to ourselves and our planet, that we should get together and do something.
-During the 1990s International agreements, including the signing of the Montreal Protocol, banned the sale of CFCs (in 1994), the main culprit in the destruction of the ozone layer.  The successful implementation of this means that it's predicted that the ozone layer will repair itself by 2060.  
-Just goes to show that by working together to do something we can mitigate "natural disasters" that we humans are bringing upon ourselves. | and 'medication'. | Actually we use much less oil and gas back then. Also the ozone was definitely true to some degree. | @uberboat4512  and lead in gasoline.</v>
+      <c r="E55" t="str">
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -1436,7 +1457,7 @@
         <v>344</v>
       </c>
       <c r="E56" t="str">
-        <v>What happens if you have some insulation, and you mix in an other kind of insulation?  Will it isulate more or less?  That depends on whether, the added type is a better or worse insulator (If we don't look into what mixing them might do chemically, as we - I - never have heard anyone talk about that) or just happens to have the same effect. It's not like we go from 100 % atmosefere to more than 100% (not like putting an extra blanket on top of the currect one) so before someone proves, and tells us about, what the numbers are, and what they result in, I'll go with the historical data, that says, Co2 LAGS temperature  NOT the other way around.. | ​ @CONEHEADDK  geologically it depends. In this case co2 leads. | If you asked the Three Stooges about climate change, Moe would get angry, Larry would say, "okay let's climb it so we can change it" and Curly would breath into his hand to measure it, then get slapped by Moe.  And all of their answers would be more accurate than these guys. | You got the names of the three stooges intellect wrong its: Biden, Harris and Newsom | @DrDoom-uu3cj   ;    Well done , Ha ! | John, great comment. So accurate. | Nah, Moe Larry and Curly could ad-lib.  The panelists just know how to lib. | Moe, Larry, cheese.</v>
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -1453,7 +1474,7 @@
         <v>6</v>
       </c>
       <c r="E57" t="str">
-        <v>4 parts per 10,000. It's a percent. | It’s been a very warm winter. Canada and the u.s. has barely gotten snow, the Great Lakes didn’t freeze. Yup not much has changed</v>
+        <v/>
       </c>
     </row>
     <row r="58">
@@ -1470,7 +1491,7 @@
         <v>344</v>
       </c>
       <c r="E58" t="str">
-        <v/>
+        <v>yup! Follow the cash. I remember Obama saying, "No one should own more than one house". He owns four the last I heard. All beach front mansions. This is after he was president. that should tell you all you need to know about most politicians. They go in pour, and come out rich. so the question is, where is the money coming from and why do you love it, more than your own people (country)? | @akmurf7429  president gets a good salary. | He will never ask that because most of his campaign donations come from the oil industry. | Always follow the money | Yes. Good point! | 97% of scientists discover what they are paid to discover! | @wheelsofafrica  Its not science but consensus driven by misunderstanding radiation in a similar way as gender confusion. | He forgot to mention that if the CO2 were at 5% we'd all be dead, 4% is fatal levels. | @Ron-d2s  Submarines are OK with 4000 parts per million however so we can look forward to a greener planet.   One day the Earth will probably die as a result of insufficient CO2 for photo synthesis. | @BrinJay-s4v  nonsense</v>
       </c>
     </row>
     <row r="59" xml:space="preserve">
@@ -1487,9 +1508,9 @@
         <v>266</v>
       </c>
       <c r="E59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Moving? We are well past that stage. | Watch the movie " Idiocracy " they must have been part of the cast. | We’re already in idiocracy. Sadly. | Can you explain to me the significance of being able to come up with this number?  Can you tell me what percentage of radon in the air is considered hazardous by the EPA? | ​ @stargazer7644 If you're an expert in any area, you should understand how ridiculous it sounds for someone who doesn't know the basics of a certain topic to make decisions in that field. Sure, they may understand it to a certain degree without being experts, but why shouldn't I be afraid of them making shortsighted or superficial decisions? | ​ @qsmlj You talk about them not being experts.  These people are legislators.  They make laws.  Most of them are lawyers.  That makes them experts at law.  They rely on the counsel of experts in other fields to advise them about what laws need to be made.  They rely on climate scientists to tell them that global warming is a problem and to make suggestions on what we can do about it.  It isn't like the politicians came up with that.  They're responding to it.  Your objections really don't make any sense.  You don't seem to understand how laws are made. | @stargazer7644 The history of science is the history of questioning. When you are making sweeping changes, asking people to make sacrifices, make sure you understand why it should be done. The problem with today is the roles of scientists and priests have changed. It is evident that we need to question the “science” because scientists are putting out a lot of garbage.
-The worst part is questioning these garbage is ridiculed, and anyone questioning them is tagged as “denier”.
-If we do not ask questions, we would still think the sun makes round the Earth, not the other way round. | @stargazer7644  In general - they are cultists, who BELIEVE into something, because somebody told them. | @stargazer7644  The significance is these people claim to be experts. Yet they do not understand something as basic as that number. As for radon that's more EPA.  Out doors normal background. Is roughly   .4 pCi/L.  Once that gets between 1 and 2 it's a concern.  4 is the EPA action level.  How do I know thus?  I Looked it up.  The same as these so  called experts should have. | @stargazer7644  the significance is children learn that at school. If they were unable to learn something specific for their job from school they aren’t even incompetent, they are just ignorant.</v>
+        <v xml:space="preserve">Moving? We are well past that stage. | Watch the movie " Idiocracy " they must have been part of the cast. | We’re already in idiocracy. Sadly. | Can you explain to me the significance of being able to come up with this number?  Can you tell me what percentage of radon in the air is considered hazardous by the EPA? | ​ @stargazer7644 If you're an expert in any area, you should understand how ridiculous it sounds for someone who doesn't know the basics of a certain topic to make decisions in that field. Sure, they may understand it to a certain degree without being experts, but why shouldn't I be afraid of them making shortsighted or superficial decisions? | @stargazer7644  The significance is these people claim to be experts. Yet they do not understand something as basic as that number. As for radon that's more EPA.  Out doors normal background. Is roughly   .4 pCi/L.  Once that gets between 1 and 2 it's a concern.  4 is the EPA action level.  How do I know thus?  I Looked it up.  The same as these so  called experts should have. | @stargazer7644  the significance is children learn that at school. If they were unable to learn something specific for their job from school they aren’t even incompetent, they are just ignorant. | @yoshiko-kawashima  Can you tell me avogadro's constant off the top of your head please?  How about the number of electrons in a coulomb?  The gravitational constant?  If you ever had chemistry or physics in high school or college you were undoubtably taught these basics at one time.  If you don't know these numbers, can I claim that you don't understand a thing about how gasoline works in your car or how the light switch functions in your house?  Unless you're a chemist, physicist or engineer now, I wouldn't expect you to know the values offhand. These people are politicians and lawmakers, not scientists.   The knowledge of a particular number that is of significance to climate scientists doesn't mean they don't understand the implications of climate change.  Oh and while I did happen to know the answer to the question was 400 parts per million, I wouldn't have been taught this in school as a child because it wasn't 400 parts per million then, nor was climate change something that was on anybody's radar. | @stargazer7644  since they tell everyone else which way to live I do expect them to know the values offhand. And if I tell you what to do, you should expect me to know the values offhand. Period | The people elected them into that position.  If you don't like the job they're doing, maybe you should run for office.  If you took even half of that self righteous energy and put it into actually learning something, you'd be much better off. | @yoshiko-kawashima   - you  know what? Scientist who know numbers nobody knows, have the right to tell other what to do, because they committed their life to find out that stuff. 
+While the everyday normal guy just doesn't care, he might accidentally destroy the earth and all living things on it!
+The scientist know the exact numbers and the dangers. Politicians have to act according to it!</v>
       </c>
     </row>
     <row r="60">
@@ -1506,7 +1527,7 @@
         <v>121</v>
       </c>
       <c r="E60" t="str">
-        <v>Because of lack of volcanic activity for the last 100 years and the fact that we do not allow the forests to burn,  we do not have enough CO2 in the atmosphere.</v>
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -1540,7 +1561,7 @@
         <v>391</v>
       </c>
       <c r="E62" t="str">
-        <v>Priceless! | I would like to buy that bumper sticker as well. | they gonna arest him . | He insults the stupid. | Way this planet is going they will be able to cover the vehicle completely in stickers | @M1cko33   still not as bad as your “ I’m with her” bumper sticker. | Spot on. I want one! | @M1cko33  Like Charles Darwin? | Is that why you had children together? | I need a bumper sticker like that</v>
+        <v/>
       </c>
     </row>
     <row r="63" xml:space="preserve">
@@ -1557,20 +1578,9 @@
         <v>207</v>
       </c>
       <c r="E63" t="str" xml:space="preserve">
-        <v xml:space="preserve">Not ignorant, liars. | And they never address how much volcanoes emit carbon monoxide! | I was confused about this too, like it makes sense that transportation people wouldn't know co2 concentration cause they just would never be dealing with that, but it seemed crazy that she somehow got that statistic wrong, but I looked it up and I guess she was just talking about California specifically lol | @jojo-beans  her number is so far off, it’s dystopian | Greenhouse gas emissions are not the same as Carbon emissions. Transport has had considerable efforts put into reducing greenhouse gasses. | @damos3000  so co2 isn’t a greenhouse gas? | @MarkNOTW  Indeed it is - but it is not the only one, which is the root of the error made in the original comment (and one it seems you also make). Vehicles are very good at producing mostly just CO2 - other industries not so much (ie farming: methane). | @damos3000  I don’t know whether to agree with you or disagree with you. I personally don’t think that CO2 has a net warming affect on our environment after researching the topic. What’s the chemical consistency of a vehicle‘s tail pipe gases? | @MarkNOTW  Modern engines, non-hybrid/electric produce CO2 (carbon dioxide), CO (carbon monoxide), H (hydrogen), O2 (ozone), and H20 (water vapor). Do not know the % off the top of my head though. I may also have missed one or two other gasses. | @phantomJK  ok thanks. I’ve always thought carbon monoxide was the primary gas produced. | every time a policy maker says something this flamingly ignorant, both science and sensible policy die a little. | I’m fairly certain if memory serves correct that 97% of the atmospheric CO2 comes from natural sources | @MarkNOTW about right. About 96% (190 billion tonnes) is naturally derived, 4% is human induced (9billion tonnes) (CSIRO). Not sure if that’s just from fossil fuels or every anthropogenic activity e.g farming and cattle, which is mostly absorbed each growing season and is also renewable I.e. it’s all based on grass growing each year, fixing CO2. | @MarkNOTW  "I’m fairly certain if memory serves correct that 97% of the atmospheric CO2 comes from natural sources" That's false, but it comes from a common misinterpretation of one data point. On the one hand, our collective annual CO2 emissions ARE only about 3-4% the size of the total annual fast carbon cycle.
+        <v xml:space="preserve">Not ignorant, liars. | And they never address how much volcanoes emit carbon monoxide! | I was confused about this too, like it makes sense that transportation people wouldn't know co2 concentration cause they just would never be dealing with that, but it seemed crazy that she somehow got that statistic wrong, but I looked it up and I guess she was just talking about California specifically lol | @jojo-beans  her number is so far off, it’s dystopian | Greenhouse gas emissions are not the same as Carbon emissions. Transport has had considerable efforts put into reducing greenhouse gasses. | @damos3000  so co2 isn’t a greenhouse gas? | every time a policy maker says something this flamingly ignorant, both science and sensible policy die a little. | I’m fairly certain if memory serves correct that 97% of the atmospheric CO2 comes from natural sources | @MarkNOTW about right. About 96% (190 billion tonnes) is naturally derived, 4% is human induced (9billion tonnes) (CSIRO). Not sure if that’s just from fossil fuels or every anthropogenic activity e.g farming and cattle, which is mostly absorbed each growing season and is also renewable I.e. it’s all based on grass growing each year, fixing CO2. | @MarkNOTW  "I’m fairly certain if memory serves correct that 97% of the atmospheric CO2 comes from natural sources" That's false, but it comes from a common misinterpretation of one data point. On the one hand, our collective annual CO2 emissions ARE only about 3-4% the size of the total annual fast carbon cycle.
 However, what's important to realize is that the land, waters, and sky both give off and ABSORB CO2/carbon, and that natural "trading system" was perfectly balanced before we started burning fossil fuels in earnest. Thus, CO2 levels were quite stable, but all of our emissions are excess emissions that drive global CO2 levels upward. Thus, since 1776, humans have raised global CO2 levels by over 54%, or to express it differently, 34% of the CO2 now in the air is up there because of our emissions. 
-Be well. | @MarkNOTW  Not sure if it was 97%, but was most certainly close to that. Anyhow, when you bring it up with people who are a bit more knowledgeable, they are claiming that that little bit of difference is going to make a huge difference in temperature and tell you to look at the science. But the science doesn't prove anything about their claim. There's a relation between rising temperature and extreme levels of CO2... but the human contribution to CO2 isn't quite so extreme it's going to make a huge difference. Not long term, not short term. Temperature is rising, sure. But if current CO2 levels have any effect on it, it's still marginal at best... and that's including human contribution. The planet was never a perfect balance and we shouldn't be concerned about maintaining a perfect balance either. Just some kind of balance. Nice if we can save some creatues and plants from dying out, but if the planet wants them dead it's gonna kill them with or without us. | @thenonexistinghero  totally agree with you. After researching it for many years it seems like co2 lags temp not the other way around. And what do alarmists do with the previous warm periods prior to fossil fuels? | @MarkNOTW  Before the industrial revolution CO2 did indeed lag behind temperature, that is because an increase in temperature lead to a reduction in ocean capacity to contain dissolved gas, therefore they release some CO2 into the atmosphere when other factor influence temperature, one of them are the Milankovitch cycle. Those cycle also beign the main source of temperature variation in the last tens thousand years before the industrial revolution, glaciation period and warm period. And before yo go blaming them for current increased we should technically be cooling down right now according to those.
-But as is very proven physics, CO2 prevent part of earth cooling by radiation, leading to a positive feedback loop, intinal cooling leads to less CO2 that leads to even more cooling, or initial warming lead to more CO2 leading to more warming, until earth stabilize at a temperature high/low enough to radiate enough energy to match incoming energy absorbed from the sun even with it's effective radition increased or decrease by the new CO2 level.
-This positive feedback loop is also present in man-made increase in CO2, CO2 goes up leading to temperature increase then leading to more natural CO2 to be released. | @M4niacks2  I’m going to deny your assertions as well. The atmosphere doesn’t know where the co2 is coming from, so to say that co2 lagged temp but only until the Industrial Revolution is special pleading at best. Fact is co2 has a net neutral impact on temperature as it blocks as much incoming solar radiation as it traps. That’s according to physicists not me. | ​ @MarkNOTW  Pollution is a bigger issue than temperature fluctuations. Fossil fuels are not as clean as solar or even nuclear. Natural gas fuel cell generators are 4x (400%) more efficient than combustible coal-fired generators. Coal is (30% conversion), NG combustion is (60% conversion), NG fuel cell is (120% conversion compared to coal). The example of natural gas fuel cells proves that combustion is not efficient. Everyone knows that combustion is highly inefficient. A fair argument is to compare energy output with pollution produced. 
-As well, the oceans and coral reefs are experiencing acidification independently of temperature increases. The collapse of coral reefs, from acidification and rising temperatures, does have the potential to limit human life on our planet. What proportion of human-caused climate change contributes to the total amount of climate change is irrelevant within the context of pollution. 
-The argument keeps shifting from temperature back to pollution when suitable. This is a strawman tactic.
-As well, we can measure the proportion of human-caused climate change by studying the ratio of carbon 12 to carbon 13 within tree rings before and after the industrial revolution, and then comparing this ratio with the current atmospheric carbon 12 and carbon 13 ratio. Fossil fuels are made from prehistoric plants. And plants prefer carbon 12 to carbon 13. We actually can estimate the proportion of human-caused climate change by comparing the difference in ratios before the industrial revolution and after the industrial revolution. 
-Furthermore, the earth is supposed to be in a cooling phase right now as the earth's axis becomes more perpendicular relative to its orbit around the sun, yet we aren't getting cooler we are getting hotter, so the idea that we are getting hotter because of natural solar effects is false. The sun is also in a cooling phase (grand minimum). Even NASA knows that humans are responsible for climate change. Scientists aren't elitists and globalists. The global elite are the oil tycoons. You have it backward! It's why the US is built for automobiles and not humans. LA used to have more metros and not so many roads, which was more efficient than individual automobiles. 
-Even the Grey aliens are telling humans that we are polluting our environment. Even God said that we shall multiply and REPLENISH the earth. Anyone who denies human-caused climate change and pollution is willfully ignorant. | @ADUAquascaping  I’m pretty much going to deny everything you stated outside the first paragraph perhaps. If we have ways to produce less pollution, I’m all for it…and we have…and we are. 
-As far as ocean acidification, Oceans can never acidify according to Woods Hole Oceanography. Too many alkaline sources. Recent studies have shown that coral reefs are doing fine and that marine life thrives just fine in varying degrees of pH. 
-Sea ice extent is stable for the past 40ish years and sea levels haven’t risen for over 100 years based on photographic evidence. 
-If humans and co2 are causing climate change since the Industrial Revolution, then we should see a direct correlation between co2 rise and temperature rise. We don’t. The warmest decade on record was the 1930’s according to numerous peer reviewed studies. The 1970’s, we were warned of a potential ice age. Furthermore, we know of several eras of global warming during which there were no fossil fuels. Furthermore, if co2 traps heat to the degree alarmists claim, we would be in a never ending warming cycle as the vast majority of co2 comes from warmer oceans. 
-So, I can assure you that many of us “deniers” are not ignorant.</v>
+Be well. | @HealingLifeKwikly  let’s say you’re right, which I seriously doubt, so what? To put it bluntly… | " The women claims.." just leave everything alone for long enough and she'll be proved right, they always are. | And on op of it, it is a minor part of the overall CO2 concentration. | The only CO2 my bike transportation emits is when my tires leak a little. But that CO2 was pumped into my tires to begin with, so no net gain. | And no doubt a lot less in other nations less addicted to big cars. | But she certainly sounded confident in her stupidity, so there's that.</v>
       </c>
     </row>
     <row r="64" xml:space="preserve">
@@ -1663,13 +1673,11 @@
       <c r="D67">
         <v>460</v>
       </c>
-      <c r="E67" t="str" xml:space="preserve">
-        <v xml:space="preserve">Very well stated. All life on this planet is definitely under threat, but NOT from the climate! | @lilyflower4962  The planet is not in danger,....We are.! | ​ @s.muller8688  Our kids are in the most danger with how fast and far the Overton window has been pushed towards condoning pxdophilia in this country, especially in our schools...er... more like indoctrination camps. | @JerdMcLean  There's never been a merge of Nazism and Marxism before until today's Democrat Party. The neo-Nazis and neo-Maoists that are concentrated within the party found out how to hold the entire left-wing philosophies together and then deflect the worst tenets onto the other side. Essentially it's a marriage of the whole family of fascism. Socialists and progressives are no longer distinguishable, they're the one and the same now | @s.muller8688  No.  We are not. I hate to disappoint you. | ​ @FuckDemocrats.  Goodonya SoL. The difference between Soviet socialism and Nazi fascism? The flag. | What a well written explanation.  Thanks.  I learned quite a bit from your comment. | @TheErik249 - consider clouds which are water vapor created by evaporation, thus essentially pure water, which absorbs CO2 out of the air and creates alkalinity.   Alkalinity is captured Carbon from the atmosphere.  I would contend fluctuations in surface water alkalinity has a lot to do with atmospheric CO2 levels.  I figure as long as it continues to rain, we would be hard pressed to see run away atmospheric co2. Especially since a hotter surface creates more evaporation, thus more clouds and rain. Direct air scrubber for carbon capture are essentially man made clouds on the ground, factor in inefficiencies and they have a net positive carbon footprint!  Let nature do it’s job. | @1922DPenny  Please send that to AOC and Gore since they do not comprehend the science.  
- When they go after my steak I get pissed | @1922DPenny  You have that backward.  Dissolved CO2 is carbonic acid; not a base.  Also, the neuter possessive pronoun is "its," not "it's."  You're welcome. | Somewhere in my reading a half  a billion years ago the earth had something like 5000 ppm CO2 and that was one of the most active periods for plant, and animal reproduction in earths history. 
-Most of the CO2 has been locked in  limestone and to a minor extent fossil fuels. It’s unlikely CO2 is coming back anytime soon which is unfortunate in my view because one study I saw by NASA the earth is 15% greener in the last 20 years what else happened during those 15 years? | @geraldcroft9020  its actually kind of frightening when u look at just the past 150 million years and u see the earth trending towards becoming a frozen planet just like mars. Half of the entire atmosphere is gone | every one forgets all the farms and forests need co2 to grow. i like food i want more food to grow and it needs co2 to bigger. | Al Gore shouted that George Bush played on our fears, then he decided that was what he wanted to do. | @bingo7799  Another plagiarist like our 'Resident' in the WH !!</v>
-      </c>
-    </row>
-    <row r="68" xml:space="preserve">
+      <c r="E67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
       <c r="A68" t="str">
         <v>@Laserfish17</v>
       </c>
@@ -1682,11 +1690,8 @@
       <c r="D68">
         <v>239</v>
       </c>
-      <c r="E68" t="str" xml:space="preserve">
-        <v xml:space="preserve">Luckily, they don't produce C02 emissions, generators run on unicorn farts! | @stapleman007   ;   You see , I did not know that , think of what you could accomplish without a Democrat ? | Thank you yes Generators # | Hey maybe set up wind turbines there? Remote area, open field, sounds like a good spot. | ​ @HoChiHoChiPlays  We have plenty of those, they don't produce 1/10 of what nuclear plants could produce on less than half the land used for turbines. | @HoChiHoChiPlays | That humor is lost on people who think it's better for the climate to import oil from other countries than to drill and use our own. | @harrylazard805  I think it's best to leave the oil in the ground and move to something that's not going pollute the environment more. | Looking forward to a country clinging on to their rusty generators while country's overtake you in renewable energy. 
-Does anyone think he perhaps has incentive not leave the gas industry for an industry that'll pay him nothing back.
- Its okay carry on getting screwed by opec and stay reliant on imported gas.
-The problem is petrol heads havnt got 2 cells to run together so asking pointless questions that have no relatability is a waste of time and proves nothing. | @jordanbryan555  The US can produce it's own oil &amp; gas, especially when there's not a democrat in office. We could be completely energy independent if energy companies were allowed to drill like they were under Trump. | @jeremiahwasabearfrog9956  but the use of oil and gas long term going to work? Why not work towards renewable energy like the rest of the developed world so you wouldn't be at the drawing board. Its just leaving a problem for the future generations to fix</v>
+      <c r="E68" t="str">
+        <v/>
       </c>
     </row>
     <row r="69">
@@ -1723,7 +1728,9 @@
         <v xml:space="preserve">If you support a course of action that is going to effect millions of people's standard of living, and will cost hundreds of thousands of jobs, you should know the actual percentage of CO2 there is in the atmosphere. | @larryclemens1850  I don't. I'm trying to work this out critically, using an organ I assume that you're using. Am I supposed to just regurgitate what you want me to accept? | @larryclemens1850  strange how no one ever points that out. Almost like we're already living in the movie idiocracy. People are just so brainwashed it's unbelievable. | @larryclemens1850  why?
 Why is the proportion relevant?
 Why does nobody talk about the actual amounts, i.e. 915,000,000,000,000 metric tones at present, up from 600,000,000,000,000 not so long ago? | The best lawyers, reporters, detectives, etc., ask questions they already know the answer too. | @ElonMuckX  That doesn't sound intelligent to me. Intelligent people are often curious and half doubtful of things they have good reason to be certain about. Models can change, or the context holding up the fact can end up negating it validity. | @larryclemens1850  sorry - you've completely lost me. 'Tanks?' | @MrYahboo   Sorry. My bad. Thought it was another thread I was commenting on. I will delete it. | @MrYahboo   Percentage of the atmosphere is what  the "absolute" values to which you refer are calculated from.  I put absolute in quotation marks bc of photosynthesis and dissolution, the amount  of CO2 in the atmosphere is going to vary. 
-But more to the point, I would argue that percentage of conposition is a better way of looking at it since sunlight is a distributed influence. If sunlight was only concentrated on one part of the planet, and that one part wàs where all the CO2 was concentrated, then it may be useful to  talk about the absolute value. Since this is not the case, I think it is clearer to frame things in terms of relative percentages. | He didn't prove anything. Those people were not climate specialists. They were witnesses representing road infrastructure companies. LaMalfa pointed out that CO2 is only a small fraction of the atmosphere. That's correct. But what he doesn't tell you is that even that small fraction is essential. Breaking that fragile balance in the atmosphere is having severe consequences. Sometimes small fractions matter: the connector connecting you steering wheel to your vehicle is only a small fraction of the car, but you won't go anywhere without it.</v>
+But more to the point, I would argue that percentage of conposition is a better way of looking at it since sunlight is a distributed influence. If sunlight was only concentrated on one part of the planet, and that one part wàs where all the CO2 was concentrated, then it may be useful to  talk about the absolute value. Since this is not the case, I think it is clearer to frame things in terms of relative percentages. | @larryclemens1850  ok, fine, but that still doesn't explain WHY it is important for laypeople to know this particular figure when they are aware that over 99% of climate scientists consider the figure, whatever it may be, to be significant. For me, knowing the % of C02 in the atmosphere is of no more importance when trying to understand what's going on than knowing the exact date of the outbreak of WWII would be to understanding its causes.
+I suspect that climate-deniers love to bring this particular number up because they ignorantly assume that anything under 1% is insignificant, regardless of the subject or context. This is, of course, false and what is truly important is the fact that CO2 levels have increased by 50% since the Industrial Revolution.
+If you are going to argue that this has not directly caused the warming that's happening, or perhaps that warming isn't even happening, then you'll need to start producing some data to support that position. | He didn't prove anything. Those people were not climate specialists. They were witnesses representing road infrastructure companies. LaMalfa pointed out that CO2 is only a small fraction of the atmosphere. That's correct. But what he doesn't tell you is that even that small fraction is essential. Breaking that fragile balance in the atmosphere is having severe consequences. Sometimes small fractions matter: the connector connecting you steering wheel to your vehicle is only a small fraction of the car, but you won't go anywhere without it. | I don't think he did. Feel free to persuade me otherwise by explaining what this 'perfect case' was. | ​ @MrYahboo  more carbon means a far greener planet. Always has throughout the history of earth. You know what that means? Runaway heating is impossible because at some point the plants and ocean protozoa level out the co2. That's just 1 point here.</v>
       </c>
     </row>
     <row r="71" xml:space="preserve">
@@ -1746,7 +1753,7 @@
 Numbers do not lie only the people using them. How Larry and Doug interpret those numbers is just magical thinking given the current climate models ... how we should adapt to the situation is still up to question 
 So Larry get off your high horse and get the climate models working so we may understand what to do before we make another mistake 
 Larry, I see no CO2-free solution everything is a tradeoff, and is CO2 free really a solution | Yes it appears so, but about 80 of the population are followers **even with critical thinking skills *** Start with  some of the Milgram experiment to start to see my point | So what does this say about the voters? | No. Anti-critical though. "Common sense" is a thought terminating tactic used by people who can't substantiate their claims. | His argument was that a number seems small so therefore it cannot have the effects on the environment that were predicted. That's not critical thinking.
-And it's especially stupid when we can see those predicted effects happening all around us. | @NomadSoul76  I am not a climate skeptic * The climate models have problems *  your claim you can see the predicted effects I am very skeptical * you can not adapt to something you  do not understand *</v>
+And it's especially stupid when we can see those predicted effects happening all around us. | @NomadSoul76  I am not a climate skeptic * The climate models have problems *  your claim you can see the predicted effects I am very skeptical * you can not adapt to something you  do not understand * | LaMalfa and critical thinking?   Please don't joke about it.</v>
       </c>
     </row>
     <row r="72">
@@ -1766,7 +1773,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" xml:space="preserve">
+    <row r="73">
       <c r="A73" t="str">
         <v>@mudwater9140</v>
       </c>
@@ -1779,11 +1786,8 @@
       <c r="D73">
         <v>427</v>
       </c>
-      <c r="E73" t="str" xml:space="preserve">
-        <v xml:space="preserve">They care more about themselves and money than the truth. | Becuase it's not thier money being spent. It's OUR money they're spending. | @newyorkfan16  Just give a wife a credit card. You will figure it out.
- You will go broke saving money on all those great discounts. | having a difficult time understanding that... | That is government in all times and all places 4 U | Hoax 
-We are fools | Most likely they all knew about it and even maybe had a deal at bar table or at a golf course ! 
-They just act like they don’t know… | Great exemple my friend! When it’s not their money they don’t really care. But it comes to their interest that’s another story. | It's all about the photo op and the next election campaign. | They do as they please and they know they are not being held accountable. That's why they are so reckless with taxpayers money</v>
+      <c r="E73" t="str">
+        <v/>
       </c>
     </row>
     <row r="74">
@@ -1803,7 +1807,7 @@
         <v/>
       </c>
     </row>
-    <row r="75">
+    <row r="75" xml:space="preserve">
       <c r="A75" t="str">
         <v>@khawkeye5039</v>
       </c>
@@ -1816,8 +1820,9 @@
       <c r="D75">
         <v>185</v>
       </c>
-      <c r="E75" t="str">
-        <v/>
+      <c r="E75" t="str" xml:space="preserve">
+        <v xml:space="preserve">First, you'd have to bring the average college student up to a middle school understanding of mathematics. I suggest using Dixie cups and dried beans. | Please dont give those kids anyrhing else so rediculous to Aspire to. | To show the world why Doug LaMalfa doesn't know what he is talking about?  .03% to .04% in 20 years is a huge increase (a 25% increase) in atmospheric CO2. | @michaelstevenbric  
+Watch planet of the humans by Michael Moore</v>
       </c>
     </row>
     <row r="76">
@@ -1857,15 +1862,20 @@
 It doesn't make much sense to me as to why Africa is hot - the middle East is hot, areas throughout Asia are hot and even in the United States we have several different climates throughout the whole country depending on where you are.
 Can someone please explain that to me? How global warming or climate change is a world-wide catastrophic prediction of the near future but the world consists of several different climates throughout itself already. How? We don't all share one climate.
 Weather amd climate have always existed and always changed in several areas throughout the world that are documented but mostly not because technology and communication and the ability to record videos and upload them to the world's eye are relatively new. Recording temperature is relatively new.
-I just do not understand the logic behind it. It doesn't make sense to me. I want to understand it, but I don't ever come to the conclusion matching the doom theory unless I factor in money. Then it all makes sense to me. Can someone explain it please. | @Cocozen  I think its mostly because the Sun hits the earth differently for example the North Pole has tendency to melt, and the South Pole has more tendency to form new Ice, the places in equator region are hotter because the sun hits more directly. The rest has to do with natural variations in the the different components of the  atmosphere. C02 is only 0,02% of the total atmosphere. | @badtuber1654  Right but they say that more CO2 will heat up the Earth. But historically, volcanoes release the most CO2 and when major volcanoes that are stratovolcanoes have erupted, it changed the earth's atmospheric temperature by a decrease not an increase. For example, when Mount Tambora in Indonesia erupted, it was a massive release of CO2 and it lowered global Temps by 6 degrees F for like the next 3 years, causing famine due to agriculture taking a hit because crops didn't grow well. And in 1991 the same thing happened. But there's nothing we can do about volcanoes. 
-Yet they still claim global warming - not cooling. Like how did we get an ice age? And is it actually only a local effect or does every area on Earth feel it. It makes my brain hurt. | @Cocozen  
-Oh, forgot to mention Ice Ages. The Earth’s orbit of the sun is not perfectly stable. This is the eccentricity of the orbit. Every 100,000 years (for the past 1-2 million years at least) the Earth’s orbit changes leading to either glacial periods or interglacial periods. This is the Milankovitch cycle. We are in an interglacial period right now. | Perfect! | You are absolutely right Carmen. This was a careless mistake that should not have ocurred. This could only have happened in a moment of fatigue or distraction..... | @AMATER898  No shame in that. Not as bad as the many media presenters who now use "million" and "billion" interchangeably, as if they meant the same thing. | I am not surprised at the lack of required knowledge to function properly. 
+I just do not understand the logic behind it. It doesn't make sense to me. I want to understand it, but I don't ever come to the conclusion matching the doom theory unless I factor in money. Then it all makes sense to me. Can someone explain it please. | @Cocozen  I think its mostly because the Sun hits the earth differently for example the North Pole has tendency to melt, and the South Pole has more tendency to form new Ice, the places in equator region are hotter because the sun hits more directly. The rest has to do with natural variations in the the different components of the  atmosphere. C02 is only 0,02% of the total atmosphere. | Perfect! | You are absolutely right Carmen. This was a careless mistake that should not have ocurred. This could only have happened in a moment of fatigue or distraction..... | @AMATER898  No shame in that. Not as bad as the many media presenters who now use "million" and "billion" interchangeably, as if they meant the same thing. | I am not surprised at the lack of required knowledge to function properly. 
 I was on a machinery standards group in Europe there were several so called experts .It soon became clear none had ever used the very complicated machine in and  some had not seen one.
 I actually had to go to one  manufacturing company and talk the so called experts through the operation of it .They were responsible for safety  changes made to thousands of machines worldwide. | Do you realise that it does not matter how much Co2 is in the atmosphere, what matters is whether the rate of change is too fast, Co2 has gone up from about 288 ppm to 414 ppm, since the industrial revolution. The Triassic period had much higher Co2, but it did not affect dinosaurs because the rate of change was over 50 million years not 150. So many people do not understand climate change so ask stupid questions, like "How much Co2 in is our atmosphere?" 
-When thinking about Climate change, factor in the rate of change to the concentrations in the atmosphere and whether life can adapt quickly enough, because evolution is very slow moving. | @geraldaird9390  " what matters is whether the rate of change is too fast,". Why is the rate of change so important? You are repeating this as a mantra. If the increased rate of change brings up CO2 from 0.03 to 0.05 in 200 years, how does it matter? And how do you know isn't because of volcanic activity? | Believe it or not, I was there and asked the questions, as a disident member of the Paraguayan delegation to COP20 and the then Paraguayan representative for the World Farmers Organization. | @AMATER898  Sure.   ;)   
-And I was at the White House in 2017 and asked all the Trump Supporters what his first name was, and 90% could not answer that question, even though they had voted for him. 
-Tell your fairy tales to someone else. | @frankbest2896  if you dont believe you denie, it’s easy, just stop oil people love dudes like you | ​ @rodrigomadeiraafonso3789 what would the phone or computer you're texting on be made of if not oil. No oil means the entire world shuts down. | ​ @johnchandler1687 
-John... you are making Rodrigos point for him...</v>
+When thinking about Climate change, factor in the rate of change to the concentrations in the atmosphere and whether life can adapt quickly enough, because evolution is very slow moving. | @geraldaird9390  " what matters is whether the rate of change is too fast,". Why is the rate of change so important? You are repeating this as a mantra. If the increased rate of change brings up CO2 from 0.03 to 0.05 in 200 years, how does it matter? And how do you know isn't because of volcanic activity? | @mariuspopescu284  That should be obvious to even a dullard! If the rate is slow it gives the Earth time to remedy. Volcanic activity is not responsible for what is happening, because, WAIT FOR IT, it's effect is too slow, it does have an effect but the rate of change is slow.
+I suggest you read up on the science, because you obviously haven't a clue of the reality. | Believe it or not, I was there and asked the questions, as a disident member of the Paraguayan delegation to COP20 and the then Paraguayan representative for the World Farmers Organization. | This is because in global warming stats, CO2 levels are typically measured and tracked in ppm and not percentage because of the convenience of tracking. Percentage is how it is taught in school (along with other gases) but ppm is for environmentalists. While CO2 % is 0.04%, the ppm is over 400. It was less than 300 before the industrial revolution. Around 150ppm increase in a very short time. With doubling in terms of ppm, temperature can rise by ~5 degrees Celsius. So we are very close to the doubling. 
+This is because water vapour and CO2 are the two main greenhouse gases and while water vapour is concentrated in certain lower altitudes and is highly variable and seasonal, CO2 extends to well over 50km in atmosphere and very slight variances impact weather very badly.
+A good analogy would be sodium in blood. In percentage term of blood it will be toooooo small (0.1%). It's expressed in mmol/L but say your sodium drops from 138 to 115 you are in big trouble. | Muah. So as such a learned person you must know then that climate change is an existential risk and thus you put all of your efforts into working to prevent it? Right? | ​ @SocratesWasRight  The climate has been changing for 4.6 billion years, so it is not new. It's been hotter before and colder before. Please don't bother stating not as fast as now because its bovine patties. | Yeah this story's been around for 10 years in several internet memes, hundreds of people claim they were there and asked that question..... and it's still as untrue as it was then..... | lack of knowledge about accurate percentage of co2 in the atmosphere doesnt change the fact that we are heating up the earth by pushing more and more co2 and other gases in to the atmoshpere. Its NOT about the what, but the why. Why do we negotiate energy transition? Because we all are in serious trouble.  We are not talking about reducing the co2 in the atmosphere, we are talking about reducing emission. Thats why the stuff about "if it falls above this and that percentage, plant life will die" is ridiculous, if it raises above this and that percentage, many many people will die, because of heat waves, extreme weather, floodings, war over ressources and mass migration. Yes Mass Migration, thats a reason why konservatives should be alarmed and crazy about climate change. | The point is not the amount of CO2 in the atmosphere being apparently negligible, but that the average concentration has increased by a 50%, and now it is way higher than what it was before the Industrial Revolution, what has been measured in ice cores going as back as 10 thousand years. 
+That's the part it is always conveniently silenced, same as chemistry and physics demonstrating that air having more CO2 retains more heat, that almost all climatologists agree that greenhouse gases are causing the climate to change - and the evidence we watch every day in the news catastrophe after catastrophe: heat waves, floods, droughts, wildfires, hurricanes, and the breaking of temperature records month after month, year after year.
+That guy is lying in the slimiest way possible. He knows he is lying, and manipulates half-truths to confound people. That was what he did to you. | ​​​ Are the truth and lies affecting you?
+Have you researched their global warming claims? | @MariaMartinez-researcher  i' m 71 years old. I can say with eye witness surety that the bad weather occur ancestors you're referring to are no worse than I've seen in those 71 years. If you ask people who's families have lived by the sea for generations they'll tell you that sea levels are exactly the same. Also, The Little Ice Age began in the 13th century and officially ended in 1846. We are just slowly warming up to pre ice age levels. In paleontologists writings O've read that in the early days of the dinosaur period CO2 levels were approximately 100 times todays and the Earth was covered with forests from pole to pole and teaming with animal life. The human priod so far is a blip on the radar and may be much shorter than we'd like. But Earth doesn't care. | @MariaMartinez-researcher  Dear María, you are at best misinformed. 
+- CO2 increased from about 0,28 to 0,42%, - still way below optimal concentración for plant growth but sufficient to produce plenty of desirable efects worth of tens of billions of $$ every year, auch as improved global ground cover, increased gross primary production and leaf área index, better agricultural yields and drought resistance of plants and therefore desert greening....
+- At least in 95% of the Earth's geological history, the CO2 concentration was varios times higher than today with temperatures hotter and cooler than today. And during the past 10.000 years, 65% were warmer than today in spite of preindustrial CO2 concentrations...
+- There is a logarithmic dependency between CO2 concentration and warming potential. Up to 20 ppm, WP is very high, the difference of WP between preindustrial and present CO2 concentrations is almost neglegible....
+- The story that all scientists or climatologists agree on the biased pseudo-science spread by institutions with a vested interest in their version of Climate Science, auch as the IPCC, is a lie. Google CLINTEL World Climate Declaration! More than 1600 highly competent scientists, among them Nobel Price Winners, signed an open letter to the UN Secretary General: There is no Climate Emergency!</v>
       </c>
     </row>
     <row r="78">
@@ -1882,7 +1892,7 @@
         <v>149</v>
       </c>
       <c r="E78" t="str">
-        <v>The answer is money to be made .there the answer in a nut shell | They are politicians NOT scientists! | This is what the bureaucratic state looks like. When the bureaucracy is so large and has so much power it renders the body of congress useles. | They're "experts." | Total apathy of the citizens.   and the few with skills are trying to pay the bills.  We do NOT live in a democracy or a meritocracy.   The smart and competent get worn down and abused to lift up all the turds they are forced to work under.  They are NOT sociopaths, so never get a meaningful promotion.  We are relegated to technicians and operators for the most part and that is where we are held.   Too useful in our role to get on the committee.   Working 70 hours a week will do that for the competent.   In answer, I don't now how we get qualified people into these jobs that pay dick and require corruption to make it worthwhile.  As the 1 competent committee member, nothing at all will get done and you will just get disenchanted as everything you try falls on deaf and dumb ears and as soon as you plug a bad corruption hole... prepare for the threats, anger, and rage of the displaced corrupt.  There is zero hope any human can make a dent without destroying themselves.  Best option... Sentient AI "leaders". | Why the people allowing it , aren’t you part of the people? Why are you allowing it to happen. | The majority of the public is | The people at NASA aren't idiots | @frutiger_owl  no but they are liars! Government stooges if you will. | @frutiger_owl  yes they are.</v>
+        <v/>
       </c>
     </row>
     <row r="79">
@@ -1919,7 +1929,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" xml:space="preserve">
+    <row r="81">
       <c r="A81" t="str">
         <v>@mariemackenzie01</v>
       </c>
@@ -1932,12 +1942,8 @@
       <c r="D81">
         <v>89</v>
       </c>
-      <c r="E81" t="str" xml:space="preserve">
-        <v xml:space="preserve">Yea don't feel bad, they're federally subsidized to farm inefficiently. Grow avocados where avocados don't grow, that kind of thing. | @SeraphsWitness  Market forces dominate. Shipping is a big deal. Tariffs are a big deal as well. In the Western US water rights are a huge deal. So many things shape what is grown and where. | @debi5292  I don't think I'd be so bold as to say market forces are dominating in agriculture. It's been heavily subsidized for a long time. Big Ag is one of the primary REASONS we have a water shortage out west. They're the primary consumers. Residential water consumption is only 5% of the total.
-So yes, when you incentivize farmers to grow almonds, for instance, of course they're going to go to greater lengths to grow almonds even if the market forces don't incentivize it; because the government is handing out free money. And almonds are one of those crops that is insanely thirsty.
-So yes there are many forces that shape the industry. But federal subsidy is easily the biggest. Look, California is the #1 producer of avocados in America by a long shot, yet we still import most of our avocados from Mexico because they're cheaper. Our market incentives are completely jacked up. | @SeraphsWitness  I can not speak to California Ag at all. In the Midwest we are much more sane in our approach. California has soooo many issues both politically and economically. 
-Ethanol is the replacement for MTBE and reduced emissions. Ag component is secondary to that. | @debi5292  Yes, California is completely jacked out here.
-That said, I don't think federal subsidies should be going to farmers at all. Let the market regulate it. People spend their own money a lot more carefully than they spend free money. | @SeraphsWitness  Oh, also, you never see farmers, like this man, complaining to the gov't panel.  Never.  MANY farmers are being forced out of business. | They get plenty of socialized help from the feds. | @joshd79  Only when weather or politics get in the way.</v>
+      <c r="E81" t="str">
+        <v>Yea don't feel bad, they're federally subsidized to farm inefficiently. Grow avocados where avocados don't grow, that kind of thing. | @SeraphsWitness  Market forces dominate. Shipping is a big deal. Tariffs are a big deal as well. In the Western US water rights are a huge deal. So many things shape what is grown and where. | @SeraphsWitness  Oh, also, you never see farmers, like this man, complaining to the gov't panel.  Never.  MANY farmers are being forced out of business. | They get plenty of socialized help from the feds. | @joshd79  Only when weather or politics get in the way.</v>
       </c>
     </row>
     <row r="82" xml:space="preserve">
@@ -1954,7 +1960,9 @@
         <v>387</v>
       </c>
       <c r="E82" t="str" xml:space="preserve">
-        <v xml:space="preserve">Face the facts. You don't know what happens to such opposition. | Representative LaMalfa is being misleading, 99% of the atmosphere is nitrogen and oxygen but neither of them are greenhouse gases like CO2, they don’t trap heat in the planet. | ​ @Garioty  by listing the actual number hes being misleading how? | yes, these politicians are idiots. but it is even more idiotic to say that an increase in co2 will have no negative impact on the climate because the numerical share is so small. | @7sonderling   Exactly, this is just strawman buffonery, the percentage CHANGE is the important fact regarding our atmosphere. in my lifetime the CO2 content has risen from 280PPM to over 400PPM that's scary to anyone who knows a bit about atmospheric science. | ​ @7sonderling  I guess you missed the part where Sen. LaMalfa pointed out that without CO2 plants will die. In fact, in my state where we have some of the LEAST CO2 emmissions, we're seeing the result of just that to some degree.️ | Your lack of understanding is truly profound. You really ought to desist from commenting on this topic before you embarrass yourself further. 
+        <v xml:space="preserve">Face the facts. You don't know what happens to such opposition. | Representative LaMalfa is being misleading, 99% of the atmosphere is nitrogen and oxygen but neither of them are greenhouse gases like CO2, they don’t trap heat in the planet. | ​ @Garioty  by listing the actual number hes being misleading how? | @williamwest9204  He's not mentioning how much that number has increased over recent years and how rapid that change has been
+It's an old climate denier trick
+I agree that the panel should know this....... if they did he'd be looking pretty embarrassed | @williamwest9204     He is trying to use this statistic to say the amount of CO2 in the atmosphere doesn’t matter or cause climate change because it is such a small amount, but that doesn’t make sense, because while nitrogen and oxygen make up 99% of the atmosphere, neither are greenhouse gases and therefore don’t cause a warming effect on the planet in the first place. Also when he says there is a “tiny change” in CO2, it has actually increased 50% since the industrial revolution, which is a massive change that will lead to changing weather patterns, increased drought and ocean acidity among other changes that many plants and animals will find it hard to adapt to in such a short time. | yes, these politicians are idiots. but it is even more idiotic to say that an increase in co2 will have no negative impact on the climate because the numerical share is so small. | @7sonderling   Exactly, this is just strawman buffonery, the percentage CHANGE is the important fact regarding our atmosphere. in my lifetime the CO2 content has risen from 280PPM to over 400PPM that's scary to anyone who knows a bit about atmospheric science. | ​ @7sonderling  I guess you missed the part where Sen. LaMalfa pointed out that without CO2 plants will die. In fact, in my state where we have some of the LEAST CO2 emmissions, we're seeing the result of just that to some degree.️ | Your lack of understanding is truly profound. You really ought to desist from commenting on this topic before you embarrass yourself further. 
 On the other hand, it is possible that you are a parody account, and that you have fooled us all with your sarcastic wit. If so, bravo. It worked. | @biggoards2772 i agree with you...plants need CO2!  but nobody wants to eliminate CO2 - we just dont so much more of it! its bad for the climate AND too much CO2 is not good for plants as well - first they grow a little better, but with much more they wither away! everything was in perfect balance - we should keep it that way... | @7sonderling  I want environmental change too, but SMART changes, not reckless ones. | @biggoards2772  agree. | @biggoards2772  So… how did plants grow before humans started burning fossil fuels? Like, we have enough carbon dioxide in the air for all plants, you don’t really get a local shortage of carbon dioxide, so idk how you get that example but it’s most likely other reasons that the plants die. Honestly I would recommend you read some scientific papers instead of getting such information from social media or politicians. | @robanvisser8714  Your statement is contradicting. We only add to CO2 levels. The problem is to what degree and to what role the environment itself plays. CO2 has existed since the dawn of the planet and to say we (humans) created CO2 is both arrogant and stupid. | @biggoards2772  I was asking that question because you state that plants need CO2 to grow. I never stated that humans were the first to create CO2, that is just you drawing a hasty conclusion. Besides, we usually see an increase in temperature and then an increase in CO2 if we look at prehistoric data, for example the ice ages. Now it’s the other way around, we first have an increase in CO2 levels and then an increase in temperature following the CO2. Burning fossil fuels releases more CO2 into the air, which is undeniable, and CO2 is a known greenhouse gas, there isn’t any other significant change that can explain the sudden change in temperature. So I would like you to give me an explanation on why the earth is heating up, and why you deny the increase of greenhouse gasses to be the cause. | @robanvisser8714  I'm not denying the increase, but rather the extent. You say that prehistoric data shows that increased CO2 leads to ice age weather? (Not really sure where you were going with that statement) But we do know that increased temperatures could be caused by a variety of issues and to single out one variable and then try and throw every resource we have at said variable is reckless. The answer is ambiguous at best, so to solve the problem, we should be innovating more and spending less. Money doesn't solve everything. If each state were to innovate ideas that were cost effective; at the very least we'd know if the problem could be pinpointed and then addressed SMARTLY. Historically, the planet has increased temperatures at various points in time, this is nothing new. The speed at which it's doing so is different, but the process remains the same. If you want to address these variables do it smartly not recklessly. Heck, I'm no scientist and even I know that government intervention is terrible for the world of science. | @biggoards2772  What is was trying to state with the ice age part, was that we usually see an increase of temperature first, and after that an increase in CO2 concentration in the air. Now it's the other way around, and we can conclude it's not part of the natural cycle. This also explains that the process is not the same. There has been one instance a few million years after the dinosaurs died, that the world suddenly increased in temperature because of greenhouse gasses, just like right now. But that went at a rate 40 to 400 times slower than right now. This was likely an increase in vulcanic activity, or another cause of a sudden increase of greenhouse gasses. but again, it went much slower than right now. And we know the increase of temperature can have varying causes. And I won't deny that, but right now, there isn't much difference between now and pre-industrial times, except of that we use fossil fuels extensively right now, and burn down large amounts of (rain) forest to plant cashcrops or have lifestock graze it. Chopping wood is not that bad, because usually the big trees produce as much oxygen during the day as they release CO2 at night. But when you burn the trees to increase fertility, all of the CO2 stored in the wood will now go back in the air, and instead of new trees you get crops which barely reduce CO2 levels. | @robanvisser8714  Unfortunately, until we find new innovations, crops are extremely necessary and so is the process; otherwise yields will be low. | Sadly he's outnumbered by fools and ignoramuses. | He’s my Rep! Kudos to Doug!</v>
       </c>
     </row>
@@ -1972,7 +1980,7 @@
         <v>229</v>
       </c>
       <c r="E83" t="str">
-        <v/>
+        <v>True! They should ask about nuclear energy. I never get good answers from posters. They don't know anything about it. | True! They should ask about nuclear energy. I never get good answers from posters. They don't know anything about it.</v>
       </c>
     </row>
     <row r="84">
@@ -2091,7 +2099,7 @@
         <v>86</v>
       </c>
       <c r="E90" t="str">
-        <v>And the answer would be that the money ultimately comes from governments.  No conflict of interests here, right? | WEF | Initials: GS, founder of the rebellion extinction cult. | Exactly</v>
+        <v/>
       </c>
     </row>
     <row r="91">
@@ -2146,7 +2154,7 @@
         <v/>
       </c>
     </row>
-    <row r="94">
+    <row r="94" xml:space="preserve">
       <c r="A94" t="str">
         <v>@camerongunn7906</v>
       </c>
@@ -2159,8 +2167,9 @@
       <c r="D94">
         <v>219</v>
       </c>
-      <c r="E94" t="str">
-        <v/>
+      <c r="E94" t="str" xml:space="preserve">
+        <v xml:space="preserve">​@Chris Jones love how u bring up smn completely unrelated cuz u know u cant win the original argument | @Chris Jones how about how many laws do most criminals give a damn about when they're made? | @Chris Jones what are these registered Firearms you're speaking of? Firearms aren't registered in the United States. In fact having a registry of firearms in the United States is against federal law.
+The question you're looking for is how many people are killed each year by legally purchase firearms. The answers of that is far less than are killed with illegally acquired firearms. Just take a look at Chicago. | ​@Chris Jones that's literally a blatant lie. | @Chris Jones my point is, if it wasn't obvious is that laws only impede the law abiding; they do nothing to restrain the criminal. Sure enforcement can do something about it, but only after the deed takes place - but with such a staunch laws, who's at the real disadvantage; the criminal or the law abiding? | I tend to think only people who use due diligence to form their opinion would have known the answer immediately | these  people  are not climate scientists. ,,why would they be expected to know the %of co2 in the atmosphere ...its like asking a panel of scientists or politicians to  answer questions on economics....Id suggest Mr La Malfa  had looked it up about an hour before proceedings....</v>
       </c>
     </row>
     <row r="95">
@@ -2177,7 +2186,7 @@
         <v>231</v>
       </c>
       <c r="E95" t="str">
-        <v>Blindsiding the panel with an irrelevant question is the point.  it doesn't matter what the accurate number for the % of CO2 is, the world is experiencing the effects regardless of whether or not the panel can answer a stupid question. | ​ @joeshithragman3264  He asked a basic question pertaining to the topic. If they're going to make an argument for reducing carbon emissions because it's leading to the end of civilization ,that's a relevant question. The fact that they couldn't answer it ,because they're clueless shows how not serious they are. | @joeshithragman3264  Why are you wasting CO2 by commenting of a device that uses electricity? | @johannesswillery7855  Almost a clever response, but what device is at issue here? | @joeshithragman3264  What device do you use? | @johannesswillery7855  I don't need no stinking devices.</v>
+        <v/>
       </c>
     </row>
     <row r="96">
@@ -2229,8 +2238,9 @@
       <c r="D98">
         <v>269</v>
       </c>
-      <c r="E98" t="str">
-        <v/>
+      <c r="E98" t="str" xml:space="preserve">
+        <v xml:space="preserve">If you expect politicians to show even a modicum of real knowledge, you'll be sorely disappointed. | @gratius1394  Funny, because the one asking questions to the panel is another politician. And I assure you he also didn't know this. | But with the new consensus math, 78+21+5=100 | @sinjin6219  Take your calculator and try again!Mine is showing 104 | To be fair, I am much younger than these panel members and even then, what I learnt about the atmosphere in school was so long ago | ​@Geordie Wishart  your also not arguing a point at a government level, in an attempt to change a way of life. This is their job and yet, like with all other subjects they claim to be experts on, they don't even comprehend the basics of the subject. They should all be forcibly fired. | Yeah, how about DON'T take a guess?  Maybe know this information.  A guess isn't good enough when you're trying to affect the lives of so many people. | At sea level. Oxygen at my altitude is 16.6% and I did not realize this till I went back to Tennessee a couple years ago and went for a hike. When I got back to my Jeep I wasn't the least bit winded. Then it occurred to me that I'm breathing in 25% more oxygen. | @HamrickCE  That's not the way it works... The composition of the atmosphere remains pretty constant across the surface of the earth, even at the tip of everest it's still about the same as at sea level (and by about, I mean not even a 1% difference in oxygen to nitrogen ratio as far as I can find), the reason you weren't winded isn't the composition of the atmosphere, but the pressure, there's not less oxygen relative to nitrogen where you are, there's just less air overall (at the tip of everest there is 70% less oxygen than at sea level, but there is also 70% less nitrogen and argon). Where you are is likely the equivalent to 16.6% oxygen at sea level, but isn't actually just 16.6% oxygen. | @BilboSwagginsTheThird  ah, so all the charts showing 16.6% oxygen at 6000 ft. Are wrong and you are right. Gotcha | @HamrickCE the air is rarer the higher you go; that’s why you need extra oxygen or pressurised premises from
+10,000 feet above MSL. But the percentage composition of air remains the same. | @sumanamjs  rarer? Meaning less. Everyone understands the charts which means you are here just to argue. | 'It was my understanding there would be no math' -Gerald Ford.</v>
       </c>
     </row>
     <row r="99">
@@ -2250,7 +2260,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" xml:space="preserve">
+    <row r="100">
       <c r="A100" t="str">
         <v>@dirgemcelvoy2583</v>
       </c>
@@ -2263,9 +2273,8 @@
       <c r="D100">
         <v>208</v>
       </c>
-      <c r="E100" t="str" xml:space="preserve">
-        <v xml:space="preserve">The amount of chlorine in a pool is about  0.000001% and yet if you add more than that it starts to make your eyes itch and even more can be hazardous.  This point of CO2 only being a small percentage is stupidly pointless. | So what did you learn?
-Did you learn WHY non-scientists claim the proportion of atmospheric CO2 is relevant? If so, I must have missed that bit. Perhaps you can direct me to the timestamp where this happened. | @MrYahboo  Well, I didn't know that CO2 represented only .04% of atmospheric gases.  No doubt you did; so it's a shame you weren't on the panel.  Otherwise, to say we "learned" something is perhaps too strong.  It would be more accurate to say that the video provided further evidence that climate change activists have no clue what they're talking about.  As for the timestamp, you might want to look at the upper left-hand corner of the video for the date of the hearing.</v>
+      <c r="E100" t="str">
+        <v/>
       </c>
     </row>
     <row r="101">
@@ -2299,7 +2308,7 @@
         <v>50</v>
       </c>
       <c r="E102" t="str">
-        <v/>
+        <v>Unfortunately; it demonstrates our general edumekasjon level.  And half of 'm are even stoopidier than the average.... | Exactly. There's no climate crisis. It's all BS</v>
       </c>
     </row>
     <row r="103">
@@ -2337,7 +2346,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" xml:space="preserve">
+    <row r="105">
       <c r="A105" t="str">
         <v>@joedennehy386</v>
       </c>
@@ -2350,11 +2359,8 @@
       <c r="D105">
         <v>129</v>
       </c>
-      <c r="E105" t="str" xml:space="preserve">
-        <v xml:space="preserve">You do know that the recent poll shows that 97% of scientists don't want to be defunded... | I’m also from NZ.  I learned that in primary school, intermediate school, secondary school and university. What the heck was that guy doing at school? | What's funny is the thought that he is likely one of those '97%' of scientists that agree  that we're all going to die due to climate change. | @stilllearning1160  Have you ever heard of a straw man? Firstly, this is an anonymous post on YouTube. Assuming it’s true, we don’t know if the person questioned was any kind of scientist. If he was, we don’t know what kind or whether he’d have any kind of expertise that allowed him to determine the truth. Also, the 97% figure refers to a very different question to how you phrased it - it’s about actively publishing climate scientists since 2000 and whether their papers state or imply an anthropogenic cause, not about whether it’s going to kill us all (it’s not btw). Also the number could be anywhere from 80-97% depending on methodology. But that doesn’t mean 3-20% actively disagree, it’s about whether an opinion on that specific topic was in the study. If you took the number who actively disagreed, then it would not be 3% and it sure as hell wouldn’t be 20%.
-You could argue “they won’t get published!” But while that would be true if they were just spouting conspiracy nonsense, peer review looks at quality of data and methodology and the rationality of conclusions. If someone had good evidence that it was not anthropogenic and their methods were sound, climate scientists would very much want to know that. 
-Incidentally if that is the case, we’re in deep trouble. If it’s us causing the problem, then we have control over how bad it is. If it’s a natural cycle then there’s probably nothing we can do about it and our civilisation is likely to face an existential threat. That doesn’t mean we’re all going to die, but it does mean everything is going to gradually get much harder and more expensive, and when that happens there are usually wars over resources | @tSp289  Did you know what the %age of CO2 was in the atmosphere when you wrote your comment? and if you did, why didn't you discuss the obvious misunderstanding of the question of the content of CO2 in the atmosphere as that is fundamental to the climate change argument.? | @philhealey4443  Any mildly inquisitive person would have found out that the current levels of CO2 are at a geological historical low. Had the level of CO2 dropped from the upper 300's ppm by the same amount as it has risen there would not be sufficient CO2 in the atmosphere to feed the plant life and plant life would have started to die, causing us to start to die too. | @davidtuer5825  Strange absence of mild inquisitiveness! | ​ @tSp289 I just have to say you're very naive about the integrity of modern science.
-I wish it was like you say. That peer review meant we could trust it. But it isn't and we can't. | ​ @tSp289 wow must be nice to be that naive and still think things like peer review isn't corrupt. don't change buddy | What was his field? | @tSp289  The man was an established scientist, he ought to know the fundamentals of the crisis we are told the world is facing. I knew the answer. | I'm curious to know. Did this nz scientist publish a book with the word 'alarmist' in the title? | Huh? Amazing! | That definitely never happened</v>
+      <c r="E105" t="str">
+        <v/>
       </c>
     </row>
     <row r="106">
@@ -2407,9 +2413,12 @@
       <c r="E108" t="str" xml:space="preserve">
         <v xml:space="preserve">With the increased plant growth from good-CO2 there will be an increased amount of Oxygen emitted back into the atmosphere, which will then lower the "parts-per-million" of Carbon Dioxide - it's almost like our Earth has some kind of finely tuned "Carbon-Cycle" built-in ! | @joeteejoetee  
 Who would have thought it! 
-I'm amazed how many well educated people fall for the CC con. I guess Goebbels was correct when he said "Tell a lie often enough and people will believe it!'. | Nicely said, thank you. | No, increasing CO2 doesn't make plant life do a lot better.  Plant life is adapted to a world with about 300PPM of CO2.  The CO2 content right now is over 400PPM.  There is no huge increase in plant life and some varieties are actually having trouble.  We need water to drink but we can also drown. | @kensmith5694  You should actually look at the evidence instead of just trusting "the narrative" as it will limit your ability to critically think through this stuff. The reality is that there has been MUCH more CO2 in the biosphere in the past &amp; the plant life was much more plentiful as a result. We have been though many surges in the CO2 amount &amp; the plants went through greening surges as a result, but unfortunately so much of the CO2 of the past is now locked away in limestone &amp; fossil fuels. Even just with the amount of extra CO2 we have released into the biosphere since the industrial revolution has measurably increased the greening of the planet, so you are completely incorrect about this. The fact is that the evidence shows our star the Sun is the only significant source of any change in climate on Earth &amp; when the sun increases the temperature on Earth, the amount of CO2 goes up as a result. | @kensmith5694  Ken with all due respect, you are simply wrong. Increased co2 increases the health and size of plants. This has been shown by simple teenage science fair projects. Also, with more co2 the plants require significantly less water since they develop fewer structures to take in Co2.
+I'm amazed how many well educated people fall for the CC con. I guess Goebbels was correct when he said "Tell a lie often enough and people will believe it!'. | Nicely said, thank you. | No, increasing CO2 doesn't make plant life do a lot better.  Plant life is adapted to a world with about 300PPM of CO2.  The CO2 content right now is over 400PPM.  There is no huge increase in plant life and some varieties are actually having trouble.  We need water to drink but we can also drown. | @kensmith5694  You should actually look at the evidence instead of just trusting "the narrative" as it will limit your ability to critically think through this stuff. The reality is that there has been MUCH more CO2 in the biosphere in the past &amp; the plant life was much more plentiful as a result. We have been though many surges in the CO2 amount &amp; the plants went through greening surges as a result, but unfortunately so much of the CO2 of the past is now locked away in limestone &amp; fossil fuels. Even just with the amount of extra CO2 we have released into the biosphere since the industrial revolution has measurably increased the greening of the planet, so you are completely incorrect about this. The fact is that the evidence shows our star the Sun is the only significant source of any change in climate on Earth &amp; when the sun increases the temperature on Earth, the amount of CO2 goes up as a result. | @Dorakuwel  I have looked at the evidence.  Plants are adapted to a 300PPM CO2 level.  Add more any you may get very large plants but you also may get a decrease in the yield of the part of the plant you want.  You can end yo with a huge pile of squash plant (for example) but with less actual squash to take to the market. | @kensmith5694  Ken with all due respect, you are simply wrong. Increased co2 increases the health and size of plants. This has been shown by simple teenage science fair projects. Also, with more co2 the plants require significantly less water since they develop fewer structures to take in Co2.
 I have seen estimates that with a doubling of co2 the Sahara desert would bloom and reduce the severity and frequency of hurricanes impacting North America.
-Also, having a bunch of biologists and geologists in the family I have had the benefit of the truth. As a retired businessman, all I can say is if someone comes to me saying in exchange for all my liberty and freedom he will control the weather, I say bulls**t! | @jamesbooth3360  No I don't have it wrong.  Some plants have a lower yield of the part of the plant you want with a bigger CO2 concentration.  A giant plant is often not the goal of growing a plant. | @kensmith5694  Some greenhouse owners use CO2 generators to increase yields. | @kensmith5694  Yes it does. Green houses for commercial vegetables use CO2 generators machines in order to increase the percentage of CO2 inside the green house to make the crops grow faster and bigger. Go to a green house farmer and you see it by yourself. | @kensmith5694  According to NASA the planet is 15% more greener than a few decades ago.  That is an area greater than the US.  You better go tell NASA they are wrong. | @sw8741  Plants have pores called stomata on their leaves through which gases pass. In arid regions, many varieties have problems surviving because if the stomata open wide enough to get enough CO2, they lose too much moisture. As CO2 levels have risen, this has become less of a problem because the stomata don't have to open so wide. | @sw8741  A few decades is a fairly small amount of time.  Read my comment more carefully and think | @kensmith5694  Sir, it is with great respect that I must inform you that your statement happens to be NOT the truth. In times past, during the age of huge plant growth, that culminated in subsequent huge animals and lots of them, the CO2 level was more like Quote; "Olsen hypothesized that even with extremely high atmospheric CO2 levels of 6,000 ppm that were recorded during the Age of Dinosaurs and the subsequent global heating, humans could potentially survive — thanks to technological advancements, rather than evolution." 6000 parts per million, NOT a mere 400. What happened next? The trees died and more trees grew before the old ones could rot. Such is the way of forests. We must be glad for that period in Earths history, for THAT period gave us coal. | @BobPackard  You clearly didn't understand the substance of my comment.  Numbers of critters and how bit they are is no indication of how happy they are. | ​ @kensmith5694  we also need oxygen to breathe. | @Flussig1  Oxygen is over 20% in the Air - That's One Fifth (1/5th) of the air, not "parts-per-million" scare tactics. | @joeteejoetee  Okay, but I never mentioned PPM, just that we need oxygen. | @Flussig1  100% agree with needing more Oxygen &lt;-- which is made by plants feeding on the very sparse amount of Carbon Dioxide that is today in Earths' atmosphere that feeds all plants wherein they use solar power to make even more Oxygen. #Photosynthesis</v>
+Also, having a bunch of biologists and geologists in the family I have had the benefit of the truth. As a retired businessman, all I can say is if someone comes to me saying in exchange for all my liberty and freedom he will control the weather, I say bulls**t! | @kensmith5694  Some greenhouse owners use CO2 generators to increase yields. | @jimbo32234  Yes, some to add CO2.  Not all do.  Have you ever considered why? | @kensmith5694  It increase yield, I can see in other comments you try to refute that but its a fact that yields increase with CO2 levels.
+Did you know there is only 0.04% CO2 in our air, and if it drops to 0.02% all of our plant life will die?
+Not a single reputable scientist can say for certain that if all of the g10 countries cut emissions to net zero tomorrow, that it will make a single degree's worth of difference to the worlds temperature. You have bought into a lie, one they have been telling for decades in one format or other.  The net zero revolution has benefitted corporations the world over by Trillions.
+Ever notice how the ultrawealthy and politicians can completely escape the measures they implement?  Bill Gates for example, he's a massive advocate for CO2 reduction, yet flies everywhere in a private jet and tries to justify it his "carbon offsetting" which is a complete joke, and only available to those with massive wealth. | @jimbo32234  Not in all cases like I said.  Some plants make more green part and less of the bit you sell.  I know that the current level is 428PPM in the last figure I saw.  In the year 1998, the level was 330PPM.</v>
       </c>
     </row>
     <row r="109">
@@ -2426,7 +2435,7 @@
         <v>80</v>
       </c>
       <c r="E109" t="str">
-        <v/>
+        <v>He seemed to say that a shift of .02% can have catastrophic effects. I'm sure that was what he was going for though.</v>
       </c>
     </row>
     <row r="110">
@@ -2443,7 +2452,7 @@
         <v>214</v>
       </c>
       <c r="E110" t="str">
-        <v>They're coming for rice too saying the paddies its grown in give off methane. | I’m sure he’s very nice, and probably very good at growing rice, but his grasp of science and mathematics appears to be poor. It’s a shame he’s been put into a role where an understanding of science would be valuable. | He sounds like the only man in California with smarts and sense.  Of course, he couldn't have gotten elected if that were the case.  Let's hear from more smart Californians and less from their liberals.... | @harrylazard805  He’s my rep, and he is not a good dude.</v>
+        <v/>
       </c>
     </row>
     <row r="111">
@@ -2550,10 +2559,10 @@
         <v>129</v>
       </c>
       <c r="E116" t="str">
-        <v>Amen! | hi. Rep Doug lamalfa. the guy in the clip, received $30,876 in campaign contributions from oil and gas lobbies this past election season. seems like common sense costs a lot, and also aligns with the interests of oil and gas companies woah that's crazy! | ​​ @stonyponyofficial  yep..hard to find politicians in California not in the progressive cult..every politician is given cash from someone in favor of something; in this example of LaMalfa,  it just happens to be true that the sky isn't falling; he speaks the truth | @stonyponyofficial  you want gas when your car is on Emty | @stonyponyofficial  okay, I'll assume that what you said is true. What difference does that make to what he said in the video? | AMEN. | When it comes to complex technical topics, “common sense” is almost always WRONG. | He's lying to you, misleading you. He knows the truth, but plays dumb people like a fiddle appealing to their "common sense". It's a thought terminating tactic to keep you from thinking to much about things. | ​@Tim Barton  what are the exact lies Mr LaMalfa is telling? -can you counter them here with truth? | @timb83  What lie?  It's true the atmosphere is made up of less than 1/2 of one percent. | @smiffm428  While the facts about the concentration of CO2 might be correct, the implication that a  subjectively “small” concentration means a “small” effect is what turns this into a lie. Throughout science and technology, “small” numbers routinely translate into enormous effects. If you think otherwise, I invite you to add 0.04% arsenic to your diet, 0.04% smoke to the air you inhabit, or 0.04% impurities to the integrated circuits in your devices. (Seriously, don’t do that. In some cases, impurities a million times more “small” than that would cause huge problems.)</v>
-      </c>
-    </row>
-    <row r="117">
+        <v/>
+      </c>
+    </row>
+    <row r="117" xml:space="preserve">
       <c r="A117" t="str">
         <v>@brandonkenney6310</v>
       </c>
@@ -2566,8 +2575,11 @@
       <c r="D117">
         <v>159</v>
       </c>
-      <c r="E117" t="str">
-        <v/>
+      <c r="E117" t="str" xml:space="preserve">
+        <v xml:space="preserve">To go from 0.4% to 0.2% is actually a 50% decrease in relative terms. So, we are miles away from the 0.2% figure. Also, the fact that CO2 levels have been increasing for many years indicates that there is very little danger of a sudden 50% drop in CO2. Moreover, if you also dropped the O2 content of the atmosphere by 50%, it would then be 10.5%, which is around the threshold where humans lose consciousness. So, of course if you suddenly start dropping the concentrations of important gases in the atmosphere by 50%, then we're going to have a problem. That isn't anything shocking or surprising. | CO2 levels ought to be considered in terms of relative change not absolute percent. This is why ppm is used for CO2 measurements. | An increase in CO2 will actually increase Oxygen through increased flora.  The system is responsive and dynamic, almost like someone designed it. | ​ @jamesstrawn6087 Yep, and it will also lead to acidification of the ocean and plant life becoming too hot and being unable to cool themselves. Which leads to mass extinctions. | @ShedShoww  
+They actually dont have that ability. However measuring isotopes in rocks and fossils gives a decent guess. | That would be a reduction of more than 50% of current CO2 levels, and that’s not going to happen. CO2 “reduction” is about offsetting our current CO2 production. Before the Industrial Revolution, the amount of CO2 in the atmosphere was around 0.028% and it wasn’t as if plants were struggling to exist back then | @davidmurphy7332  the issue is that CO2 is required for humans and all other mammals to exist as well. It is the molecule that our lungs process to oxygenate blood. 
+CO2 isn't the problem. And reducing it would be detrimental to all life on the planet. | @davidmurphy7332  They actually are. Farmers pump CO2 to over 1000ppm and higher. We are well below optimum levels for plants and still at the lowest levels in the geological record. What's worse is that CO2 levels drop during glacial maximums. We are approaching the end of the warm (interglacial) period of the present ice age, so if we had not put CO2 back into the atmosphere it could have been devastating for plant life. | @davidmurphy7332  didn't know they had the ability to measure C02 200 years ago | @alanchilds1456  Ice locks in atmosphere when it forms. A simple Ice core sample can fairly reliably give you a history of the atmosphere. 
+FYI CO2 is in a very difficult balance. At 0.2% concentration you will begin to feel ill and at 4% all animal life is dead. Anything over 0.5% is classed as too dangerous for working in. Also CO2 tends to build up indoors so it's not uncommon to see 0.12% CO2 is some places. | @alanchilds1456  science is amazing! | @chrisdodds1877  Wrongo bongo. During the Jurassic period CO2 was as high as 15% of the earths atmosphere. What happened? The world was a vast greenhouse with no polar ice caps. Enormous plants and greenery lead to enormous herbivores, which lead to enormous carnivores. (Sometimes a little research goes a long way) | ​@RandalColling During the jurassic, the C02 levels were about 5 times what they are today. Meaning around .2% to .25% nowhere near the 15% death trap you're talking about. | @danny234555  A little research would do you some good my friend.   But yes I think the real numbers were 5% of the atmosphere back 500 million years ago. | @RandalColling  the jurassic was 145-200 million years ago. 500 million years ago was the Cambrian where life hadn't even left the oceans. | ​ @alanchilds1456  Well, listen I'm no climate activist but of course you can find frozen samples from 200 years ago to measure CO2 levels from that time. You'd be amazed how advanced Geology research is these days. | @alanchilds1456  bro old air trapped in my places can be dated | @chrisdodds1877  exactly | @blazingguyop  optimal growing conditions are 0.045 Co2</v>
       </c>
     </row>
     <row r="118">
@@ -2604,7 +2616,7 @@
         <v>God help us!</v>
       </c>
     </row>
-    <row r="120" xml:space="preserve">
+    <row r="120">
       <c r="A120" t="str">
         <v>@citomp1240</v>
       </c>
@@ -2617,10 +2629,8 @@
       <c r="D120">
         <v>145</v>
       </c>
-      <c r="E120" t="str" xml:space="preserve">
-        <v xml:space="preserve">@terenceiutzi4003  Since you want smart conversation, how much radiation is reflected back by the other more abundant gases in the atmosphere, oxygen, nitrogen and argon? What would be the planet average conversation without CO2 in the atmosphere? Do you know any of these? How unintelligent you are without knowing those numbers. The answer are zero, 0 for all three. The average temperature without CO2 would be 260 Kelvin, with 0.02% (half of what is today, pre industrial era) was 286. Just 0.02% makes the planet at least 10% hotter. What do you expect to happen with double that amount? | @Braiam  nitrogen reflects back the most because it is the most abundant but water vapor is by far the greatest | @Braiam  at what concentration does Co2 start reflecting more IR back away from the earth's surface that was proven in the early 1800! | @Braiam  how much warner was it at the end of the Medevil warm period then it was at the start of the industrial Era | Here's where that .03% figure comes from if anyone is curious:
-In 1998 a paper was published with this .03% but it was talking about carbon flux, not total c02 in the atmosphere. A blogger read the abstract of the paper and misunderstood what it was saying. No, he didn't even bother to read the whole paper. The authors of the paper contacted him and explained his error. He eventually admitted his mistake and deleted the post, but by that time it had been picked up by another more prominent climate denial blog and was propagating through the internet. I'm fairly sure that climate denial blog still has that same post. 
-So, here we are 25 years later with politicians repeating falsehoods they don't understand all because someone else didn't understand what they were reading and didn't make an effort to understand it. | @Terence Iutzi  Russia uses oil so your comment is lunatic | @terenceiutzi4003  Agreed. You will never get a sensible comment out of the Klimate Kult. | He uses talking points that are at least 10 years old and have been addressed, except he makes it even more incoherent and inane than it was originally. He doesn't understand science much less pseudoscience. Whether it's science or pseudoscience you're after, I wouldn't listen to this guy for information. | @tripe2237  They've never been addressed by the Kult. And you seem to be spectacularly unaware of 'logarithmic response' means. | Your not going to get an intelligent conversation taking to this man. He will tell you what you want to hear, and you'll feel better, but you'll be stupider for it.</v>
+      <c r="E120" t="str">
+        <v/>
       </c>
     </row>
     <row r="121">
@@ -2694,8 +2704,11 @@
 Thers a clear case that life on the planet is better off at higher co2 levels and that human activity might have averted the entire cold death of the planet.
 No one can give a case that higher co2 levels are bad or that warming is bad, perhaps the rate that its happening is too fast but its near impossible to tell, especially when direct habitat destruction causes far more damage than the climate changing, there is no case for spending billions on the climate instead of the environment.
 Oil is relatively low impact environmentaly, co2 is not a pollutant, lithium and cobalt for renewables is causing massive pollution and is environmentaly devastating. | @quillo2747  dang, its almost like there are many other factors that exist of which all of them you ignore.
-nice job oil apologist, you really have bought their propaganda and stand tall against the science. | @rorycannon7295  you have no idea what science even is. | @bigdogbill119  "you have no idea what science even is."
-which is why im majoring in stem, huh. | Relatively speaking it is a large increase but as a % of the atmosphere it is still negligible and considering that the biggest explosion of life on earth occured when it was massively (magnitudes) higher. As the speaker points out we are actually at the bottom of the scale in terms of what is required for a healthy planet. Any less and plants can't survive. | No it isn’t | @Shena1580  about 6000 years old | Fun Fact C02 levels during the time of the Dinosaurs was over 5 times higher (over 1500ppm compared to todays roughly 400).  It's due to tectonic plates subducting (going under) on the ocean floor.  As one slips under the other massive amounts of decaying organic matter (mostly from plankton/algae) that has fallen to the floor goes with it, sealing away C02 virtually the rest of time (some comes up during volcanic eruptions but most disappears into the core).  I sometime wonder if the sole purpose of humans in the grand scheme of things was to prevent the early heat death of the planet through the eventual collapse of the greenhouse effect.  There's some irony considering how much effort we are going to prevent something that to the long term success of life on the planet is actually helping. | @123chargeit  Hmm. At what point during the "dinosaur era"? You do know that there were catastrophic climate events that took place during the course of that peroid. They were kind of slow though (tens of thousands of years or much longer) and still managed to kill off a huge % of the life and species on the planet. The rate the climate is changing now is the important bit. The ecosystem have no chance to adapt at such a short period of time. That is what the scientists are worried about...rightly so. | @123chargeit  claiming themselves wise, they became as fools | There is a saying "the dose makes the poison". We should be aware and not ignorant, but for we should not be hysterical. One other fact is, that CO2 tend to goes down (where it is being consumed, but also partially emitted again by trees). So the atmosphere is not a static parameter. | How egotistical are humans to believe we can cause the levels of our atmosphere to bend to our will. As if during the last ice age the planet warmed because of all the cars and "fossil fuels" being used. Incredible. These people.</v>
+nice job oil apologist, you really have bought their propaganda and stand tall against the science. | Relatively speaking it is a large increase but as a % of the atmosphere it is still negligible and considering that the biggest explosion of life on earth occured when it was massively (magnitudes) higher. As the speaker points out we are actually at the bottom of the scale in terms of what is required for a healthy planet. Any less and plants can't survive. | No it isn’t | @Shena1580  about 6000 years old | Fun Fact C02 levels during the time of the Dinosaurs was over 5 times higher (over 1500ppm compared to todays roughly 400).  It's due to tectonic plates subducting (going under) on the ocean floor.  As one slips under the other massive amounts of decaying organic matter (mostly from plankton/algae) that has fallen to the floor goes with it, sealing away C02 virtually the rest of time (some comes up during volcanic eruptions but most disappears into the core).  I sometime wonder if the sole purpose of humans in the grand scheme of things was to prevent the early heat death of the planet through the eventual collapse of the greenhouse effect.  There's some irony considering how much effort we are going to prevent something that to the long term success of life on the planet is actually helping. | @123chargeit  Hmm. At what point during the "dinosaur era"? You do know that there were catastrophic climate events that took place during the course of that peroid. They were kind of slow though (tens of thousands of years or much longer) and still managed to kill off a huge % of the life and species on the planet. The rate the climate is changing now is the important bit. The ecosystem have no chance to adapt at such a short period of time. That is what the scientists are worried about...rightly so. | @123chargeit  claiming themselves wise, they became as fools | There is a saying "the dose makes the poison". We should be aware and not ignorant, but for we should not be hysterical. One other fact is, that CO2 tend to goes down (where it is being consumed, but also partially emitted again by trees). So the atmosphere is not a static parameter. | How egotistical are humans to believe we can cause the levels of our atmosphere to bend to our will. As if during the last ice age the planet warmed because of all the cars and "fossil fuels" being used. Incredible. These people. | No it isn't, it's a change of 0.01%. | @richardhall4830  if the concentration of cyanide in you changed by 0.01%, you would die. Even if a number looks tiny it can still have an impact. Right now, we're fine, but if CO2 levels rise too far we could be in trouble. | a decent-sized but irrelevant change | At the beginning of the industrial revolution, carbon levels were around 280 parts per million. Now they are around 406. Photosynthesis begins to fail at around 150. When the dinosaurs roamed this planet, their counterparts were the largest plants in history. Carbon levels were between 4 and 6 thousand parts per million. | The increase has has an effect. It's caused plant life to grow and become greener. | And that is the point. The attempt to destroy the fact that CO2 emissions are the most important reason for climate change by pointing out some people do not know about the numbers is not helping the cause nor changing this fact. Even more, if you consider that this seemingly tiny (absolute) change has such a great impact, it is even more important to consider!
+And yes, you don't need to change to renewables in remote areas, but that is not the point.
+Plus, reading all the comments about how smart this guy is just gives me the creeps about how easily you are all blinded by the way someone argues while totally overlooking the actual science. | You said it yourself. 
+More co2 means more plants. You OFFICIALLY agree with Alex Jones on his climate theories!! More co2 is ideal for us!! Welcome to the side of factual reality, all the people confused above me, only prove it because they're just flabbergasted that, like all Democrat policies, the OPPOSITE of what they propose is the actual best course of action. | @Kaleki935  more co2 doesn’t necessarily mean more plants. If left to their own devices…sure…maybe more co2 means more plants. Meanwhile, rainforests are getting chopped down, urban cities are sprawling, etc. | Actually,  rising CO2 would result in more food for planet. | What I took from that point is, if they want to lower CO2 levels, how low do they want it? do they want it low enough to kill all plant life? not much wiggle room in there | @muchoaustin  yup | ​ @muchoaustin There's a lot of wiggle room. Luckily no one is proposing that we lower CO2 levels so low that plants would die, if we're lucky we might get back to natural levels | I am starting to wonder if global warming is actually good for us | ​ @mcleanF1  
+The planet was warmer not too long ago. Greenland was livable as little as 600 years ago. | @mcleanF1  It is, but of course that has its limits. The worst times for humanity have been when the climate has cooled (The Dark Ages, the Little Ice ages). Cooler temperatures lead to crop failures which lead to famine which lead to disease. Then the climate warms again, and civilizations thrive. | The more that CO2 rises... the more that Plants will produce Oxygen... hence, balancing out the proportions of CO2 to O2. | ​ @johndough8115  That's not how it works. The temperature increase from the CO2 also causes water vapour the condense less, trapping it in our atmosphere. Water vapour is also a GHG.</v>
       </c>
     </row>
     <row r="125">
@@ -2748,10 +2761,10 @@
       </c>
       <c r="E127" t="str" xml:space="preserve">
         <v xml:space="preserve">In 1998 it was 0.033% | ​ @kensmith5694  yeah and that's with massive increases to the amount of vehicles, people, farming, aeroplanes and rocket launches etc since then...... Back in 1998 the global population was 5.98 billion, today it's 7.94 billion and in 1951 it was 2.58 billion, the global population has basically tripled within the last 70 years and yet co2 only went up 0.007%
-It's almost as if more people mean more co2 entering the atmosphere but only by a marginal amount and given time I'm sure the planet will readjust the atmosphere and balance itself back out like it's done numerous times in the past without our help | @Idlepit2  The planet will adjust.  Mankind will have to also.  In the adjustment there will no doubt be wars and famine etc as the areas that could grow crops no longer can.  The human population may well decrease in the result.  Some of it will happen even if we did manage to cut CO2 production but less will.</v>
-      </c>
-    </row>
-    <row r="128" xml:space="preserve">
+It's almost as if more people mean more co2 entering the atmosphere but only by a marginal amount and given time I'm sure the planet will readjust the atmosphere and balance itself back out like it's done numerous times in the past without our help</v>
+      </c>
+    </row>
+    <row r="128">
       <c r="A128" t="str">
         <v>@niamcd6604</v>
       </c>
@@ -2764,34 +2777,25 @@
       <c r="D128">
         <v>316</v>
       </c>
-      <c r="E128" t="str" xml:space="preserve">
-        <v xml:space="preserve">Then do your job, as a citizen. Vett your candidates... Starting with  the boring lower tier ones, school district positions, judges, commissioners, etc. See who is funding their campaign. Find out who is endorsing them. Make sure they're not activists posing as qualified candidates... Check and triple check all QUALIFICATIONS!, if they can't balance a checking account or have strings of failed businesses, that's a red flag. | Then you have to get rid of Democracy, because Democracy is not about skills/competence, it's essentially just a popularity contest, where a bunch of people - who don't nessecarily need to know anything - compete in sweet-talking the public, and political decisions (votes) are done by people who don't have any knowledge on the topic, but ordinary people who feel like because they are citizens they should decide about topics they have no knowledge about, be it about the military, energy, asylum politics etc. As long as politics is about popularity and "who says the most things that make me feel warm and fuzzy inside", you can't achieve max. efficiency. Unfortunately, if you decide to try a political system run by those who are competent, the ordinary citizens will start to feel "opressed" because they don't get to make political decisions. Seems we can't win at this game. | So long beeing politician is an overpayed job... you have people like these. People dont make this job for create the future or being the right for the job..... no only to smile and make money. | @justpat1420  If you pay them less, you just end up with even richer, even lazier politicians who are just in it for the political power. Because that's then who can afford to be an elected official. If you want competent experts, then you need to pay at least vaguely competitive rates to what they can earn in the private sector. | They might be incompetent, but they are also bought and paid for. | Its sad because during the last three years people have proven that they had no clue about health issues, Blood circulates all day long in every part of the body and people try to guess where some fluid will go in the body, People ignore that the air we breath in is different than the air we breath out. CO2 goes 0.04% to 4%, Even the Boss of the WHO is no medical doctor and never was one in his life, he is unable to make a diagnosis nor is he allowed to give you some medication. | It is more about POWER, and control. Read your bible. It gives you the whole story | WHY? 
-Why on earth would anybody make such claim??? 
-Would it no be easier to simply decline payment when you are not satisfied with the result? Is it not what you do on a daily basis, BTW?
-Why do you expect that people whose payment you cannot refuse, do things the way you would be actually willing to pay for?
-WHY would they do thatt, if you cannot decline the payment anyway???
-And btw, how to they KNOW that they are doing the right things with people's money if they have NO FEEDBACK- EVERYBODY must keep on paying them! HOW do they know?? Magical tricks??
-Don't  you understand that this claim is ridiculous and even ludicrous???
-What are you proposing next?
-That we all beg??
-On our knees??.... | That will never happen.  What they need to do is believe the people who DO know, something that Repugnicans refuse to do. | whos supposed to "train" them? you?</v>
+      <c r="E128" t="str">
+        <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>@peterjackson2625</v>
+        <v>@MarktheMole</v>
       </c>
       <c r="B129" t="str">
-        <v>True perspective on CO2 and the electric vehicle myths.</v>
+        <v>What are the names of the four turkeys giving evidence??</v>
       </c>
       <c r="C129" t="str">
         <v>Unknown</v>
       </c>
       <c r="D129">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E129" t="str">
-        <v/>
+        <v>Grumpy, Dopey, Bashful, Sleepy...</v>
       </c>
     </row>
     <row r="130">
@@ -2825,7 +2829,7 @@
         <v>152</v>
       </c>
       <c r="E131" t="str">
-        <v>They'd no nothing to regulate it - that's why we know they'd do a pretty good job. | Its not a class. Mlre like puppet show | Would a kindergartener also not understand the difference between .03 and .04? I think any middle schooler could tell you that's a huge change, not a small one. 33% in fact. | ​ @yokotaashi bro it's not just CO2, there's methane and other such greenhouse gases...all combined is giving the global warming effect...we are trying to reduce 1 component of global warming...all small changes in percentage of all gases adds up... | @yokotaashi  Yes 33% of fek all</v>
+        <v/>
       </c>
     </row>
     <row r="132" xml:space="preserve">
@@ -2849,16 +2853,16 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>@MarktheMole</v>
+        <v>@peterjackson2625</v>
       </c>
       <c r="B133" t="str">
-        <v>What are the names of the four turkeys giving evidence??</v>
+        <v>True perspective on CO2 and the electric vehicle myths.</v>
       </c>
       <c r="C133" t="str">
         <v>Unknown</v>
       </c>
       <c r="D133">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -2878,7 +2882,7 @@
         <v>156</v>
       </c>
       <c r="E134" t="str">
-        <v>Perhaps a case of How to Lie With Statistics? | @professorsogol5824  and where statistics are being misrepresented, those doing the misrepresentation should be called out publicly, investigated, allowed to offer defense, and prosecuted if they’re shown to be acting in bad faith… how many politicians would we already be rid of if this was the norm?! | @professorsogol5824  There's a great picture floating around of Bill Gates promoting some  "What billionaires read" campaign and that book is right at the top of his stack. It's like they think we're all blind fools or are just taunting us at this point. | So the % of CO2 in the "atmosphere" has gone from .028% to .04% in just 2 decades. That's a 43% increase. That's pretty darn significant and should not be trivialized as the gentleman is trying to do. None of these men being questioned is a scientist of any sort I'd guess as any educated scientist could tell you the composition of the air we breath is mostly nitrogen (almost 80%) the rest is mostly oxygen (at 20.8%) the remainder is mainly inert games including argon, neon and yes, CO2. The part I don't kmow with any certainty is how these percentages change as elevation increases. I know the partial pressure decreases for them all, but I don't know if it decreases at the same rate or of this affects the percentages of each gas. It is conceivable that the  percentage of CO2 is different (greater or less) at different altitudes. | @iansutube  Not correct, not in 2 decades. | @iansutube  the further you go up you get more nitrogen, and then when you go up more it’s mostly molecular oxygen</v>
+        <v/>
       </c>
     </row>
     <row r="135">
@@ -2932,10 +2936,10 @@
         <v>95</v>
       </c>
       <c r="E137" t="str">
-        <v>He did his home work. | rednecks, smarter than city folk now xD 2023 is wonderful</v>
-      </c>
-    </row>
-    <row r="138">
+        <v/>
+      </c>
+    </row>
+    <row r="138" xml:space="preserve">
       <c r="A138" t="str">
         <v>@margaretbedwell3211</v>
       </c>
@@ -2948,8 +2952,9 @@
       <c r="D138">
         <v>103</v>
       </c>
-      <c r="E138" t="str">
-        <v/>
+      <c r="E138" t="str" xml:space="preserve">
+        <v xml:space="preserve">Well, once they have us all forced into electric cars, they'll just turn off our chargers and tell us to walk or ride bikes. | @eljefeamericano  America's greatest threat, exercise. | @xSaltix_32  I will happily do one push-up, or one sit-up, for... one cheeseburger. | @eljefeamericano  yeah. thats whats going to happen. | What's wrong with you? You can't ask those pertinent questions. Lol | That's the point. Then you'll pay more for it. | First, I agree with the sentiment of your post. That said, batteries won't go in landfills. There are already multiple, very rapidly growing companies (I have worked with them) that have created recycling methods that take waste lithium-ion batteries from cars and break them back down to their original elements to be reused in the manufacturing process. That piece will not be a problem. How the hell we will charge the batteries in the near term, I have no clue. | @aronkerr  Thank you for your information.  That was the one thing that really concerned me.  And like you, how will everybody get charged up.  As I am 84, I probably won't be around to see how this problem will be solved. | Poison dead batteries that cost close to 30 thousand dollars to replace and poisonous to landfills or anywhere. | You don’t bury the dead batteries, there are hydrometallurgic processes to recover the raw materials. | Do you not try to keep the engine of your car cool? What if we added 10 degrees to it, how cool could your engine be? They ask this because the hotter the material are, the harder is to transmit electricity since it increases resistance, which makes it hotter and you have a runaway effect were on the same load, the infrastructure is several times hotter than it would be. | The heat waves are mad worse by oil. If we never used oil, you wouldn't be so hot in the first place | ​ @ceoatcrystalsoft4942  
+No, dude, oil is not causing rising temps - and EVs will need more oil than gas vehicles, actually. | ​@CEO At Crystalsoft  Not entirely true, but I am definitely tired of having "the hottest summer on record" almost every fucking year. | ​ @ceoatcrystalsoft4942  no</v>
       </c>
     </row>
     <row r="139">
@@ -2966,7 +2971,7 @@
         <v>100</v>
       </c>
       <c r="E139" t="str">
-        <v/>
+        <v>The vampire overlords clearly found a different source of power. | @RedYDG   Yes, it's called money. | Powerful, yes. Too bad that all too many people think that might makes right.</v>
       </c>
     </row>
     <row r="140">
@@ -3003,7 +3008,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" xml:space="preserve">
+    <row r="142">
       <c r="A142" t="str">
         <v>@BruceDeitrickPrice</v>
       </c>
@@ -3016,15 +3021,11 @@
       <c r="D142">
         <v>51</v>
       </c>
-      <c r="E142" t="str" xml:space="preserve">
-        <v xml:space="preserve">Planting trees is the perfect solution to climate change.  But not because trees will store CO2 but rather trees will stabilize humidity which in turn will moderate climate.  
-I bet that the 1.1 billion hectares of deforestation since 1900 has a bigger role in climate change than the +100 ppm increase in CO2 concentration. | What about those who want to plant trees vs those who want to deforest (Rain forests disappearing)?  Who has the most power and resources? | Doubling the amount of CO2 in the atmosphere increases global temperature by 3 C.
-Tree planting is one of the methods in use to reduce the amount of CO2 which continues to be added to the atmosphere.
-Mann's 1998 paper was evaluated by the National Science Foundation which presented its findings in a 160 page report y to congress. It found Mann's results to be valid.
-Since then numerous studies have confirmed Mann's results and extended the time period back, the most recent to 24,000 years ago. | I hear lots and lots and lots of people talking about planting trees and some people are doing it.  No amount of trees we could practically plant will take up the amount of CO2 we produce from burning fossil fuels.  The numbers show that many other things take up CO2 a lot faster and even those things would not keep up. | @kensmith5694  If you were correct, why is the amount of atmospheric CO2 not showing any substantial rise over the last 20 years?  A shortage of volcanos spewing CO2 into the atmosphere?</v>
-      </c>
-    </row>
-    <row r="143">
+      <c r="E142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143" xml:space="preserve">
       <c r="A143" t="str">
         <v>@seitenwind7940</v>
       </c>
@@ -3037,8 +3038,11 @@
       <c r="D143">
         <v>421</v>
       </c>
-      <c r="E143" t="str">
-        <v/>
+      <c r="E143" t="str" xml:space="preserve">
+        <v xml:space="preserve">And how they followed each other with their answers. The worst example of group think. | It is taught to kids in primary school, science subject,right?? No, not now ??? | These were unelected government bureaucrats, (people running the day to day operations of our government, hired for life!!) not politicians, who could not name the percentage of CO2. It is incredible considering these bureaucrats are supposedly concerned with CO2!!!!!!!!!!!!!!!!!! | Moreover, not one of them had the decency to just refrain from answering since they weren't sure. | Then why don't you tell us all what the important measure of atmospheric C02 is, seeing as you know so much. | That's the problem with politics their employment is so far disconnected from their performance it causes a perversion in all of their priorities. | just because they didn't answer correctly doesn't mean they don't know the answer.  ppl call them incompetent, but what if they're just flat out lying? | Don't need to know a specific number to know what it does to the world.
+A lot of bad things come in very small percentages | @TheWhitePianoKeyProductions A little ignorance can do a lot of harm too. | @TheWhitePianoKeyProductions  Yep.  What percent of your body weight of cyanide will kill  you?  (it's a small number) | They use Co2 in industrial refrigeration, i call them hillbillie con artists. Co2 has one of the lowest specific heat index's
+It's 0.04 %  or  400 parts of 1,000,000  400 ppm, im not even sure it's that high. | @will-ob7pr  Water has a high specific heat that means it takes a lot of radiant heat from the sun to even warm it slightly. The oceans as as a giant heat sink to distribute heat from the equatorial region both north and south to the higher latitudes. Without the oceans the earth would have the same climate as the moon +250 deg F on the dayside to -250 deg F on the nightside. | @will-ob7pr  Pray explain how "they" used Co2 in refrigeration. | ​ @will-ob7pr  I seen a man on YouTube when he was having a lecture the reading was 1,700 ppm. They allow 4 to 5 thousand on a submarine even more than that in a spaceship, 400 is nothing. | Baseline at 0.03%, stated that falling to 0.02% would be catastrophic but that rising to 0.04% is a tiny number we shouldn't worry about.  _x000d_
+DO YOU TRUST A FARMER TO UNDERSTAND CLIMATE SCIENCE IF THEY DON'T UNDERSTAND THE FLAWS IN THEIR OWN ARGUMENT? | ​@zampha2065  he said at .02% plant life could start to die.  That is bc plants absorb co2 to make oxygen. Its a necessary chemical from them. So if there's not as much available then naturally plant life will begin to diminish. | @zampha2065  Nothing wrong with that arguement. Below 0.02 plants stop thriving and above a certain level they grow more and faster, that's why FARMERS add CO2 to greenhouse spaces. | @zampha2065  There is a minimum amount of nutrients that your organism need to take just to survive. Less, would be catastrophic for your health. You should find out that amount and not eat a tiny bit more than that. Or it would be also equally catastrophic. | Because the internet does not know the answer. | @Rockercaruthonyoutube  i looked it up and it was the first result lol.. | @Rockercaruthonyoutube  Don't talk nonsense.</v>
       </c>
     </row>
     <row r="144">
@@ -3106,8 +3110,7 @@
         <v>176</v>
       </c>
       <c r="E147" t="str" xml:space="preserve">
-        <v xml:space="preserve">@paulrendell8797  i think i should start worying when our dams break and citys flood, which coincidently allready happened... And will happen more often, and yes we shouldnt stop climate change, no sane person should be asking for that, we should slow it down though | Why is it a 'great question' and why would it be important for a non-scientist to know the answer? | @MrYahboo  To educate the people voting on the policies they apparently don't really understand. | @viopsadmin  I take it you believe you're educated on the subject then, correct?
-Which is great news - you should be able to explain to me why this figure is particularly relevant. | It isn't a great question actually. It's meant to downplay the effect CO2 has on climate change. No scientist is going to deny to deny these levels. If you look at any climate change graph, you'll usually find CO2 listed in ppm. Parts per million. And it is publicly displayed at a little over 400 ppm, up to 418 as of 3 days ago. Up over 100 ppm since the pre-industrial era, and the highest the planet has seen in nearly a million years. | @mikoi7472  He said the answer. Next he mentioned what was recorded at one point in time. Then he said the lowest possible number to supply CO2 for plant life. There is nothing misleading in his statement. | ​ @mikoi7472  nope, it's not meant to downplay anything. It's meant to show that people considered experts on climate don't know even the basic things about a field they're supposed to be experts in | @mikoi7472  - So, how many SUVs and coal fire power plants were around a million years ago? | ​​ @mikoi7472  more co2 = more plant life, a more green earth. A more green earth = less co2. Beautiful how Earth works isn't it? | ​ @charlespancamo9771  more co2 is indeed more green life, but also higher water levels (because also those have changed throughout history) and would probably mean less space for humans, and probably less humans if they didnt move before a critical storm | @charlespancamo9771  "more co2 = more plant life"
+        <v xml:space="preserve">@paulrendell8797  i think i should start worying when our dams break and citys flood, which coincidently allready happened... And will happen more often, and yes we shouldnt stop climate change, no sane person should be asking for that, we should slow it down though | Why is it a 'great question' and why would it be important for a non-scientist to know the answer? | @MrYahboo  To educate the people voting on the policies they apparently don't really understand. | It isn't a great question actually. It's meant to downplay the effect CO2 has on climate change. No scientist is going to deny to deny these levels. If you look at any climate change graph, you'll usually find CO2 listed in ppm. Parts per million. And it is publicly displayed at a little over 400 ppm, up to 418 as of 3 days ago. Up over 100 ppm since the pre-industrial era, and the highest the planet has seen in nearly a million years. | @mikoi7472  He said the answer. Next he mentioned what was recorded at one point in time. Then he said the lowest possible number to supply CO2 for plant life. There is nothing misleading in his statement. | ​ @mikoi7472  nope, it's not meant to downplay anything. It's meant to show that people considered experts on climate don't know even the basic things about a field they're supposed to be experts in | @mikoi7472  - So, how many SUVs and coal fire power plants were around a million years ago? | ​​ @mikoi7472  more co2 = more plant life, a more green earth. A more green earth = less co2. Beautiful how Earth works isn't it? | ​ @charlespancamo9771  more co2 is indeed more green life, but also higher water levels (because also those have changed throughout history) and would probably mean less space for humans, and probably less humans if they didnt move before a critical storm | @charlespancamo9771  "more co2 = more plant life"
 No it doesn't. Firstly, this is a faulty premise in the first place. Plants can thrive in the short term and suffer in the long term. Increased CO2 does indeed lead to a short phase of increased growth in plants. But this is offset by the toll it takes on the soil. The plants effectively mine the soil for minerals and nutrients to continue growing and as such, rapid growth leads to a nutrient poor soil. Not only that, but the rapid increase in plant growth also itself leads to increased CO2 due to increased microbial activity.
 You can find this in a paper titled "A trade-off between plant and soil carbon storage under elevated CO2" in the journal nature. It's a meta analysis on 108 other experiments.
 But go ahead and push your climate change denialism some more. I've been arguing against people like you for over a decade now and it's still just as easy. | ​ @larsrademakers6070  Keep drinking the kool-aid | ​ @mikoi7472 yo are a bot created to cause unrest and to be an antagonist in the comments sections | @bunchofgrapesorafig  even if he is, his response is valid so I kindly suggest you deal with that instead of making completely unfounded and unverifiable claims.
@@ -3129,7 +3132,7 @@
         <v>133</v>
       </c>
       <c r="E148" t="str">
-        <v>Obviously, .04% of all gumbo is consumed in Tokyo | They fly private jets have yachts. One yacht corporation emits 10x more CO2 than all cars in Europe together, but no one talks about that | ​ @vernkidd2539  In what world do yachts produce that much CO2? They're very bad on a per capita basis but they are not that awful. | Gumbo and Tokyo were  important to that story why? | @KaiserBlade  cuz it was an unforgrtable experience overall... It was in an apartment that was like $8k a month rent too. So the whole conversation was super surreal and crazy yet the CO2 stuck with me just as much as the 25 story view of the Tokyo Tower right out the window. | was it shrimp or chicken gumbo? | @JohnBrown-vn2qw  shrimp | The gumbo smelled like troll to me. | @keisreeman  he said it was shrimp | So working for a fossil fuel company makes him a neutral arbiter? | But isn’t the point that it doesn’t matter what most people think or believe, it’s the scientists that work on this that we should be listening to?  When the IPCC says that CO2 levels are getting dangerously high, it’s not subjective.  Whether its getting from 1% to 2% or 10% to 20% doesn’t matter as much as what the increase itself will lead to because it’s in relative terms. | @write2pras84  95% of emitted CO2 is by nature. Less than 1% of the 5% emitted by humans is from cars. What are we talking about here? | It frustrates me when people who know what happens if you leave the engine running in a closed garage, dismiss the danger on a larger scale, because of what the people who work for the oil companies say in public. Despite what they say in private. When exposed. | @atticuswalker8970  That’s carbon monoxide that kills you in a closed garage, not CO2. You know nothing.</v>
+        <v/>
       </c>
     </row>
     <row r="149">
@@ -3180,7 +3183,7 @@
         <v>28</v>
       </c>
       <c r="E151" t="str">
-        <v>Ecology 101... Every textbook... | Rather than now saying Co2 is 0.04 of our atmosphere -- we used to say "400 parts per million" (ppm) | @garyviehe9365  Both are correct, except you made a minor error in your statement. CO2 is not .04 of our atmosphere. It is .04 % of our atmosphere which means the actual amount is .0004. In other words, a tiny amount that poses no threat to our environment whatsoever, but as we saw in this video, even highly educated leaders have no idea. If CO2 gets much lower than that, plants, which “breathe,” CO2 and give us oxygen in exchange, won’t grow. We needs more CO2, not less.</v>
+        <v/>
       </c>
     </row>
     <row r="152">
@@ -3231,7 +3234,7 @@
         <v>53</v>
       </c>
       <c r="E154" t="str">
-        <v/>
+        <v>I wish I could give this a million "thumbs up!"</v>
       </c>
     </row>
     <row r="155">
@@ -3265,7 +3268,7 @@
         <v>80</v>
       </c>
       <c r="E156" t="str">
-        <v>People in cities think farmers are unnecessary. Food comes from supermarkets right? | @alanjm1234  So True Alan!  So true. | Thank you for explaining that. It sure feels like they want this country to suffer. | Im a heavy truck mechanic of 20+ years. I mostly stay busy repairing aftertreament systems these days. New trucks, able to pull freight, but neutered to 5mph cause the muffler is doing what it’s supposed to do. | Mahindra | Tier 4 is a regulation of NOX , not CO2 - if you don't understand that, you are in the wrong discussion.  Those pollutants have nothing to do with CO2, or why 'cleaner' engines doesn't mean more efficient. | Bagels up from 59 cents to 99 cents in my supermarket in 12 months.</v>
+        <v/>
       </c>
     </row>
     <row r="157">
@@ -3540,7 +3543,7 @@
         <v/>
       </c>
     </row>
-    <row r="173" xml:space="preserve">
+    <row r="173">
       <c r="A173" t="str">
         <v>@davidhfranz</v>
       </c>
@@ -3553,13 +3556,8 @@
       <c r="D173">
         <v>35</v>
       </c>
-      <c r="E173" t="str" xml:space="preserve">
-        <v xml:space="preserve">Nitrogen is 78% of the troposphere.
-20.78% is oxygen.
-.04% is carbon dioxide.
-There are several other trace gases in the atmosphere.
-Methane .00015%
-Argon 1%. | @TheErik249  My reference shows Methane as 2PPM and Neon at 18PPM | actually it is just less than 78% Nitrogen almost 21% Oxygen and 0.9% Argon with CO2 at 0.042%.    Methane isn't even .0001%  All other gases less than that. | Just recently the environuts were screeching about too much nitrogen in the atmosphere. What dumbasses!! Imagine what would happen if oxygen levels were increased. Any fires would be more energetic and destructive and too high a level of oxygen is actually toxic. I kinda like things just the way they are. | ​ @killerdoxen  But oxygen is good for animals, so doubling it would make it double as good for animals | Uh, no. Not even. Addressing local atmosphere at sea level because that's the benchmark for how heat escapes. | Maybe the word. Not what you think</v>
+      <c r="E173" t="str">
+        <v/>
       </c>
     </row>
     <row r="174">
@@ -3614,7 +3612,7 @@
         <v/>
       </c>
     </row>
-    <row r="177">
+    <row r="177" xml:space="preserve">
       <c r="A177" t="str">
         <v>@atraxian5881</v>
       </c>
@@ -3627,8 +3625,12 @@
       <c r="D177">
         <v>75</v>
       </c>
-      <c r="E177" t="str">
-        <v/>
+      <c r="E177" t="str" xml:space="preserve">
+        <v xml:space="preserve">oxygen levels have a direct relationship to co2 levels. | .04% CO2 in the air we breath | Well, first of all, your numbers are not quite correct: It is about 78% (78.08%) nitrogen but almost 21% oxygen (20.95%). Then your statement does not make any sense: CO2 is one of the greenhouse gases: Our global temperatures are about 32 degrees Celsius (c. 58 degrees Fahrenheit) higher because of them, making the planet (on average) liveable even though they make up how many percent of the atmosphere? | The average temperature is 15°C. | ...yes because the atmosphere is breathable it can't be so hot that ice cannot exist on the surface of earth.
+You just said "you can breathe in ovens, so 400 degrees isn't a problem" | @reyalsregnava  you completely missed my point.
+It was about how ridiculous the numbers the politicians were saying.
+So grossly exaggerated.
+Is a change of 0.01% CO2 impactful? Yes, probably, but that wasn't my point.</v>
       </c>
     </row>
     <row r="178">
@@ -3645,7 +3647,7 @@
         <v>54</v>
       </c>
       <c r="E178" t="str">
-        <v>1XM_MX1   ;   And the Correct Answers we , will not get from any Democrat .</v>
+        <v/>
       </c>
     </row>
     <row r="179">
@@ -3662,7 +3664,7 @@
         <v>32</v>
       </c>
       <c r="E179" t="str">
-        <v>Polar bears went to the Antarctic for that period. | Reference please.</v>
+        <v/>
       </c>
     </row>
     <row r="180">
@@ -3732,7 +3734,7 @@
         <v>61</v>
       </c>
       <c r="E183" t="str">
-        <v>I want preface this statement by saying I am not on board with the climate wackos at all. That said, any modern vehicle with a catalytic converter(anything after 1975) actually does emit CO2 and almost no CO when the vehicle is functioning properly. Don't take my word for it though, look up how a catalytic converter functions. | Perfectly summed up. The goal is 15minute eco city with big brother AI | You hit the nail on the head. It’s all about the rich getting richer! | Utter bunkum. I just had my car smog tested for annual registration in California. CO and oxides of nitrogen were tiny fractions of the emissions. | Finally someone else figuring this CO2 and CO  difference. I've been telling people this for years | Older cars before catalytic converters had this problem with carbon monoxide levels in the exhaust. That's why it used be a common warning to never keep the windows completely closed if the car would be sitting idling for any length of time. Since carbon monoxide was odorless, people could pass out without any warning and it would lead to death if it went on too long. Modern cars, for the most part, don't have this problem if the engine and exhaust system are maintained. | Once again, all I was ever looking for was CO, there was never a concern for a high CO2 level.</v>
+        <v/>
       </c>
     </row>
     <row r="184">
@@ -3768,8 +3770,16 @@
       <c r="D185">
         <v>100</v>
       </c>
-      <c r="E185" t="str">
-        <v/>
+      <c r="E185" t="str" xml:space="preserve">
+        <v xml:space="preserve">Remember this? If the earths atmosphere were a 100 story building...
+If we put all of our resources into the effort...
+We could not alter the linoleum on the first floor. 
+The founder of the weather channel said it, 42,000 physicists endorsed it. | @ronferderer9088  " 42,000 physicists endorsed it"
+whatever they are endorsing they do bc they want grants and not to get kicked out.
+it's survival .
+would you put you're name on something you didn't read?
+would you put you're name on something you had no choice if you wanted to keep your job? | I suspect that most politicians neither know what PPM stands for or how to convert it into percentage or any useful understanding of how little 420 PPM really is. | A student once asked his/her guidance counselor: "I have no talent with my hands. I can't build, diagnose or fix anything such as building a room, fixing an electrical or plumbing problem. I am not good at math, science or any STEM discipline. I cannot write or speak cogently. What should I do to become successful? "
+The counselor replied: "The answer is as plain as the nose of your Islamic face: "Go into politics. It's an avocation which requires no useful talent, only 'useful idiots'. | Calibrate the amount in the atmosphere?!?!? Experts like the people who want mass depop? | Fortunately for us, the planet already has a functioning biological ecosystem that thrives on co2 and is capable of handling any significant increase. Even more fortunately is that with that increase, the ecosystem's capacity for handling even more increases so there's an effective check to runaway carbon emissions. Biological systems that are already functioning well enough don't need our help, they just need to be left alone to do their job without interference. | @salemfoster1709  based on what exactly? You do know that evolution takes GENERATIONS to make any significant changes right? In the span of around 270 years we've raised it by 50%. Mind explaining why earth somehow maintained this level of CO2 for thousands of years but somehow after industrial revolution, earth failed to maintain it anymore?</v>
       </c>
     </row>
     <row r="186">
@@ -3871,7 +3881,7 @@
         <v>29</v>
       </c>
       <c r="E191" t="str">
-        <v>They are expected to make laws for every field of expertise in existence. That means a lot of areas of their knowledge are going to be lacking because they don't get to spend much time on all of them.  We should have them go through a short education on a topic directly prior to making a law for it, but we don't. Instead, we get special interests like this guy bringing up their ignorance as if that makes the point when it doesn't. Yeah so what, he came prepared with a statistic. That doesn't mean he's an authority on the subject and they should all just take his word for it. As we all know, the authorities on the subject tend to take an opinion opposing his. His statistic is not going to be persuasive. He said the amount is .04% of the total atmosphere. And a few decades ago it was .03%. So the concentration of it is up 33% from what it was a few decades ago. And right after he explained that plants would die if it was below .02%. So clearly, even though the number is small, we are still able to impact it because a small absolute change still makes a big difference. The relative change is the important part. So what if its 50% to 66.66% or .03% to .04%. The result is we are making an impact. | The point of this is they are doing things like shipping aggregate in rather than dig, crush, screen and transport for infrastructure projects etc because their mandates prohibit it being done locally and they have the gall to think its a positive impact on emissions when all it does is move the emissions source but it makes them feel good about hamstringing the local economy and job market while serving their ego's as environmental philanthropists and their "look at me, look what I did'. Whether or not you subscribe to climate change fear mongering or what ever its not even remotely what the proport it to be as it probably increases emissions being that the industrial practices of the areas they are sourcing it from probably have few if any interests let alone the simple issue of modern construction equipment which is lower emissions by evolution and efficiency so their ego's are focused on local emissions not global emissions that they are enabling and that is called hypocrisy at their constituents expense !</v>
+        <v/>
       </c>
     </row>
     <row r="192">
@@ -3973,10 +3983,10 @@
         <v>192</v>
       </c>
       <c r="E197" t="str">
-        <v>Can tell he takes his job seriously and standing up for his constituents | He is also very humble as many intelligent people are. I’ve often marvelled at how the stupid seem to be the ones that want to tell everyone else what to do. No doubt, they’re noting that he’s not as expensively groomed as they are and therefore shouldn’t be taken seriously. | Good to get the message out. Keep their guard down. | He is working to emphasize one number, the fact that CO2 is but a small portion of the atmosphere while deliberately ignoring another number: that the increase in the amount of CO2 in the atmosphere is enormous.  The amount of CO2 in the atmosphere is now some 34% greater than in 1950 (10 years before Representative LaMalfa was born) | @Professor Sogol  he is emphasizing that the people making decisions about transportation and regulating emissions have no effing clue wtf they are talking about. | @professorsogol5824  Huh, it does not matter how much “more” it is than the “1950s”. How much exists NOW?????? Funny you didn’t mention that 1950s number</v>
-      </c>
-    </row>
-    <row r="198" xml:space="preserve">
+        <v>Can tell he takes his job seriously and standing up for his constituents | He is also very humble as many intelligent people are. I’ve often marvelled at how the stupid seem to be the ones that want to tell everyone else what to do. No doubt, they’re noting that he’s not as expensively groomed as they are and therefore shouldn’t be taken seriously. | Good to get the message out. Keep their guard down. | He is working to emphasize one number, the fact that CO2 is but a small portion of the atmosphere while deliberately ignoring another number: that the increase in the amount of CO2 in the atmosphere is enormous.  The amount of CO2 in the atmosphere is now some 34% greater than in 1950 (10 years before Representative LaMalfa was born) | @Professor Sogol  he is emphasizing that the people making decisions about transportation and regulating emissions have no effing clue wtf they are talking about. | @NeuKrofta  they don’t need to know anything about it, that’s what scientists are for. | @silentterrorhawk  if they are going to legislate and regulate it's part of their job. | @NeuKrofta  it’s there job to legislate after taking advise from experts. No one can be an expert in every subject. | @silentterrorhawk  cope harder | @NeuKrofta  speak English | @professorsogol5824  Huh, it does not matter how much “more” it is than the “1950s”. How much exists NOW?????? Funny you didn’t mention that 1950s number</v>
+      </c>
+    </row>
+    <row r="198">
       <c r="A198" t="str">
         <v>@alwyzDTF</v>
       </c>
@@ -3989,12 +3999,8 @@
       <c r="D198">
         <v>116</v>
       </c>
-      <c r="E198" t="str" xml:space="preserve">
-        <v xml:space="preserve">The only thing he exposed is his inability to do basic mathematics. He stated that the baseline pre-industrial CO2 levels were 0.03%, that we’ve already exceeded that by 33%, and that if we’d gone 33% the other way then life on Earth would already be extinct.
-Seriously, the guy should have stuck to farming and left critical thinking to the experts. | ​ @markgearing   Where in this video is that claim stated clearly? Seems like you are either wrong or making shit up after re watching this video with you comment in mind. | @alwyzDTF  - 1:33 LaMalfa: “Point zero four percent. It’s gone up from point zero three in the last couple of decades.”
-1:43 LaMalfa: “If we get below point zero two, plant life starts dying off.”
-It’s stated clearly if you’re prepared to to do some very simple mathematics and critical thinking. An increase from 0.03 to 0.04 is a 33% increase, the difference of 0.01 being a third, or approximately 33%, of 0.03. Similarly, a decrease from 0.03 to 0.02 is a 33% decrease for the same reason. Finally, if plant life dies we all die.
-I paraphrased LaMalfa, so you won’t find my exact words in his mouth, but I haven’t changed any of the facts he stated. If I were going for accuracy, though, I could have used the actual figures of 421ppm CO2 in 2022, up from 280ppm pre-industrial, which is a 50% (approx) increase, much more than LaMalfa’s 33%. LaMalfa rounded them off to favour his argument and I was feeling generous, especially since he also rounded the 150ppm where photosynthesis stops to 0.02% which is actually a 50% (approx) reduction from pre-industrial levels, not 33%. | @markgearing  That makes sense, thanks for clearing it up. My original comment still stands though. I think yours applies as well. Seems we need to get all of these lying criminals out of the office.</v>
+      <c r="E198" t="str">
+        <v/>
       </c>
     </row>
     <row r="199">
@@ -4014,7 +4020,7 @@
         <v/>
       </c>
     </row>
-    <row r="200" xml:space="preserve">
+    <row r="200">
       <c r="A200" t="str">
         <v>@deniswauchope3788</v>
       </c>
@@ -4027,13 +4033,11 @@
       <c r="D200">
         <v>187</v>
       </c>
-      <c r="E200" t="str" xml:space="preserve">
-        <v xml:space="preserve">If you noticed, the shift has begun on blaming the animal production.  Too much water is used.   Water is not destroyed when used in food production.  It evaporates or goes in the rivers to be used again. | Chech out the Younger Dryas period.... | Just plant more trees. | That what i learned in earth science in school. | I say that to my kids all the time!! They come home from being indoctrinated (SCHOOL) and I put them right! | It's hilarious seeing the CO2 truck behind the woke campus refilling the cafeteria and science bldg tanks.
-Not to mention at the greenhouses at the horticultural annex | @JoeandAngie  is it still co2 when it leaves the body ? | This is nonsense. We normalize seasonal effects using fourier transforms/wavelet analysis/etc as well as other cyclic effects that we're pretty certain of and still observe an abnormal rise in CO2. Now CO2 is yes, involved in chemical processes that we depend on, but like any other chemical, it can participate in other processes, and it's these processes that we are concerned about. This isn't just a CO2 problem either, nor a methane problem, but rather all sorts of pollutants that cause issues yet have varying degrees of scientific attention because our politicians and idea people refuse to listen to math people.
-Nuclear radiation is perfectly natural and is involved in the vital procedure of evolution. So why not line up and get irradiated by Chernobyl? It's only natural - your body needs it to evolve. What are you waiting for? | @ruedelta  Guy says "Nonsense." Proceeds to equate cancer to evolution | @ruedelta  and that's why we should produce more natural gas plants since natural gas burns clean. | @CPreacher40  No such thing. They burn cleaner than coal and oil but that's about it. Nuclear is the way to go, with the renewables for supplemental parts, and natural gas as load following and rural applications. | @ruedelta  and the nuclear waste lol?</v>
-      </c>
-    </row>
-    <row r="201" xml:space="preserve">
+      <c r="E200" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="201">
       <c r="A201" t="str">
         <v>@Astrosisphere</v>
       </c>
@@ -4046,10 +4050,8 @@
       <c r="D201">
         <v>100</v>
       </c>
-      <c r="E201" t="str" xml:space="preserve">
-        <v xml:space="preserve">It’s the AGEN-DA! | ​ @cornstar1253  That may apply generally. With view to others, like changes of climate, you already fine when your hypthesis is in line with with what your model says - again and again and again. | @Leon Löwenstädter  models are still garbage in, garbage out. You can't use linear analysis to measure an integrated system then extrapolate the data, Which is what is going on here. There are models that suggest that CO2 has a net cooling effect in the atmosphere as well, But that theory doesn't get funding so you've likely never seen those models. | It's even explained in several films. E.g. in Prometheus the planet has an atmosphere with 3% of CO2 and it's lethal to be without mask | Imagine when they find out the atmosphere has 78% of Nitrogen | If it goes below .02 he said plants die | I think I am pretty aware of the CO2 hoax… I thought a tenth of 1% and I was off by more than twice… these industry mouthpieces are fools no wonder we as a society are so lost… we all need to start praying ️ | @supernaturalagriculture6261  It's not a "hoax", you just lack even the most basic understanding of the greenhouse effect. The surface of the earth absorbs energy from the sun and then re-emits that energy in the infrared. Nitrogen, oxygen, and argon, more than 99.9% of the atmosphere, are transparent to these specific infrared wavelengths. As far as the greenhouse effect is concerned, they don't exist. CO2 on the other hand, is opaque. In the context of this discussion, CO2 is more like 40% of the atmosphere than .04. | ​ @jacobnebel7282  Seeing as we're supposedly coming out of a cool period, and that the earth's climate varies without us - I think it's time to stop complaining.
-This is the first time we've actually measured it, and seeing as most all of our greenhouse effect comes from water vapor, and higher CO2 means more respiration/more plant growth...which in turn will provide the crops for a higher population...I don't see what you're complaining about.
-You are the carbon they want to neutralize. | ​ @piterpraker3399  Wow, I am amazed of what you don't know. Just one fact: Looking on ice cores, you can find out both the temperature and CO2 content for minimum the past 50.000 years. There has been no period of time when CO2 content and global temperature went up that quickly. | I knew it was around 400 parts in a million, I just couldn't convert it to percent on the spot. :D</v>
+      <c r="E201" t="str">
+        <v>It’s the AGEN-DA! | ​ @cornstar1253  That may apply generally. With view to others, like changes of climate, you already fine when your hypthesis is in line with with what your model says - again and again and again. | @Leon Löwenstädter  models are still garbage in, garbage out. You can't use linear analysis to measure an integrated system then extrapolate the data, Which is what is going on here. There are models that suggest that CO2 has a net cooling effect in the atmosphere as well, But that theory doesn't get funding so you've likely never seen those models. | It's even explained in several films. E.g. in Prometheus the planet has an atmosphere with 3% of CO2 and it's lethal to be without mask | Imagine when they find out the atmosphere has 78% of Nitrogen | If it goes below .02 he said plants die | I think I am pretty aware of the CO2 hoax… I thought a tenth of 1% and I was off by more than twice… these industry mouthpieces are fools no wonder we as a society are so lost… we all need to start praying ️ | @supernaturalagriculture6261  It's not a "hoax", you just lack even the most basic understanding of the greenhouse effect. The surface of the earth absorbs energy from the sun and then re-emits that energy in the infrared. Nitrogen, oxygen, and argon, more than 99.9% of the atmosphere, are transparent to these specific infrared wavelengths. As far as the greenhouse effect is concerned, they don't exist. CO2 on the other hand, is opaque. In the context of this discussion, CO2 is more like 40% of the atmosphere than .04. | I knew it was around 400 parts in a million, I just couldn't convert it to percent on the spot. :D</v>
       </c>
     </row>
     <row r="202">
@@ -4137,7 +4139,7 @@
         <v/>
       </c>
     </row>
-    <row r="207">
+    <row r="207" xml:space="preserve">
       <c r="A207" t="str">
         <v>@henrytomas</v>
       </c>
@@ -4150,8 +4152,10 @@
       <c r="D207">
         <v>39</v>
       </c>
-      <c r="E207" t="str">
-        <v/>
+      <c r="E207" t="str" xml:space="preserve">
+        <v xml:space="preserve">Oxygen burns nitrogen burns , co2 does not burn. It's also iced in fire extinguishers. 
+Huge amounts of oil and gas reserves or rare earth minerals for batteries ? The word rare might be a good hint.
+Lots of coal and oil in  Antartica according the U.S. Navy.</v>
       </c>
     </row>
     <row r="208">
@@ -4321,7 +4325,7 @@
         <v>3</v>
       </c>
       <c r="E217" t="str">
-        <v>LaMalfa has no clue what ppm means. Ask his what a 50% increase in an atmospheric gas means for the earth, watch his squirm.</v>
+        <v/>
       </c>
     </row>
     <row r="218">
@@ -4338,7 +4342,7 @@
         <v>33</v>
       </c>
       <c r="E218" t="str">
-        <v>Common sense is often quite silly. This is a great example. 0.04% sounds like nothing, but that just means human contributions make a bigger difference. He’s making the exact opposite point of what he thinks. | @jonathanfields4ever  Actually the CO2 proportion of the atmosphere is .004. What's more this level is at the saturation point where more CO2 does not create any further greenhouse warming effect.</v>
+        <v>Common sense is often quite silly. This is a great example. 0.04% sounds like nothing, but that just means human contributions make a bigger difference. He’s making the exact opposite point of what he thinks. | @jonathanfields4ever  Actually the CO2 proportion of the atmosphere is .004. What's more this level is at the saturation point where more CO2 does not create any further greenhouse warming effect. | @donaldclifford5763  Wrong. | @ Not wrong. Science.</v>
       </c>
     </row>
     <row r="219">
@@ -4358,7 +4362,7 @@
         <v/>
       </c>
     </row>
-    <row r="220">
+    <row r="220" xml:space="preserve">
       <c r="A220" t="str">
         <v>@trytellingthetruth.2068</v>
       </c>
@@ -4371,8 +4375,9 @@
       <c r="D220">
         <v>70</v>
       </c>
-      <c r="E220" t="str">
-        <v/>
+      <c r="E220" t="str" xml:space="preserve">
+        <v xml:space="preserve">Along those lines, if CO2 levels rise too much can't we simply plant more trees and fix the issue within a couple decades? These grifters just won't suggest it because there's not much money to be made. | If only we could stop cutting trees down! | ​ @marcheezy.  Nice thought but mankind is doing the opposite and continuing to deforest vast areas. Both to cater for the demand for more living space and for pasture for the meat industry and the soy farms it requires. | @marcheezy.  
+Streets in London, especially out in the suburbs, used to be lined with trees. Unfortunately, most have been removed by local Councils over time. These tree's did a great job of dealing with CO2 emissions from cars. | 97% of the oxygen on the planet comes from the ocean.... | ​ @jrhayes6901  Photosynthesis in algae is the same as the photosynthesis in plants on land. Most of that algae is around the surface of the water not at the bottom of the ocean. | @sonniepronounceds-au-ni9287  what are you talking about. It’s nothing to do with algae. Rather H2O is 2 hydrogen and 1 Oxygen. Boil the water or evaporates in weather cycle. Boom hydrogen gas and oxygen. | ​@SorryTruth  water doesn't evaporate into hydrogen and oxygen, it evaporates into water vapor aka still h2o | @Waluigi164  Dude, that was the most moronic thing you could have ever said in response to my comment. That's not how water molecules work at all. You can't just tear water molecules apart into their basic elements by boiling it. The reason people say that most of our breathable oxygen comes from the ocean is because of the plant algae that live around the water surface. It doesn't mean it actually comes from the water itself. | @sonniepronounceds-au-ni9287  so when you drink water what do you think happens. Lmao you think it becomes vapor or does it not get split an used by the cells too. | @sonniepronounceds-au-ni9287  dare insult my intelligence. Well you only fool yourself bud | @coreyscolaro288  “Four common techniques for the removal of dissolved oxygen from water have been examined: boiling at 1 atm, boiling under reduced pressure, purging with N(2) and sonication under reduced pressure. After treatment, the residual oxygen in solution was analysed by the Winkler method.” | @jrhayes6901  Where are you getting that number? According to the National Ocean Service, only 50% of oxygen comes from the ocean, and most of which is consumed by aquatic organisms. Humans aren’t getting that oxygen.</v>
       </c>
     </row>
     <row r="221">
@@ -4423,7 +4428,7 @@
         <v>18</v>
       </c>
       <c r="E223" t="str">
-        <v>Agreed. They will all go back, and tell everyone that will listen, that its 4%! | @andycap6786 | It's about 20 times higher than the daily interest rate bank of America offers on your savings account. Maybe they understand that | Many commenters here don't either. The .04 is expressed as a percent. That makes it just .004 as a proportion of the atmosphere.</v>
+        <v/>
       </c>
     </row>
     <row r="224" xml:space="preserve">
@@ -4442,7 +4447,7 @@
       <c r="E224" t="str" xml:space="preserve">
         <v xml:space="preserve">I wouldn't be too judgmental about that. I had to look it up to. And even if I knew it was below 1 %, I was still way off. The real bummer here is, that LaMalfa looked it up beforehand, and then used their ignorance as evidence, that there isn't a problem, when there clearly is. | @Misophist  What problem? No temp increase in 50 years of CO2 sales and paranoia comes out as a rather lame frame for causing deep fear in severeal generations...it's a money and power grab friend. | @Misophist  The entire point of the climate change movement over the past few years or so involves cutting down on "carbon emissions" though.
 How in the world is carbon emissions such an important focus when the experts don't even have data relevant to said carbon emissions? If this were so important, they should have data on where we're at, what our target should be, and what the effects would entail.
-What if these carbon emissions only lowered the .04% CO2 down to .038% by their target year of 2035? That would have been 25-30 years spent doing activities that, if their goal was to lower overall CO2 in the atmosphere, had a high opportunity cost for almost no gain whatsoever (assuming that CO2 reduction is, in fact, a good thing). | Yeah that information is one click away. Funny how only the person who asked knew. Also funny how that question is totally irrelevant. The concentration of co2 the atmosphere is relevant which is measured in ppm not the percentage. The quantity of gases that does not affect the global warming is totally irrelevant. but the guy just wanted to put the number into a bigger perspective so that the number looks smaller. Is like saying the earth does not matter. It’s only 0.0000000000001% of the galaxy. | @mariusmihai1292  Doh...please show some proof for your belief in climate change. This subtle word play conveys no more than an ad homonym. | @paulrevere47  proof or beliefs? i can believe people don't know today elementary physics. You know what a solar is? 1. the increased average temperature on earth/year. 2. the average of 800.000 years concentration of co2 in the atmosphere  increase by 70% in the last 50 years. The concentration of Co2 is directly proportional with the average temperature on earth/year. | @mariusmihai1292  800,000 year data juxtaposed on how many BILLION? Naw, if the BILLIONS were not presently measured in profits to CO2 traders, you might have a case. Who paid for that 800k/yr data you cite?</v>
+What if these carbon emissions only lowered the .04% CO2 down to .038% by their target year of 2035? That would have been 25-30 years spent doing activities that, if their goal was to lower overall CO2 in the atmosphere, had a high opportunity cost for almost no gain whatsoever (assuming that CO2 reduction is, in fact, a good thing). | Yeah that information is one click away. Funny how only the person who asked knew. Also funny how that question is totally irrelevant. The concentration of co2 the atmosphere is relevant which is measured in ppm not the percentage. The quantity of gases that does not affect the global warming is totally irrelevant. but the guy just wanted to put the number into a bigger perspective so that the number looks smaller. Is like saying the earth does not matter. It’s only 0.0000000000001% of the galaxy. | @mariusmihai1292  Doh...please show some proof for your belief in climate change. This subtle word play conveys no more than an ad homonym.</v>
       </c>
     </row>
     <row r="225">
@@ -4459,7 +4464,7 @@
         <v>1</v>
       </c>
       <c r="E225" t="str">
-        <v/>
+        <v>These aren't climate specialists.</v>
       </c>
     </row>
     <row r="226">
@@ -4548,11 +4553,8 @@
       <c r="D230">
         <v>73</v>
       </c>
-      <c r="E230" t="str" xml:space="preserve">
-        <v xml:space="preserve">And an atomic bomb is smaller than a car, which one is potentially more destructive? | So what about CO?  Carbon Monoxide.  Should we be ok if it is say....  0.01%? | @vessbakalov8958  pretty sure there isn't that much CO, it is a very unstable molecule, oxydises to CO2 fast | In the last percent it would be 4%. | Remainder is Politicians' fart. | If you want to put it that way then:
-Chlorinated water is recommended to have a chlorine level of 4 ppm, a 50% increase in cl levels to 6ppm is considered dangerous and potentially toxic. How big is 6ppm you ask? 0.0006% of the mass/volume of the water you're drinking from. | 1% other gases and only 0,04% CO2 ! | That is correct. Itˋs also the case that the content of CO2 in the atmosphere in past 100 years increased by about 40%. | @leonlowenstadter9223  How much of that increase was caused by nature as opposed to human activity? | @y2knoproblem  As far as I know the vast majority was caused by human activity. It's easy to understand: The natural CO2 changes are changes within a "closed" system as no CO2 was added. Over-simplyfied it like that: CO2 was stored in plants, the plants die and decay, CO2 is released and stored in another plant. Since like 100 years, we dug for coal, oil and gas and burnt it. This released unbelievable quantities of CO2 which are now in the atmosphere. I think by adding up the quantities you can get a pretty reasonable number on how much CO2 was emitted by human activity. | I had one cent...then I had two cents, that's an increase of 100 percent....oxygen and nitrogen burn well. Does co2 ? | @leonlowenstadter9223  Well: The Meyers Lexikon (1896) says 0.04 %. In my Knaurs Lexikon (1936) it says 0.03 - 0.06 % ... And TODAY we have the CO² content still with ~0,04 %. I cannot see any increase here.
-WHAT climate-damage do you want to fight with CO² taxes?
-It is rather about the impoverishment of the masses and NOT about any climate protection... | @powerfarmer  Well, I don't know where they got their information from, but I guess this details hasn't been of that much importance then and to have a general idea of what gases our atmosphere consists of, it's fine to say 0.04%. However until about 1950 the historic content was measured with ice cores and since 1950 it's measured on several stations around the world. The stations may not be precise, but as all stations show an significant inrease, the tendency seems to be right. | @powerfarmer  4 ppm of chlorine in your water is considered safe by the CDC whereas 6 ppm is considered dangerous and potentially toxic. 4 ppm is just 0.0004% of the water's weight/volume | ​ @leonlowenstadter9223  And what was the CO2 content in the atmosphere in the 1930's which cooked North America to a crisp? Hmm. | Sure, but the increase of co2 as an effect is still in the margin of error of water vapour released by oceans. | And 95% co2 from car fumes. | @Rockercaruthonyoutube  false, nearly third of the co2 comes from cement production and industrial transportation, civil transportation adds only a fraction to the sum | @Rockercaruthonyoutube  Sourse please…</v>
+      <c r="E230" t="str">
+        <v/>
       </c>
     </row>
     <row r="231">
@@ -4586,7 +4588,7 @@
         <v>13</v>
       </c>
       <c r="E232" t="str">
-        <v>No, control is the end game. Money is small part of it.. | Your number is out of date.  Today it is over 400PPM.</v>
+        <v/>
       </c>
     </row>
     <row r="233">
@@ -4621,7 +4623,15 @@
       </c>
       <c r="E234" t="str" xml:space="preserve">
         <v xml:space="preserve">Because knowing It don't help to sell the narrative. | You have properly heard the ppm (parts per million) amount which is just a finer grained "percentage". It really doesn't matter the exact amount though since without studying the subject you don't know how sensitive it is to change. | Because if they told them.  They would think that co2 wouldn’t have its effect because it’s concentration is low.  Which is a terrible way of thinking. | I learned it in school since grade 6.....  Does your country curriculum intend to hide this fact? | Interesting comnent. Most people have no idea of the numbers involved nor the geological variability of CO2 concentrations. Only 300 million years ago CO2 was at 1500ppm, a number inconceivable in the next few million years. | ​ @carleddison7479  pre industrial times it was at 288ppm, so not that much higher than is actually the lowest requirement for plants to live, and is now around 420ppm.
-So 300Million to go from 1500ppm to 288, then &lt;200 years to go back up to 420. So on average 250k years to drop 100ppm (I know it wasn't that linear) and now &lt; 200 year to go back up 100 ppm. Doesn't sound  like a huge change, but relatively speaking it is a pretty decent amount. If that increase continues, it'll be back at 1500ppm in 2.4k years, not a few million years that you suggest would be inconceivable. A number that would potentially kill off most of life on the planet, because life needs a lot longer than that to adapt and change. Not saying that it what will happen, but 1500ppm is definately not inconceivable within the next couple of Millennia. | ​@carleddison7479 The oxygen level was also at 30%, it really isn't comparable to today's climate. This fact just makes some people feel like they have enough information to discount the arguments for climate change, when they really don't. | @BobBobissen   Very sensitive, like in the models, right?! | You have internet access. If you would be interested you could look this up within a minute. If you are surprised now this only means that never in your life you bothered to spend a minute to check the number. The only thing that "kept that out of your mindset" was your lack of interest.
+So 300Million to go from 1500ppm to 288, then &lt;200 years to go back up to 420. So on average 250k years to drop 100ppm (I know it wasn't that linear) and now &lt; 200 year to go back up 100 ppm. Doesn't sound  like a huge change, but relatively speaking it is a pretty decent amount. If that increase continues, it'll be back at 1500ppm in 2.4k years, not a few million years that you suggest would be inconceivable. A number that would potentially kill off most of life on the planet, because life needs a lot longer than that to adapt and change. Not saying that it what will happen, but 1500ppm is definately not inconceivable within the next couple of Millennia. | ​ @muzzan1448 CO2 levels have been as low as 185 ppm during the coldest part of glaciation, and plants survived. | @muzzan1448  there are many good things that stop your catastrophic scenario from happening.
+1. Plant grow faster when co2 concentration is higher, up to 2 or 3 times. So, when co2 is higher, the rate absorbed by plant is also higher, as well as our food productivity.
+2. Oil and gas are limited resources and are running out. No matter what you do it won't increase that much.
+3. More co2  , plankton grow faster, shellfish grow faster, rate of conversion from CO2 to carbonate is also higher, leading to faster reduction of CO2
+There are all lie that benefits those green companies trillion of dollar in my opinion , what a waste of human resources. | @Google_ai_told_me_my_iq_is155  
+1. Plants grow faster with more CO2, if they are in the right conditions e.g. their temperature is within the correct range, rainfall somes at the right time and there is enough sunlight at the right time. That requires a stable climate.
+2. There is enough oil and gas left in the ground to create 3.5 trillion tons of CO2, which is seven times more than we can afford to emit if we want to have only moderate damage from climate change. If we burned all that, it would leave large areas of the planet uninhabitable, completely disrupt agriculture and submerge coastal cities.
+3. Plankton (specifically oxygen producing diatoms) and shellfish rely on stable pH of seawater to form their shells. Greater CO2 absorbtion into seawater raises acidity, meaning they can't form shells as easily. They also thrive in colder waters. In short, they die by their trillions.
+I think you're looking for liars in the wrong place. | ​@carleddison7479 The oxygen level was also at 30%, it really isn't comparable to today's climate. This fact just makes some people feel like they have enough information to discount the arguments for climate change, when they really don't. | You have internet access. If you would be interested you could look this up within a minute. If you are surprised now this only means that never in your life you bothered to spend a minute to check the number. The only thing that "kept that out of your mindset" was your lack of interest.
 But to your defense, the absolute value is not essential to understand what is going on with carbon emissions and climate. The quantity of greenhouse gases (CO2 and others) that has been in the air in preindustrial times was sufficient to warm our planet by 33 degrees Celsius. Greenhouse gases saved us and life on Earth from freezing to death. So greenhouse gases have an enormous effect. And now we pump more and more geenhouse gases into the atmosphere and it is no surprise at all that the warming effect gets stronger. This is what scientist tell us since many decades. Many did not want to believe this, even more people just did not care at all, but now we can see it ourselves, e.g. when visiting shrinking glaciers all over the planet. | @justanotherguy2824 melting glaciers is not a good thingn</v>
       </c>
     </row>
@@ -4770,7 +4780,7 @@
         <v/>
       </c>
     </row>
-    <row r="243">
+    <row r="243" xml:space="preserve">
       <c r="A243" t="str">
         <v>@tomdallas3690</v>
       </c>
@@ -4783,8 +4793,9 @@
       <c r="D243">
         <v>24</v>
       </c>
-      <c r="E243" t="str">
-        <v/>
+      <c r="E243" t="str" xml:space="preserve">
+        <v xml:space="preserve">Well said, and the older I get  (60 now)  the more obvious this becomes. 
+I wish it wasn't so, it seems to be getting worse.</v>
       </c>
     </row>
     <row r="244">
@@ -4835,7 +4846,7 @@
         <v>22</v>
       </c>
       <c r="E246" t="str">
-        <v/>
+        <v>Were you in grade school a very long time ago? I could be wrong, but I'd be surprised if that knowledge is allowed in school today. | @brianpaasch2665  it feels like a long time ago | @brianpaasch2665  what happened?? They contorting this fact too? | That's what I learned as well! | Most of the 'everything else' is Argon. | @RyeOnHam  yep. I was just going from memory.</v>
       </c>
     </row>
     <row r="247">
@@ -4889,7 +4900,7 @@
         <v/>
       </c>
     </row>
-    <row r="250">
+    <row r="250" xml:space="preserve">
       <c r="A250" t="str">
         <v>@johnhamaker8441</v>
       </c>
@@ -4902,8 +4913,10 @@
       <c r="D250">
         <v>35</v>
       </c>
-      <c r="E250" t="str">
-        <v>Pollution is our way of life! | @CountingStars333  Life on Earth would not exist without CO2.    6CO2 + 6H2O + light energy = C6H12O6 + 6O2.   Recognize that equation??  CO2 is not pollution.</v>
+      <c r="E250" t="str" xml:space="preserve">
+        <v xml:space="preserve">Pollution is our way of life! | @CountingStars333  Life on Earth would not exist without CO2.    6CO2 + 6H2O + light energy = C6H12O6 + 6O2.   Recognize that equation??  CO2 is not pollution. | @Krusty-kl5ej  
+No-one is saying we don't need CO2.  The fact is that life as we know it cannot exist if the percentage increases too quickly and too much. The rate of increase in CO2 is unprecedented. It's the highest level in 14 million years, and it's a fact that the three main mass extinctions were accompanied by high CO2 levels. If you don't think the modern rise in CO2 is dangerous because .02% is a negligable amount, how do you square that with LaMalfa's assertion that a drop of 33% would mean no plants could grow. why is one figure  disastrous, but the other figure somehow not equally a problem? | @Krusty-kl5ej  Look up the greenhouse effect and then the enhanced greenhouse effect. They are different things. | @bengreen171  1) That is NOT a fact. You're talking about a change of 0.01 or 0.02% increase in a trace gas  2)  CO2 used to be well over 1 per cent, even as high as 10 percent (from proxy estimates) for most of the Earth;s history and well into the Paleozoic/Mesozoic coupled with record periods of evolutionary expansion with gross increase fluctuations well above amounts of change seen at the outset of the Industrial Age.  The issue with the plants is a totally different problem of scale.  We need 18% atmospheric oxygen to function normally.  Drop that to 15% and you become lethargic and/or pass out.   Plants can still live above 160 ppm, but most biologists tell you immediately if you drop below that level, they are asphyxiated.  Conversely, most plants see optimum growth at 500 to 1000 ppm. | @Krusty-kl5ej  
+lol. The Paleozoic - famous for its plantlife...</v>
       </c>
     </row>
     <row r="251">
@@ -4937,7 +4950,7 @@
         <v>31</v>
       </c>
       <c r="E252" t="str">
-        <v>Don't forget what a divisive issue this is......all part of the strategy | @elisabethpearl9790  yep..almost a 'Cult'..deliberately..</v>
+        <v/>
       </c>
     </row>
     <row r="253">
@@ -5163,7 +5176,7 @@
         <v>Wrong. Water vapor by a big margin.</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" xml:space="preserve">
       <c r="A266" t="str">
         <v>@yakbreeder</v>
       </c>
@@ -5176,8 +5189,15 @@
       <c r="D266">
         <v>54</v>
       </c>
-      <c r="E266" t="str">
-        <v/>
+      <c r="E266" t="str" xml:space="preserve">
+        <v xml:space="preserve">More importantly, what fraction of the ~33% increase is man made? | @grantcivyt  A 33% increase in feck all is feck all.  CO2 concentration was 2000 - 5000 ppm when most plants evolved.  300 to 400ppm is insignificant, especially as CO2's radiative forcing in inversely logarithmic.  Once above 100ppm it's effect is negligible,  water vapour and cloud cover percentages much more important, and very likely these vary with multi-decadal and centennial solar / ocean cycles. | ​ @grantcivyt  probably quite big since we cut a lot of jungles few hundreds year back, however that is not a case anymore since we keep planting new trees (yes I know forest is not exactly a same thing but for co2 it nearly well is). Also we could just make bio diesel since we aren't going to introduce anything new to atmosphere | @jamessan3404  Biodiesel is bad for humanity though. There are other types of methods. 
+Biodiesel takes precious land and resources from food production that we definitely need. 
+Is a big waste to have farmers growing plants for biodiesel. | @1ofZero  better than mining coal until we figure out how to use something renewable. Btw somehow collecting methane from farms and waste would be good idea too | @1ofZero  Bio fuel from Hemp would be the best realistic plan of action. Rotating the crops, hemp perfectly prepares he soil for all other crops, and hemp seeds are pretty much the most nutritious naturally growing food source on the planet. Plus, hemp should be used to make paper instead of trees, but I've never once heard Greta or these modern greens calling for this change. Cotton production is more toxic than producing fabrics from hemp, and cotton is by far an inferior fabric than hemp fabric. Hemp is nature's gift that could fix sooooooo many of the world's problems. Only problem is tha it grows everywhere, easily, so there isn't much money in it. THST is why it has been illegal for the best part of a century, NOT because our governments care so much about our health that they will send us to prison for possessing hemp flowers. | ​ @jamessan3404  aint algae the biggest co2 consumer? | @jamessan3404  No it isn't. I'm from Lancashire in the north of England. They closed the coal mines in the area despite there being coal seams still there. Instead Drax power station takes logs from prime forests in Canada (which utilise CO2 to produce oxygen) and which are shipped across the ocean to the power station, they are then chipped and used in the power station to provide electricity. This is less efficient than using coal, and you have deforested an area of Canada which were absorbing CO2, and shipped it across an ocean, wasting resources and creating more environmental damage than using the God given resources that were on your doorstep. Not only this but they claimed subsidies from the EU as being environmentally friendly!
+ The coal mines were closed by the conservative prime minister in the 1980's, destroying the communities and causing mass unemployment to those who would generally have voted labour, and which rather suggests a political basis for any decision. | @JM-dm3qk  well we can mine coal and return atmosphere to time of dinosaurs but bio diesel is closed cycle in nature. Also deforestation only happens if you have too little wood. It is supposed to be reforested after cutting down trees and then you cut different place another year. By cycling that you can keep forest at same level always. Cutting trees is dangerous if it is motivated by urbanisation or ( a bit less but still bad) when it's due to agriculture | @jamessan3404 that’s a thing already | @grantcivyt  Increase from a couple decades ago? Atmospheric concentrations in 1820 and 1940 were higher than today. | Seriously, though, Rich Wilson just asked me how can we know we are running out of fossil fuels when "no one knows where they come from".  I thought he was joking, but apparently not.  Anyone want to take this one? | @MICHAEL-vy3ch  every one knows fossil fuels come from dead dinosaurs, come on man! I kid, I kid.
+It did come across as a serious comment though. | none of it. | I’ve enjoyed reading these comments. It’s CLEAR that you people know more about this topic than those panelists do.&amp;I appreciate the fact that it speaks well of our current generation that we are staying informed and are no longer taking for granted that the “experts” actually ‘know’ what to do and/or how to do it. (This is probably one of the biggest unintended gifts of the “pandemic”-more people starting to think for themselves. ). KUDOS TO ALL | After reading the responses, I was curious so I looked the numbers up.  Of the 0.04% of CO2 in the atmosphere, 3% of that is man made.  That means that around 0.0012% of CO2 is man made and of that, 0.000396% of total CO2 represents the increase over the last 60 years (since measurements of total CO2 started to be taken at Mauna Loa) caused by man.  That is a 0.0000066% increase each year caused by man.  At the current rate, in one thousand years we will have raised the total amount of CO2 in the atmosphere from 0.04% to around 0.05%.  
+Not an insignificant amount, given that CO2 is technically poisonous to humans and creates a greenhouse warming effect on the planet with disastrous results, but not an immediate threat either given that we will run out of fossil fuels long before that. | @MICHAEL-vy3ch  I did the math roughly 10 years ago and was blown away, hence my comment.
+We've all heard sea levels would rise "X" feet in "X" years. What they don't tell us is that it'll take thousands of years to get there. Also easily solved by simple math.
+Once you do the math (most people don't/won't) the gloom and doom walks right out the door.</v>
       </c>
     </row>
     <row r="267">
@@ -5216,6 +5236,11 @@
 Do also note that all that trapped carbon in fossil-fuels used to be free, our planet was booming of life way more in the past than it is now, as you can read about how they 3x the CO2 value in greenhouses to boost plant growth. | @harry.4.2.0  yes the atmospheric concentration of CO2 being minuscule doesn’t change the fact that it has a huge impact. The physical evidence speaks for itself. Human activity has increased CO2 by 50% over the past two centuries. We didn’t cause global warming but we have artificially accelerated it past the breaking point. We will all continue to argue over the details while we suffocate and starve. | @harry.4.2.0  " atmospheric CO2 content has a significant impact on climate"   says who? | @codetech5598  most credible research | @harry.4.2.0   Nowhere have I seen a repeatable laboratory bench experiment showing the temperature effect of adding increasing amounts of CO2 at atmospheric concentrations under controlled conditions to an air sample. 
 Can you for example tell me what difference incremental increases of CO2 (say 0.01%) make by reference to an experiment, not computer model calculations?  What might the effect of adding water vapour at various concentrations be?
 If you know of such an experiment,  I would be interested to know the details. | @gam1471  doesn't matter anyway since the Earth isn't an enclosed box like all experiments to measure the greenhouse effect have to be. Since you can't actually measure the greenhouse effect in an open system like the Earth is,that is also connected to the wider universe heh. 
+Another real example is Venus and Mars both have ~96% CO2 in their atmosphere ones is extremely hot and the other cold, the difference being that Venus has ~90 ATM pressure compared to Earth(and a similar mass of atmosphere  ~90 times ) and closer to the Sun while Mars is ~0.1% pressure of Earth and alot less in mass(smaller planet) and further from the Sun. So what causes the temps on planet is related to their mass of atmosphere  and distance from the Sun, its one of the reasons Titan is cold, to its 3 times Earth pressure but alot less mass and is too far away from the sun even tho its atmosphere is mainly methane a 'potent greenhouse gas', by alarmist logic Venus, Mars and Titan should all be friggin hot lol! | @gam1471  you can’t fit a planet on a lab bench. If you want an experiment demonstrating the climate effects of raising CO2 levels you’re in luck: we’re living on it. | It's worth noting that the presence of water vapour affects the atmospheric concentration of CO2. 
+CO2 measurements are taken on dry samples because the amount of water vapour in air varies from around 0.2 to 4%. | And yet atmospheric CO2 content has a signficant impact on climate regardless of the fact it's a small part of the atmosphere. We are not the same. | ​ @harry.4.2.0  You should ask yourself what is the ideal concentration for vegetation? | @harry.4.2.0  So how significant? You can find an interesting study online regarding this called "infrared saturation of carbon-dioxide", basically showing how you have to keep doubling CO2 to increase the average temperature by 0.5 degrees. 
+Do also note that all that trapped carbon in fossil-fuels used to be free, our planet was booming of life way more in the past than it is now, as you can read about how they 3x the CO2 value in greenhouses to boost plant growth. | @harry.4.2.0  yes the atmospheric concentration of CO2 being minuscule doesn’t change the fact that it has a huge impact. The physical evidence speaks for itself. Human activity has increased CO2 by 50% over the past two centuries. We didn’t cause global warming but we have artificially accelerated it past the breaking point. We will all continue to argue over the details while we suffocate and starve. | @harry.4.2.0  " atmospheric CO2 content has a significant impact on climate"   says who? | @codetech5598  most credible research | @harry.4.2.0   Nowhere have I seen a repeatable laboratory bench experiment showing the temperature effect of adding increasing amounts of CO2 at atmospheric concentrations under controlled conditions to an air sample. 
+Can you for example tell me what difference incremental increases of CO2 (say 0.01%) make by reference to an experiment, not computer model calculations?  What might the effect of adding water vapour at various concentrations be?
+If you know of such an experiment,  I would be interested to know the details. | @gam1471  doesn't matter anyway since the Earth isn't an enclosed box like all experiments to measure the greenhouse effect have to be. Since you can't actually measure the greenhouse effect in an open system like the Earth is,that is also connected to the wider universe heh. 
 Another real example is Venus and Mars both have ~96% CO2 in their atmosphere ones is extremely hot and the other cold, the difference being that Venus has ~90 ATM pressure compared to Earth(and a similar mass of atmosphere  ~90 times ) and closer to the Sun while Mars is ~0.1% pressure of Earth and alot less in mass(smaller planet) and further from the Sun. So what causes the temps on planet is related to their mass of atmosphere  and distance from the Sun, its one of the reasons Titan is cold, to its 3 times Earth pressure but alot less mass and is too far away from the sun even tho its atmosphere is mainly methane a 'potent greenhouse gas', by alarmist logic Venus, Mars and Titan should all be friggin hot lol! | @gam1471  you can’t fit a planet on a lab bench. If you want an experiment demonstrating the climate effects of raising CO2 levels you’re in luck: we’re living on it.</v>
       </c>
     </row>
@@ -5250,7 +5275,7 @@
         <v>27</v>
       </c>
       <c r="E270" t="str">
-        <v>And putting things into a bigger perspective to look smaller. Like saying it’s ok to nuke the whole earth. The earth means 0.0000000000006% of the galaxy.</v>
+        <v/>
       </c>
     </row>
     <row r="271">
@@ -5321,7 +5346,7 @@
         <v/>
       </c>
     </row>
-    <row r="275" xml:space="preserve">
+    <row r="275">
       <c r="A275" t="str">
         <v>@tygrn</v>
       </c>
@@ -5334,9 +5359,8 @@
       <c r="D275">
         <v>18</v>
       </c>
-      <c r="E275" t="str" xml:space="preserve">
-        <v xml:space="preserve">As a farmer who sees that the supposed rise of CO2 has loosely correlated with better crop yields, would the reduction of CO2 see the uptick of mass starvation? I guess these clowns don't realize they use CO2 generators in greenhouse plant production. 
-I wish they'd just say what they really mean... | @livestock9722  As a farmer myself who can't see CO2 because it's an invisible gas, I ask, what do they really mean? | @jonahmoran3751  whatcha sayin there? | @tygrn  oh shit read it wrong | Ice cores show it's been as low as 185 ppm. | My Colliers Encyclopaedia of 1970 gives the percentage of CO2 in the atmosphere as 0.037% which gives an increase of 0.003% in 50 years! | The moral of he story you cannot control Gods planet just like you can’t control earth quakes or Volcanos</v>
+      <c r="E275" t="str">
+        <v/>
       </c>
     </row>
     <row r="276">
@@ -5407,7 +5431,7 @@
         <v>And the children mining it...</v>
       </c>
     </row>
-    <row r="280" xml:space="preserve">
+    <row r="280">
       <c r="A280" t="str">
         <v>@sa3270</v>
       </c>
@@ -5420,14 +5444,8 @@
       <c r="D280">
         <v>39</v>
       </c>
-      <c r="E280" t="str" xml:space="preserve">
-        <v xml:space="preserve">If an illegal who has a 6th grade education and cannot speak the language gets hired preferentially to you, then you need to re-evaluate your life. | @janbaer3241 Because they are a lot cheaper. 
-We had the same issue here in Germany 20 years ago. 
-The gouvernment decided to implement a minimum salary- now losing your job because of cheap foreign workers is rare | @janbaer3241  
-I just noticed your comment. It’s racist. | No, slave | With the foreseeable changes in climate more and more people will have to leave their places because they can't grow food any more. | Illegal immigration is not a main priority issue at all. the economy is tho | @twenty99  
-Yeahhh illegal immigration is a factor to our declining economy so… | @dianem6951  a very tiny one &amp; it’s a crutch to push ideologies that are harmful at the bottom line to those that aren’t American born. | @dianem6951  name me the top 10 largest contributing factors to our economy based on fact &amp; numbers not political bias &amp; I’ll take what you say with more than a grain of salt | @twenty99  
-What political bias? It seems you have one. | @dianem6951  what bias would that be since yk so much? I bet you’d have 0 clue I was on the right bc you made an assumption based off 1 single topic of immigration, as a political ideology, not a human rights topic. YOU have the political bias | @twenty99  
-You started the political bias thing. I didn’t. Go back and look. It was you. | @dianem6951   all I said was to state numbers &amp; facts not political bias. I didn’t accuse anybody of having one I said to bring facts not involving political bias &amp; I was then accused of having a political bias for trying to keep it out of the convo. you never brought numbers or facts, you just accused me of having a political bias. lmao you dug yourself into a hole here | @dianem6951  you’ve completely waltzed around the facts of the convo &amp; re directed it by focusing on the least important part of my reply  classic “I don’t really know what I’m talking ab” behavior</v>
+      <c r="E280" t="str">
+        <v/>
       </c>
     </row>
     <row r="281">
@@ -5531,7 +5549,7 @@
         <v>25</v>
       </c>
       <c r="E286" t="str">
-        <v>Gas cars are already “computerized”. | @brkbtjunkie  Not to the extent of modern electric cars, which are smart and can be controlled remotely. If you think this wouldn’t happen, boy do I have bad news for you.</v>
+        <v/>
       </c>
     </row>
     <row r="287">
@@ -5739,7 +5757,7 @@
         <v/>
       </c>
     </row>
-    <row r="299" xml:space="preserve">
+    <row r="299">
       <c r="A299" t="str">
         <v>@jaysonrees738</v>
       </c>
@@ -5752,9 +5770,8 @@
       <c r="D299">
         <v>27</v>
       </c>
-      <c r="E299" t="str" xml:space="preserve">
-        <v xml:space="preserve">The denialist trope of pointing out the % of atmospheric CO2 as though this somehow renders it insignificant, with no explanation as to why, comes directly from paying lobbyists and paid politicians (like Doug LaMalfa), which is ironic, given your comment. | @MrYahboo  You clearly ignored my point entirely. I was stating that these are people who don't even care enough to learn about the things they regulate. Your focus is completely on how important the questions are. By the way, he did go somewhere with his questions, but that has nothing to do with what I said. | ​ @MrYahboo  our sun affects the climate more than humans. always has and always will. people are so worried about plant food in the atmosphere they forgot the true arbiter of life is our sun, and our magnetic field strength is exponentially decreasing as the poles make their way around our planet. this not only explains the more frequent extreme weather events, but also the ozone hole above the Arctic and the strange migration patterns that leave populations in ruin. if we were to be hit by another Carrington Event it would be an absolute disaster. not only that, but ice core samples show these polar flip excursion events cause ungodly amounts of precipitation, mess up the entire flow of ocean currents, and wreck populations. from 1860 to 2000 the magnetic field lost 10% of it's strength. from 2000 to now, it's lost likely more than 5% and it is still speeding up. Gothenburg, laschamp, mono lake, lake mungo, these events happen every 12 and 6 thousand years, and all signs point that this is going to happen again. our ancestors talk about events like these but nobody takes them seriously, they're just stories. I believe these cyclical disaster events are caused by our solar systems round trip through the galaxy and encountering a galactic current sheet. this seems much more likely and threatening than co2 melting glaciers. the entirety of climate science revolves around the dollar, anything with that much government backing and misleading propaganda and fear mongering is bs, if you can't see it sorry. they want carbon taxes, meat reduction, energy and internet limits, limits on what and how you drive, limits on fertilizers and God knows what else all in order to stop a menace that has yet to be seen. meanwhile, an ESA director mentions a polar flip is inevitable and he's fired a week later how funny. did you know the CIA classified the Adam and Eve story by Chan Thomas in the 60s? what would the point of that be? is it a coincidence this was done a little over a decade after the US military sent 5,000 men to the antarctic where they established ice core drilling? and another thing, why is the focus always on western nations for these green initiatives? India and the whole of southeast Asia are the main polluters, yet nobody does a goddamn thing about it, they just have trash rivers. oh I know why because you can't extort guilt and money out of them so we just let them wallow in filth while complaining about car exhaust and recycling paper. it's a fucking joke and it makes me laugh when people talk about a greener future because it's simply not possible when half the world is still trying to industrialize and the other half is actively trying to destroy itself in order to become equally poor. | Why do you think it's important to know the answer to this question?
-Is it also important to know what year Karl Marx wrote The Communist Manifesto to have an opinion on Communism?</v>
+      <c r="E299" t="str">
+        <v/>
       </c>
     </row>
     <row r="300" xml:space="preserve">
@@ -5840,7 +5857,7 @@
         <v>33</v>
       </c>
       <c r="E304" t="str">
-        <v>Plants use CO2 for photosynthesis | You write what I think. Although the panelist maybe clueless, the guy is either ignoring facts on purpose or because he didn't understands them. | @leonlowenstadter9223 hearing his point, and knowing American politics, it is on purpose | @leonlowenstadter9223  I've stopped trying to figure out who's ignorant and who's lying.</v>
+        <v/>
       </c>
     </row>
     <row r="305">
@@ -5874,7 +5891,7 @@
         <v>24</v>
       </c>
       <c r="E306" t="str">
-        <v>Anything less than 1% is a trace gas... Earth's atmosphere consists of 78 percent nitrogen, 21 percent oxygen, 0.93 percent Argon, 0.04 percent carbon dioxide as well as additional trace amounts of neon, helium, methane, krypton, ozone and hydrogen, as well as water vapor, which varies from ~0 to 4 percent.</v>
+        <v/>
       </c>
     </row>
     <row r="307">
@@ -6049,9 +6066,8 @@
       <c r="D316">
         <v>32</v>
       </c>
-      <c r="E316" t="str" xml:space="preserve">
-        <v xml:space="preserve">I just could not buy a generator from a co that couldn't bother taking the 'generic generator' out of the cookie cutter ads | All that technology, and no will to do.
-What has the US come to. A country stuck in the 80s. | Solar panels? | Because Republicans | You know the carbon footprint for electric is almost as bad as fossil right?</v>
+      <c r="E316" t="str">
+        <v/>
       </c>
     </row>
     <row r="317">
@@ -6291,7 +6307,7 @@
         <v>14</v>
       </c>
       <c r="E330" t="str">
-        <v/>
+        <v>0.0415% of the atmosphere is CO2, ie One in every 8,000 other gaseous atmospheric molecules. So plants have to breathe in a lot of air molecules before it can photosynthesize the one CO2 molecule.   In the process it loses many water molecules via transpiration from the open leaf stomata. | By doubling the CO2 percentage to 0.0830 ppm by using fossil fuels the higher by doubling the CO2 levels means plants double their rate of carbohydrate of metabolism, for the same amount of water lost in transpiration, thus enabling plants to flourish in more arid areas more efficiency say by reducing their number of stomata / sq inch. | ​ @patricksharp1063  Your figures are way off, unfortunately. | Fun fact: the 0.04% was allready mentioned in an encyclopedia from 1898, it has never changed since than. | @DantesDarkside  it was around 0.03% in 1900. 0.027% a few centuries prior. We have plenty of data on that. | Nope lol. The atmosphere is mostly nitrogen, about 70%, and oxygen makes up most of the remaining 30%, with trace gases like CO2 and argon sharing a single percentage point | Give?? Where do we 'give'?</v>
       </c>
     </row>
     <row r="331">
@@ -6360,7 +6376,7 @@
         <v>9</v>
       </c>
       <c r="E334" t="str">
-        <v>CO2 is a MINOR greenhouse gas thats effect does NOT increase linearly with its concentration.  As its concentration rises its greenhouse effect becomes proportionally less.  I.e doubling the concentration does not double its greenhouse effect. | CO2 is NOT a thermostat for the Globe. Where do you get your information?</v>
+        <v/>
       </c>
     </row>
     <row r="335" xml:space="preserve">
@@ -6383,7 +6399,7 @@
         <v>11</v>
       </c>
       <c r="E335" t="str">
-        <v/>
+        <v>CO2 is actually an important part of the atmosphere for life to exist. Plants need CO2 to grow, without plants no animals and no humans. CO2 also plays an important part in regulating the temperature of the planet, we'd be really cold (think ice age movies) without it. However the important part is in moderation, too much CO2 can be just as dangerous as not enough. The planet tends to be pretty stable, change happens on a geological time frame, over millions of years, humans are changing the planet on the scale of hundreds of years. Nearly every fast environmental change is followed by mass extinctions, and many of those changes were much slower than what we're doing. | Yes that was the point he was making, good job for being able to understand that.</v>
       </c>
     </row>
     <row r="336" xml:space="preserve">
@@ -6426,7 +6442,7 @@
         <v>15</v>
       </c>
       <c r="E336" t="str">
-        <v>Thank you | The Earth is greening up due to the extra CO2!  This is a good thing.  Plants use/need less water as CO2 increases.  Ask anyone that runs greenhouses how this all works. | CO2 makes sea water more acid.  This makes it harder for things to make shells and bones not easier. | ​ @kensmith5694 the oyster shells are hard as they ever were. I just shucked a half dozen yesterday. Ocean acidification is meh. Some scientists trying to get funding tested a theory that had inconclusive evidence. ️</v>
+        <v/>
       </c>
     </row>
     <row r="337">
@@ -6463,7 +6479,7 @@
         <v>How is this supposed to be a critical number? CO2 levels in the atmosphere aren't going to decrease at all in the next centuries (instead they are increasing rapidly) and are definitly not going to crash far beneath pre industrial levels... | @jakob321123  It's all about balance. With world population looking more and more likely to fall in the next decade, all emissions will fall as well. Coupled with technologies to lower emissions already and Carbon Capture technology becoming more and more efficient and viable, we could over do it in the next century; pulling too much CO2 out of the atmosphere. The fact that Atmospheric CO2 has increased by about 50% in the past 200 years means that we can vary the amount quickly. The fact that we are still close to the minimum needed means we could just as easily in the near future go too far that way as well.</v>
       </c>
     </row>
-    <row r="339">
+    <row r="339" xml:space="preserve">
       <c r="A339" t="str">
         <v>@shamanahaboolist</v>
       </c>
@@ -6476,8 +6492,9 @@
       <c r="D339">
         <v>19</v>
       </c>
-      <c r="E339" t="str">
-        <v/>
+      <c r="E339" t="str" xml:space="preserve">
+        <v xml:space="preserve">That's what I was thinking. The fact that it is such a small percentage means new CO2 will have a bigger impact. | @AnEngagedNormie  No that is not correct, further increases in CO2 will have little or no effect on temperature. In fact temperatures have plateaued over the last ten years. | Nope. | current amount: 412 parts in a million. 500 million years ago: 4000 parts in a million.
+If the small increase of .01 to the current amount(100 parts in a million) is huge and by some accounts "life threatening" due to a runaway greenhouse effect, how come 10 times that much couldnt cause that runaway effect? | @mr.meatsoup5639  because 500 million years ago the ecosystem of the planet was entirely different and it didn't have 8 billion humans on it who'd quite like to still stay fed.</v>
       </c>
     </row>
     <row r="340">
@@ -6669,7 +6686,7 @@
         <v>15</v>
       </c>
       <c r="E350" t="str">
-        <v>So if we reduce CO2 production, and keep deforestation at the current rate. We'll all end up suffocating to death from lack of oxygen produced... Welcome to Spaceballs people. | @danielkapp9468  But at least our moral superiors will die knowing they saved the world. | @dizzyrick7653  Yea the current atmosphere contains 21% oxygen, humans need at least 19.5% for proper function, but we can survive down to 14% but by that point the oceans and lakes would be dead. Trees and plant's don't need oxygen, but pollinators do, so the only plant's that could guarentee their survival are most grasses and bamboos. I'm of the opinion we should do as marginal of changes as possible as we don't know what the effects are. Like running towards a cliff in the fog. | Yes and we've actually been seeing accelerated forest growth now compared to 100 years ago, which provides some evidence for your claim.</v>
+        <v/>
       </c>
     </row>
     <row r="351">
@@ -6686,7 +6703,7 @@
         <v>10</v>
       </c>
       <c r="E351" t="str">
-        <v/>
+        <v>Heavy man. | 7000??! (facepalm) Just FYI: "The levels of CO2 in the air and potential health problems are: 2,000–5,000 ppm: level associated with headaches, sleepiness, and stagnant, stale, stuffy air. Poor concentration, loss of attention, increased heart rate and slight nausea may also be present." | @kanizh  US  Navy level for submariners is 9000 and NASA's for spacecraft is 11,000. Did you not see the Tom Hanks movie Apollo 13? | Very good points, thank you. | Thank you! This carbon zero garbage is just ridiculous. I have questioned this and was told, 'Carbon Zero is easier for the public to understand'. So, it's a marketing issue, not scientific. | There are theories that if the co2 doubled  it would have little impact on climate, but would make plant growth more prolific | With current life and settings on earth probably the optimum amount would be around 800-1500 probably. Most plants grow far better until you reach those levels and then it kinda flattens out. CO2 fertilisation is is already doing wonders for the planet and humanity.</v>
       </c>
     </row>
     <row r="352">
@@ -6737,7 +6754,7 @@
         <v>9</v>
       </c>
       <c r="E354" t="str">
-        <v>Excellent comment</v>
+        <v/>
       </c>
     </row>
     <row r="355" xml:space="preserve">
@@ -6806,7 +6823,7 @@
         <v>8</v>
       </c>
       <c r="E358" t="str">
-        <v>No,because it was 15 times higher and biodiversity improved if anything, the fossil record shows this.</v>
+        <v/>
       </c>
     </row>
     <row r="359" xml:space="preserve">
@@ -6826,11 +6843,14 @@
       <c r="D359">
         <v>8</v>
       </c>
-      <c r="E359" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="360" xml:space="preserve">
+      <c r="E359" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. The fraction may be small, but the amount of CO2 is still large. Those "small" fractions of greenhouse gases raise the global avereage temperature from about -18°C, or -0.4°F.
+2. Ice cores show it's been as low as about 185 ppm. | @anderslvolljohansen1556  
+1. you didn't specify the "to", but I expect some number that can not be backed by anything but pseudo-science (aka models and feedback loops). The factual effect of CO2 is that it takes a doubling of CO2 to cause 1 degree C of warming, with exponential diminishing returns (in round numbers roughly 400ppm=0C, 800ppm=1C, 1600ppm=2C, 3200ppm = 3C). | @JanusKjempff  To about 14°C before the industrial revolution, or about 15°C now. (57°F or 59°F).
+2. 172ppm is the record low from the Antarctic ice core that goes back 800k years.</v>
+      </c>
+    </row>
+    <row r="360">
       <c r="A360" t="str">
         <v>@twostate7822</v>
       </c>
@@ -6843,10 +6863,8 @@
       <c r="D360">
         <v>10</v>
       </c>
-      <c r="E360" t="str" xml:space="preserve">
-        <v xml:space="preserve">Thank you for pointing that out. | What you are saying is not wrong. However, it is up to you to prove that an increase of CO2 would be devastating for the planet (as the environmentalists claim). In fact, all that we really know is that we need a minimum amount of CO2 in the atmosphere to maintain life on Earth and in the past CO2 was much higher than it is nowadays. Maintaining the planet's status quo not only is it impossible, but it also goes against nature. | @overthetip  Most climate change is gradual, over hundreds and thousands of years. Among the exceptions are periods of intense volcanic activity, or large meteor strikes which can cause climate change almost immediately.
-What scientist are seeing is rapidly increasing temperatures over the course of mere years, and the only variable that is fluctuating abnormally is CO2 level which are having almost unprecedented rates of increase.
-Scientists are not worried that the climate is changing. They are worried that the climate is changing so fast that it will affect  almost all life on the planet.</v>
+      <c r="E360" t="str">
+        <v/>
       </c>
     </row>
     <row r="361">
@@ -6883,7 +6901,7 @@
         <v>How is it a fallacy?</v>
       </c>
     </row>
-    <row r="363">
+    <row r="363" xml:space="preserve">
       <c r="A363" t="str">
         <v>@Darkmerge</v>
       </c>
@@ -6896,11 +6914,16 @@
       <c r="D363">
         <v>9</v>
       </c>
-      <c r="E363" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="364" xml:space="preserve">
+      <c r="E363" t="str" xml:space="preserve">
+        <v xml:space="preserve">Because at lower concentrations plant photosythesis essentially ceases.
+As the concentration goes up, photosythesis ramps up.
+Probably the main reason CO2 concentrations have remained nearly constant over the 800,000 years we have ice cores for.
+Climate cultists tend to ignore history in favor of alarmism. | I don't think you understand what he's implying. It's the opposite of your argument. Stop the climate alarmist nonsense | That's the problem, becuase it's such a small change relative to the atmosphere it makes it easy for most ppl to think it's not an issue. But then everyone does it - frame the numbers in a way that suites their narrative and makes the opposition look poor/silly etc. | You miss the whole picture. Free your thought barriers. 
+For instance: It is not a question of how much a content of CO2 changed. The question is, is this change for the good or for the bad? Can we maybe live an even better life if we have more CO2 in our atmosphere while learning to adapt to it? Or are costs to keep status quo too high? See, there were times in middle Europe not so long ago, where we had no glaciers in the alpes. Farmers were able to harvest cereals two times in the year. Desertification is less a subject of global warming but more a subject of ruthless exploitation of forest resources. Do you even have the slightest idea on how strong the impact of forest land is on regional rainfall patterns? How strong regional weather patterns are influenced by ocean currents? How suddenly global climate can be changed by only one major volcanic eruption? Even solar changes need to be considered. Those factors by far outweigh the CO2 factor. Imagine, global society would start operating CO2 negative by CO2 certificate and start to exploit CO2 recourses to make a profit. That is a very short-sighted construct. To feed billions of individuals we would need to have increase carbon levels to cover carbon requirements for all of us. 
+But at the same time, we would need to have leveled up carbon cycle between soils, green cover area, blue cover area and the atmosphere to a new equilibrium. As you see how complex this is, you should not limit your brain cells to a CO2 ideology.</v>
+      </c>
+    </row>
+    <row r="364">
       <c r="A364" t="str">
         <v>@swiftlytiltingplanet8481</v>
       </c>
@@ -6913,10 +6936,8 @@
       <c r="D364">
         <v>9</v>
       </c>
-      <c r="E364" t="str" xml:space="preserve">
-        <v xml:space="preserve">And what influence do you think/ believe do people have on/contributes to this 0.04% | Also important to not the saturation effect. More CO2 does not create more greenhouse effect. | The percentage of CO2 in 1970 was 0.04%, the same as it is today.  It hasn't changed in 50 years.  If it drops any more we won't be able to grow food. | @franktriggs  Actually it has increased from about 350  in 70 to about 420 today. Still a low number and not a cause for global warming. | @ 
-NewAtlas put it at 14 ppm increase for the last 55 years.
-That alone tells me, because we can't verify it ourselves, they can feed us any numbers they like to support the narrative. | @nonconformist4802  What the hell is "NewAtlas? I see a standard keeling curve on NOAA's homepage with a CO2 concentration just below 320ppm in 1960. 55 years later in 2015 it was at 400ppm. That is a rise of 80ppm in 55 years and those years are not even the most recent years (where the rise has been faster). I find it ironic that you have a no B.S. icon when you are the one espousing B.S.</v>
+      <c r="E364" t="str">
+        <v/>
       </c>
     </row>
     <row r="365">
@@ -6936,7 +6957,7 @@
         <v/>
       </c>
     </row>
-    <row r="366">
+    <row r="366" xml:space="preserve">
       <c r="A366" t="str">
         <v>@petemenhennet9792</v>
       </c>
@@ -6949,8 +6970,9 @@
       <c r="D366">
         <v>10</v>
       </c>
-      <c r="E366" t="str">
-        <v/>
+      <c r="E366" t="str" xml:space="preserve">
+        <v xml:space="preserve">Its actually gone up by 0.011% in the last hundred years which is 0.00011% per year of which 27% is allegedly from transport, so thats is 0.00003%...and you think people should be concerned.... | @manoo422  These people have worked themselves into an 'existential crisis' which does not exist from pop "talking points". They should be 'concerned' about per- and polyfluoroalkyl compounds but that chemistry is way to complicated for the 'average' person. So, they jibber-jabber on about CO2 without knowing anything about it. | No it is not a "cause for concern". He is talking about CO2 not poison. You exhale CO2 and the concentration is around 4%. Atmospheric CO2 has been 10 times higher in the past. At the turn of the 20th century atmospheric CO2 concentrations were at an all time low. Higher concentrations mean a greener earth. You don't know what you are  talking about but, you are worried. | @hubrisnaut  Firstly that's not the point of his analogy. He was only saying that the size of a number has no significance at all without context and is no basis for an argument.
+As for the other points you make, I strongly recommend you find some reliable data on how CO2 ppm have changed over time and the obvious impact of humans on that figure. I would be happy to explain why the "greener earth" argument is completely misleading but it would take time and there are plenty of people who have spent their lives studying this kind of thing that explain it far better. Be very careful where you get your information from. | @HubrisNaut, exactly.</v>
       </c>
     </row>
     <row r="367" xml:space="preserve">
@@ -6986,7 +7008,7 @@
         <v>7</v>
       </c>
       <c r="E368" t="str">
-        <v>Diesel and gas do NOT burn greener than electricity! | @Dan-sc7us  how do you think that electricty is made? 60% of electricty in the grid is made by burning a fossil fuel. But to be specific I was refering to less methane (which is 23x more potent than CO2 as a green house gas and persists for longer) is produced by diesel than the mining, manufacturing and use of many other sources.. like hydrogen, some batteries, ect. | @Dan-sc7us    Oh man, next you're gonna tel us that they don't destroy the earth using child labor digging for rare earth metals to make "green" batteries. | Try getting the % of methane and your claim becomes even more absurd than that environmentalist panel. | There has to be an industrial use for the pure carbon powder deposits from burning diesel. How is it different than graphene? | @russell-gt1dy  quite different in structure. But.. there are techniques to turn any carbon source into graphene through high voltage. The manufacturing is not expandable to scale yet (ever?). Plus every time someone sells something as "we use this waste and recycle it into this" they never really do. So even if we got soot collectors to make graphene, companies would just mine graphite for raw materials.</v>
+        <v/>
       </c>
     </row>
     <row r="369">
@@ -7277,7 +7299,7 @@
         <v>0</v>
       </c>
       <c r="E385" t="str">
-        <v/>
+        <v>Wow, talking about an utterly irrelevant remark ... you just aced it.</v>
       </c>
     </row>
     <row r="386">
@@ -7656,16 +7678,16 @@
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>@cpfalcon51</v>
+        <v>@MrMjolnir69</v>
       </c>
       <c r="B408" t="str">
-        <v>People on this panel are making major decisions. That's great.</v>
+        <v>Uh Hwat now? Csn you repeat that question son?</v>
       </c>
       <c r="C408" t="str">
         <v>Unknown</v>
       </c>
       <c r="D408">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E408" t="str">
         <v/>
@@ -7673,16 +7695,16 @@
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>@MrMjolnir69</v>
+        <v>@cpfalcon51</v>
       </c>
       <c r="B409" t="str">
-        <v>Uh Hwat now? Csn you repeat that question son?</v>
+        <v>People on this panel are making major decisions. That's great.</v>
       </c>
       <c r="C409" t="str">
         <v>Unknown</v>
       </c>
       <c r="D409">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E409" t="str">
         <v/>
@@ -7930,10 +7952,10 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>@davidwright4211</v>
+        <v>@stevenclarkson1853</v>
       </c>
       <c r="B424" t="str">
-        <v>No Co2 no food. .</v>
+        <v>The only good thing about less reliance on oil is denying some Countries revenue.</v>
       </c>
       <c r="C424" t="str">
         <v>Unknown</v>
@@ -7947,10 +7969,10 @@
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>@stevenclarkson1853</v>
+        <v>@davidwright4211</v>
       </c>
       <c r="B425" t="str">
-        <v>The only good thing about less reliance on oil is denying some Countries revenue.</v>
+        <v>No Co2 no food. .</v>
       </c>
       <c r="C425" t="str">
         <v>Unknown</v>
@@ -8067,36 +8089,36 @@
     </row>
     <row r="432" xml:space="preserve">
       <c r="A432" t="str">
+        <v>@leoaquino1479</v>
+      </c>
+      <c r="B432" t="str" xml:space="preserve">
+        <v xml:space="preserve">These politicians are so 
+Ignorant</v>
+      </c>
+      <c r="C432" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D432">
+        <v>0</v>
+      </c>
+      <c r="E432" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="433" xml:space="preserve">
+      <c r="A433" t="str">
         <v>@marklewis8067</v>
       </c>
-      <c r="B432" t="str" xml:space="preserve">
+      <c r="B433" t="str" xml:space="preserve">
         <v xml:space="preserve">We are actually in a CO2 drought. We do not have enough CO2 in the atmosphere. 
 The largest green house gas is actually water vapor - CLOUDS.
 Nobody complains about clouds though.</v>
       </c>
-      <c r="C432" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D432">
+      <c r="C433" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D433">
         <v>1</v>
-      </c>
-      <c r="E432" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="433" xml:space="preserve">
-      <c r="A433" t="str">
-        <v>@leoaquino1479</v>
-      </c>
-      <c r="B433" t="str" xml:space="preserve">
-        <v xml:space="preserve">These politicians are so 
-Ignorant</v>
-      </c>
-      <c r="C433" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D433">
-        <v>0</v>
       </c>
       <c r="E433" t="str">
         <v/>
@@ -8170,7 +8192,7 @@
         <v>0</v>
       </c>
       <c r="E437" t="str">
-        <v>I never fell for their BS</v>
+        <v/>
       </c>
     </row>
     <row r="438">
@@ -8243,16 +8265,16 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>@larryvanbarriger6670</v>
+        <v>@normlor</v>
       </c>
       <c r="B442" t="str">
-        <v>Yup the electric industry powered by the gasoline industry</v>
+        <v>NO REASON NOT TO RID OUR WHOLE ATMOSPHERE OF ALL Co2</v>
       </c>
       <c r="C442" t="str">
         <v>Unknown</v>
       </c>
       <c r="D442">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E442" t="str">
         <v/>
@@ -8273,22 +8295,35 @@
       <c r="D443">
         <v>1</v>
       </c>
-      <c r="E443" t="str">
-        <v/>
+      <c r="E443" t="str" xml:space="preserve">
+        <v xml:space="preserve">And?  What is the effect and what causes this? | @mrunning10  
+So the BEST question is - what is the job function of the panelists?
+Are they climate scientists?
+Why do THEY not know this answer?
+Because this gotchya is being promoted as the "experts dont know". | @mrunning10  
+the "greenhouse effect".
+Why are you asking a nonsense question?
+Edit
+Oh did you give me a thumbs?
+Then you asking the obvious for obviously. | @thedubwhisperer2157  it is a big change.
+It is the change that the questioner ignored.
+His %of atmosphere is a strawman.
+What you on about? | @themightykabool  My apologies.  Completely misread your post!  Comment deleted - sorry. | @thedubwhisperer2157  ah ok
+Glad we agree! | @themightykabool  Absolutely Dude!</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>@normlor</v>
+        <v>@larryvanbarriger6670</v>
       </c>
       <c r="B444" t="str">
-        <v>NO REASON NOT TO RID OUR WHOLE ATMOSPHERE OF ALL Co2</v>
+        <v>Yup the electric industry powered by the gasoline industry</v>
       </c>
       <c r="C444" t="str">
         <v>Unknown</v>
       </c>
       <c r="D444">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E444" t="str">
         <v/>
@@ -8308,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="E445" t="str">
-        <v>Canada could dissapear tommorrow and it wouldn’t even make 1% difference in [something the platform doesnt want me to say], so why are we hurting ourselves to try and make a  ‘difference’?</v>
+        <v/>
       </c>
     </row>
     <row r="446">
@@ -8449,10 +8484,10 @@
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>@MrApplewine</v>
+        <v>@TiGGer1098</v>
       </c>
       <c r="B454" t="str">
-        <v>I like money.</v>
+        <v>Funny how that was worded as 0.4% as if it’s negligible, when it’s really not at all. We’ve increased it from 0.25% and seem hellbent on doing nothing to stop a further increase which will dramatically increase the amount of heat trapped in our atmosphere!</v>
       </c>
       <c r="C454" t="str">
         <v>Unknown</v>
@@ -8466,10 +8501,10 @@
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>@TiGGer1098</v>
+        <v>@MrApplewine</v>
       </c>
       <c r="B455" t="str">
-        <v>Funny how that was worded as 0.4% as if it’s negligible, when it’s really not at all. We’ve increased it from 0.25% and seem hellbent on doing nothing to stop a further increase which will dramatically increase the amount of heat trapped in our atmosphere!</v>
+        <v>I like money.</v>
       </c>
       <c r="C455" t="str">
         <v>Unknown</v>
@@ -8603,108 +8638,108 @@
         <v/>
       </c>
     </row>
-    <row r="463">
+    <row r="463" xml:space="preserve">
       <c r="A463" t="str">
-        <v>@mathboy8188</v>
-      </c>
-      <c r="B463" t="str">
-        <v>There's a YT video critiquing this garbage with the title "CO2 Misconceptions: Debunking Doug LaMalfa on Climate Change"</v>
-      </c>
-      <c r="C463" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D463">
-        <v>2</v>
-      </c>
-      <c r="E463" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="464" xml:space="preserve">
-      <c r="A464" t="str">
         <v>@brianterence3211</v>
       </c>
-      <c r="B464" t="str" xml:space="preserve">
+      <c r="B463" t="str" xml:space="preserve">
         <v xml:space="preserve">That these people have a strong opinion about a subject which they obviously
 know nothing about is astonishing.</v>
       </c>
+      <c r="C463" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D463">
+        <v>0</v>
+      </c>
+      <c r="E463" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>@mathboy8188</v>
+      </c>
+      <c r="B464" t="str">
+        <v>There's a YT video critiquing this garbage with the title "CO2 Misconceptions: Debunking Doug LaMalfa on Climate Change"</v>
+      </c>
       <c r="C464" t="str">
         <v>Unknown</v>
       </c>
       <c r="D464">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E464" t="str">
         <v/>
       </c>
     </row>
-    <row r="465" xml:space="preserve">
+    <row r="465">
       <c r="A465" t="str">
+        <v>@PInk77W1</v>
+      </c>
+      <c r="B465" t="str">
+        <v>Not a single one of them will b fired</v>
+      </c>
+      <c r="C465" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D465">
+        <v>0</v>
+      </c>
+      <c r="E465" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="466" xml:space="preserve">
+      <c r="A466" t="str">
         <v>@dingodog5677</v>
       </c>
-      <c r="B465" t="str">
+      <c r="B466" t="str">
         <v>And these people are supposed to be aware of the issues. They’re all demonstrably unqualified for their positions.</v>
       </c>
-      <c r="C465" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D465">
-        <v>0</v>
-      </c>
-      <c r="E465" t="str" xml:space="preserve">
+      <c r="C466" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D466">
+        <v>0</v>
+      </c>
+      <c r="E466" t="str" xml:space="preserve">
         <v xml:space="preserve">[] ... They’re all demonstrably unqualified for their positions.
 _x000d_
 _x000d_As is the questioner. Who is oblivious of the consequential effect of the increase in atmospheric CO2 concentration.
 Of course, if the panel would have consisted of actual atmospheric scientists, they easily could have correctly answered this question. As these scientists would also have corrected the ignorant perception of the questioner.</v>
       </c>
     </row>
-    <row r="466">
-      <c r="A466" t="str">
-        <v>@PInk77W1</v>
-      </c>
-      <c r="B466" t="str">
-        <v>Not a single one of them will b fired</v>
-      </c>
-      <c r="C466" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D466">
-        <v>0</v>
-      </c>
-      <c r="E466" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="467" xml:space="preserve">
+    <row r="467">
       <c r="A467" t="str">
+        <v>@norcal_gamer</v>
+      </c>
+      <c r="B467" t="str">
+        <v>RIP MR LaMalfa you were one of the few honest people in our government,</v>
+      </c>
+      <c r="C467" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D467">
+        <v>0</v>
+      </c>
+      <c r="E467" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="468" xml:space="preserve">
+      <c r="A468" t="str">
         <v>@DANCEGARAGEPUNK</v>
       </c>
-      <c r="B467" t="str" xml:space="preserve">
+      <c r="B468" t="str" xml:space="preserve">
         <v xml:space="preserve">Corporate Interests control the narrative ! : (
 And finance misinformation sites like this !  : )</v>
       </c>
-      <c r="C467" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D467">
+      <c r="C468" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D468">
         <v>1</v>
-      </c>
-      <c r="E467" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="str">
-        <v>@norcal_gamer</v>
-      </c>
-      <c r="B468" t="str">
-        <v>RIP MR LaMalfa you were one of the few honest people in our government,</v>
-      </c>
-      <c r="C468" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D468">
-        <v>0</v>
       </c>
       <c r="E468" t="str">
         <v/>
@@ -8818,7 +8853,7 @@
         <v/>
       </c>
     </row>
-    <row r="472">
+    <row r="472" xml:space="preserve">
       <c r="A472" t="str">
         <v>@RhichardHostettler</v>
       </c>
@@ -8831,8 +8866,9 @@
       <c r="D472">
         <v>0</v>
       </c>
-      <c r="E472" t="str">
-        <v/>
+      <c r="E472" t="str" xml:space="preserve">
+        <v xml:space="preserve">If you don't know the percentage by weight of arsenic that can kill you, then we certainly don't know if it can kill you at all.
+-- LaMalfa, really smart fella</v>
       </c>
     </row>
     <row r="473">
@@ -9121,7 +9157,7 @@
         <v>5</v>
       </c>
       <c r="E489" t="str">
-        <v>And a 5 second Google search shows you that we are at a record low level compared to any other geological era. So, CO2 levels are not a concern.</v>
+        <v/>
       </c>
     </row>
     <row r="490">
@@ -9143,16 +9179,16 @@
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>@TheGrimReaper1</v>
+        <v>@qqwwaa2</v>
       </c>
       <c r="B491" t="str">
-        <v>And what about all those volcanoes polluting the atmosphere? How much pollution do they chuck out and nobody says a dicky bird, they can just blow their tops with impunity. .</v>
+        <v>This congressman is a complete idiot. He  thinks he sounds smart but whithout realizing the stupidity of his arguments and the dumb things he said about "tiny" change etc.</v>
       </c>
       <c r="C491" t="str">
         <v>Unknown</v>
       </c>
       <c r="D491">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E491" t="str">
         <v/>
@@ -9160,16 +9196,16 @@
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>@qqwwaa2</v>
+        <v>@TheGrimReaper1</v>
       </c>
       <c r="B492" t="str">
-        <v>This congressman is a complete idiot. He  thinks he sounds smart but whithout realizing the stupidity of his arguments and the dumb things he said about "tiny" change etc.</v>
+        <v>And what about all those volcanoes polluting the atmosphere? How much pollution do they chuck out and nobody says a dicky bird, they can just blow their tops with impunity. .</v>
       </c>
       <c r="C492" t="str">
         <v>Unknown</v>
       </c>
       <c r="D492">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E492" t="str">
         <v/>
@@ -9189,15 +9225,15 @@
         <v>1</v>
       </c>
       <c r="E493" t="str">
-        <v/>
+        <v>Better express it a a proportion of the earth's atmosphere which is .004.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>@iracer9395</v>
+        <v>@emmabaker4925</v>
       </c>
       <c r="B494" t="str">
-        <v>Climate change is a $$$/Control scam being pushed on society by anti-capitalists.</v>
+        <v>What is good will be called bad and what is bad will be called good. This world is backwards.</v>
       </c>
       <c r="C494" t="str">
         <v>Unknown</v>
@@ -9211,10 +9247,10 @@
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>@emmabaker4925</v>
+        <v>@christopherward9230</v>
       </c>
       <c r="B495" t="str">
-        <v>What is good will be called bad and what is bad will be called good. This world is backwards.</v>
+        <v>So, these clowns turned up at a meeting without the facts and numbers of their argument, wow</v>
       </c>
       <c r="C495" t="str">
         <v>Unknown</v>
@@ -9228,10 +9264,10 @@
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>@christopherward9230</v>
+        <v>@iracer9395</v>
       </c>
       <c r="B496" t="str">
-        <v>So, these clowns turned up at a meeting without the facts and numbers of their argument, wow</v>
+        <v>Climate change is a $$$/Control scam being pushed on society by anti-capitalists.</v>
       </c>
       <c r="C496" t="str">
         <v>Unknown</v>
@@ -9342,7 +9378,7 @@
         <v>1</v>
       </c>
       <c r="E502" t="str">
-        <v>No, please enlighten us.</v>
+        <v/>
       </c>
     </row>
     <row r="503">
@@ -9498,49 +9534,49 @@
         <v/>
       </c>
     </row>
-    <row r="512">
+    <row r="512" xml:space="preserve">
       <c r="A512" t="str">
-        <v>@dougreeves7092</v>
-      </c>
-      <c r="B512" t="str">
-        <v>They're fuckin playing the price is right at an environmental hearing! Wtf?! They thought it was a game! And they were shut the fudge down!</v>
-      </c>
-      <c r="C512" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D512">
-        <v>0</v>
-      </c>
-      <c r="E512" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="str">
-        <v>@geoffmorgan2794</v>
-      </c>
-      <c r="B513" t="str">
-        <v>C O 2     is it the Carbon they want to remove or the Oxygen???</v>
-      </c>
-      <c r="C513" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D513">
-        <v>0</v>
-      </c>
-      <c r="E513" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="514" xml:space="preserve">
-      <c r="A514" t="str">
         <v>@spacemissing</v>
       </c>
-      <c r="B514" t="str" xml:space="preserve">
+      <c r="B512" t="str" xml:space="preserve">
         <v xml:space="preserve">Anyone in a position of power who is truly concerned about the environment 
 should have the exact figures of the top ten elements involved 
 On The Tip Of Their Tongue, along with other important specifics.</v>
       </c>
+      <c r="C512" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D512">
+        <v>0</v>
+      </c>
+      <c r="E512" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="str">
+        <v>@dougreeves7092</v>
+      </c>
+      <c r="B513" t="str">
+        <v>They're fuckin playing the price is right at an environmental hearing! Wtf?! They thought it was a game! And they were shut the fudge down!</v>
+      </c>
+      <c r="C513" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D513">
+        <v>0</v>
+      </c>
+      <c r="E513" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="str">
+        <v>@geoffmorgan2794</v>
+      </c>
+      <c r="B514" t="str">
+        <v>C O 2     is it the Carbon they want to remove or the Oxygen???</v>
+      </c>
       <c r="C514" t="str">
         <v>Unknown</v>
       </c>
@@ -9551,30 +9587,30 @@
         <v/>
       </c>
     </row>
-    <row r="515">
+    <row r="515" xml:space="preserve">
       <c r="A515" t="str">
-        <v>@steveogee7458</v>
-      </c>
-      <c r="B515" t="str">
-        <v>Common sense is not common.</v>
-      </c>
-      <c r="C515" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D515">
-        <v>0</v>
-      </c>
-      <c r="E515" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="516" xml:space="preserve">
-      <c r="A516" t="str">
         <v>@asahito2004</v>
       </c>
-      <c r="B516" t="str" xml:space="preserve">
+      <c r="B515" t="str" xml:space="preserve">
         <v xml:space="preserve">Yup perhaps...  How about holding 0.000000001 gram plutonium 239 impact?
 But you're right.... Switching full ev car is also not any wiser</v>
+      </c>
+      <c r="C515" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D515">
+        <v>0</v>
+      </c>
+      <c r="E515" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="str">
+        <v>@steveogee7458</v>
+      </c>
+      <c r="B516" t="str">
+        <v>Common sense is not common.</v>
       </c>
       <c r="C516" t="str">
         <v>Unknown</v>
@@ -9600,7 +9636,7 @@
         <v>2</v>
       </c>
       <c r="E517" t="str">
-        <v>Oh my. That guy needs more than an education.</v>
+        <v/>
       </c>
     </row>
     <row r="518">
@@ -9651,7 +9687,7 @@
         <v>0</v>
       </c>
       <c r="E520" t="str">
-        <v/>
+        <v>The gas that causes trouble come out the front end of the cow.  I suggest the reader of your comment check you on that fact before accepting the rest.</v>
       </c>
     </row>
     <row r="521">
@@ -9758,10 +9794,10 @@
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>@WayneAustin-f3u</v>
+        <v>@GHOST5663</v>
       </c>
       <c r="B527" t="str">
-        <v>We think we are smart but we are actually pretty stupid</v>
+        <v>They don't care.</v>
       </c>
       <c r="C527" t="str">
         <v>Unknown</v>
@@ -9775,10 +9811,10 @@
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>@GHOST5663</v>
+        <v>@WayneAustin-f3u</v>
       </c>
       <c r="B528" t="str">
-        <v>They don't care.</v>
+        <v>We think we are smart but we are actually pretty stupid</v>
       </c>
       <c r="C528" t="str">
         <v>Unknown</v>
@@ -9933,10 +9969,10 @@
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>@thebob01</v>
+        <v>@BrianMiller-r3f</v>
       </c>
       <c r="B537" t="str">
-        <v>The climate change agenda is the biggest farce ever brought on the populace. It's nothing but BS propaganda.</v>
+        <v>Carbon dioxide makes up about 0.04% of dry air, the fourth most common gas in the atmosphere (when humidity or water vapor is at 0%), Even Argon, the third most common gas, is at 0.93%, which is many times that of carbon dioxide. Any "climate expert" that doesn't know that basic fact should not be involved in setting policy decisions.</v>
       </c>
       <c r="C537" t="str">
         <v>Unknown</v>
@@ -9950,10 +9986,10 @@
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>@BrianMiller-r3f</v>
+        <v>@thebob01</v>
       </c>
       <c r="B538" t="str">
-        <v>Carbon dioxide makes up about 0.04% of dry air, the fourth most common gas in the atmosphere (when humidity or water vapor is at 0%), Even Argon, the third most common gas, is at 0.93%, which is many times that of carbon dioxide. Any "climate expert" that doesn't know that basic fact should not be involved in setting policy decisions.</v>
+        <v>The climate change agenda is the biggest farce ever brought on the populace. It's nothing but BS propaganda.</v>
       </c>
       <c r="C538" t="str">
         <v>Unknown</v>
@@ -10143,10 +10179,10 @@
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>@JupiterThunder</v>
+        <v>@dcs6230</v>
       </c>
       <c r="B549" t="str">
-        <v>It's fair to say that it's not necessarily the % CO2 content of the atmosphere that's important, but nevertheless, the total ignorance of these people is quite astounding.</v>
+        <v>They cannot tell you how much CO2 is in the atmosphere but they’re in front of congress discussing a subject they have no understanding of it.</v>
       </c>
       <c r="C549" t="str">
         <v>Unknown</v>
@@ -10160,10 +10196,10 @@
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>@dcs6230</v>
+        <v>@JupiterThunder</v>
       </c>
       <c r="B550" t="str">
-        <v>They cannot tell you how much CO2 is in the atmosphere but they’re in front of congress discussing a subject they have no understanding of it.</v>
+        <v>It's fair to say that it's not necessarily the % CO2 content of the atmosphere that's important, but nevertheless, the total ignorance of these people is quite astounding.</v>
       </c>
       <c r="C550" t="str">
         <v>Unknown</v>
@@ -10317,10 +10353,10 @@
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>@marcelfsilva</v>
+        <v>@shaunflowers-cp8ws</v>
       </c>
       <c r="B559" t="str">
-        <v>0,04 % ou 424 ppm in may 2023. it is about 100x lower of they said</v>
+        <v>this reduction of energy and gas production is borderline treason to the country</v>
       </c>
       <c r="C559" t="str">
         <v>Unknown</v>
@@ -10334,10 +10370,10 @@
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>@shaunflowers-cp8ws</v>
+        <v>@marcelfsilva</v>
       </c>
       <c r="B560" t="str">
-        <v>this reduction of energy and gas production is borderline treason to the country</v>
+        <v>0,04 % ou 424 ppm in may 2023. it is about 100x lower of they said</v>
       </c>
       <c r="C560" t="str">
         <v>Unknown</v>
@@ -10536,7 +10572,7 @@
         <v>1</v>
       </c>
       <c r="E571" t="str">
-        <v>Not a governmental study.</v>
+        <v/>
       </c>
     </row>
     <row r="572">
@@ -10625,37 +10661,37 @@
         <v/>
       </c>
     </row>
-    <row r="577" xml:space="preserve">
+    <row r="577">
       <c r="A577" t="str">
+        <v>@Boerikoe</v>
+      </c>
+      <c r="B577" t="str">
+        <v>being led by the ignorant.... frightening reality !</v>
+      </c>
+      <c r="C577" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D577">
+        <v>0</v>
+      </c>
+      <c r="E577" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="578" xml:space="preserve">
+      <c r="A578" t="str">
         <v>@anthonyquinn3671</v>
       </c>
-      <c r="B577" t="str" xml:space="preserve">
+      <c r="B578" t="str" xml:space="preserve">
         <v xml:space="preserve">The amount of Co2 Released into our Atmosphere from the production of Lithium Batteries From Mining, Smelting and the transportation of the Lithium vastly outweighs the benefits from EVs Solar Panels and Wind Farms! 
 CO2 actually makes our Planet Greener because Plant Life Depends on CO2s for Natural growth, and as the specialist said if CO2 levels dropped below 0.2% Plant Life would start to Die off, leaving us with Starvation and mass Extinction of Animals and Humans!
 LET THAT SINK IN GRETA THUNBERG!</v>
       </c>
-      <c r="C577" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D577">
+      <c r="C578" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D578">
         <v>1</v>
-      </c>
-      <c r="E577" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" t="str">
-        <v>@Boerikoe</v>
-      </c>
-      <c r="B578" t="str">
-        <v>being led by the ignorant.... frightening reality !</v>
-      </c>
-      <c r="C578" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D578">
-        <v>0</v>
       </c>
       <c r="E578" t="str">
         <v/>
@@ -10820,62 +10856,62 @@
     </row>
     <row r="588">
       <c r="A588" t="str">
+        <v>@kkcw6668</v>
+      </c>
+      <c r="B588" t="str">
+        <v>Skewed a tad. The question is flawed because it fails to get closer to "your home", say like the slice of atmosphere in your nthn hemisphere, or just the nthn hemisphere atmosphere, since the two (sth &amp; nth) circulate exclusive of each other! Your damage imposed on us in the Sthn hemisphere is via ocean temps &amp; currents.</v>
+      </c>
+      <c r="C588" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D588">
+        <v>0</v>
+      </c>
+      <c r="E588" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="str">
+        <v>@stman63438</v>
+      </c>
+      <c r="B589" t="str">
+        <v>Trying to restrict growth that’s what this is about then that restricts people’s ability to grow their families. The carbon they want to get rid of is people</v>
+      </c>
+      <c r="C589" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D589">
+        <v>0</v>
+      </c>
+      <c r="E589" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="str">
         <v>@POWROTTATY</v>
       </c>
-      <c r="B588" t="str">
+      <c r="B590" t="str">
         <v>C is life, O² is life; CO² is super life.</v>
       </c>
-      <c r="C588" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D588">
+      <c r="C590" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D590">
         <v>1</v>
       </c>
-      <c r="E588" t="str">
+      <c r="E590" t="str">
         <v>H2O is life as well but H is explosive. But keep making dumb statements.</v>
       </c>
     </row>
-    <row r="589" xml:space="preserve">
-      <c r="A589" t="str">
+    <row r="591" xml:space="preserve">
+      <c r="A591" t="str">
         <v>@fredbarnes196</v>
       </c>
-      <c r="B589" t="str" xml:space="preserve">
+      <c r="B591" t="str" xml:space="preserve">
         <v xml:space="preserve">Talk about dopes!
 That’s a 33% increase in CO2 levels.</v>
-      </c>
-      <c r="C589" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D589">
-        <v>0</v>
-      </c>
-      <c r="E589" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="590">
-      <c r="A590" t="str">
-        <v>@kkcw6668</v>
-      </c>
-      <c r="B590" t="str">
-        <v>Skewed a tad. The question is flawed because it fails to get closer to "your home", say like the slice of atmosphere in your nthn hemisphere, or just the nthn hemisphere atmosphere, since the two (sth &amp; nth) circulate exclusive of each other! Your damage imposed on us in the Sthn hemisphere is via ocean temps &amp; currents.</v>
-      </c>
-      <c r="C590" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D590">
-        <v>0</v>
-      </c>
-      <c r="E590" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="591">
-      <c r="A591" t="str">
-        <v>@stman63438</v>
-      </c>
-      <c r="B591" t="str">
-        <v>Trying to restrict growth that’s what this is about then that restricts people’s ability to grow their families. The carbon they want to get rid of is people</v>
       </c>
       <c r="C591" t="str">
         <v>Unknown</v>
@@ -10938,7 +10974,7 @@
         <v/>
       </c>
     </row>
-    <row r="595">
+    <row r="595" xml:space="preserve">
       <c r="A595" t="str">
         <v>@ollyk22</v>
       </c>
@@ -10951,8 +10987,14 @@
       <c r="D595">
         <v>1</v>
       </c>
-      <c r="E595" t="str">
-        <v/>
+      <c r="E595" t="str" xml:space="preserve">
+        <v xml:space="preserve">Bad Argument/Myth #9: CO2 only makes a small portion of the atmosphere._x000d_
+1) He wasn't driving drunk, he just had a trace of blood alcohol; 0.08%. _x000d_
+2) Don't worry about your iron deficiency, iron is only 4.4 ppm of your body’s atoms. _x000d_
+3) Ireland isn't important; it's only.066%) of the world population. _x000d_
+4)That ibuprofen pill can't do you any good; it's only 3 ppm of your body weight _x000d_
+5)The Earth is insignificant, it's only 3 ppm of the mass of the solar system. _x000d_
+6) Your children can drink that water, it only contains a trace of arsenic (0.01 ppm is the WHO and US EPA limit).</v>
       </c>
     </row>
     <row r="596">
@@ -10974,32 +11016,32 @@
     </row>
     <row r="597" xml:space="preserve">
       <c r="A597" t="str">
+        <v>@jeffreyyoung4104</v>
+      </c>
+      <c r="B597" t="str" xml:space="preserve">
+        <v xml:space="preserve">We are supposedly adding tons of CO2 into the atmosphere, yet we see only a 0.01% increase in the atmospheric CO2. But we don't hear about the oceans, which also use CO2 to support the aquatic plant life and other life forms in the oceans.
+And the total CO2 level in the atmosphere being only 0.04%, up from 0.03% does not reflect the panic the government officials seem to put into the laws being passed, which does not reduce the CO2 levels produced from the manufacturing end of the equation, nor does it affect the levels of CO2 produced by other countries, like China and many others where we have shipped the American manufacturing off to, in order to have lower costs due to the laws made in error of bad data being constantly repeated by the protesters and other ecology based groups.
+We need to take a giant step back and look at what has happened in America over the last 100 years of industrial revolution, and come up with the real data about the amount of pollutants we are creating, and modify the current laws to reflect the real data of the pollutants that affect our lives, rather than go with the emotions that books like silent spring and other fairy tales have caused the government officials to create stifling laws that have ruined our economy and sent our industrial companies running to nations with little to no laws regarding safety or environmental dangers, and where the people who do the labor get little to no training of the dangers about the chemicals and materials they use, nor do they get any safety equipment, like steel toed shoes, goggles, or even hearing protection that Americans refuse to work without today.</v>
+      </c>
+      <c r="C597" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D597">
+        <v>1</v>
+      </c>
+      <c r="E597" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="598" xml:space="preserve">
+      <c r="A598" t="str">
         <v>@Scubadooper</v>
       </c>
-      <c r="B597" t="str" xml:space="preserve">
+      <c r="B598" t="str" xml:space="preserve">
         <v xml:space="preserve">The real problems with this are: 
 1 - all of them should have known it was 420 parts per million, so they should all have been able to work out it was 0.042%
 2 - they allowed the guy asking the question to make out increases in CO2 don't matter as the percentage is low (increases DO matter, the fact that it has such a major impact at such a low percentage is only more worrying!)</v>
       </c>
-      <c r="C597" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D597">
-        <v>1</v>
-      </c>
-      <c r="E597" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="598" xml:space="preserve">
-      <c r="A598" t="str">
-        <v>@jeffreyyoung4104</v>
-      </c>
-      <c r="B598" t="str" xml:space="preserve">
-        <v xml:space="preserve">We are supposedly adding tons of CO2 into the atmosphere, yet we see only a 0.01% increase in the atmospheric CO2. But we don't hear about the oceans, which also use CO2 to support the aquatic plant life and other life forms in the oceans.
-And the total CO2 level in the atmosphere being only 0.04%, up from 0.03% does not reflect the panic the government officials seem to put into the laws being passed, which does not reduce the CO2 levels produced from the manufacturing end of the equation, nor does it affect the levels of CO2 produced by other countries, like China and many others where we have shipped the American manufacturing off to, in order to have lower costs due to the laws made in error of bad data being constantly repeated by the protesters and other ecology based groups.
-We need to take a giant step back and look at what has happened in America over the last 100 years of industrial revolution, and come up with the real data about the amount of pollutants we are creating, and modify the current laws to reflect the real data of the pollutants that affect our lives, rather than go with the emotions that books like silent spring and other fairy tales have caused the government officials to create stifling laws that have ruined our economy and sent our industrial companies running to nations with little to no laws regarding safety or environmental dangers, and where the people who do the labor get little to no training of the dangers about the chemicals and materials they use, nor do they get any safety equipment, like steel toed shoes, goggles, or even hearing protection that Americans refuse to work without today.</v>
-      </c>
       <c r="C598" t="str">
         <v>Unknown</v>
       </c>
@@ -11007,7 +11049,7 @@
         <v>1</v>
       </c>
       <c r="E598" t="str">
-        <v/>
+        <v>what impact?  The United States was hotter during the 20s through the 40s. What is the climate supposed to be today vs. were it is with human life? Why has not one single prediction came to pass? I have heard this nonsense since the 1980s when I was 4 years old. The planet should be beyond saving and repair 100 times over by now. Why do you people forget the scandal involving NOAH and NASA changing historical temp. data and falsifying current data to suit the narrative and ignore what the real data is telling them. Did our carbon go back in time and create the Sahara Desert, was not always a desert you know?</v>
       </c>
     </row>
     <row r="599">
@@ -11177,7 +11219,7 @@
         <v>0</v>
       </c>
       <c r="E608" t="str">
-        <v>On average about 0.02%.</v>
+        <v/>
       </c>
     </row>
     <row r="609">
@@ -11216,16 +11258,16 @@
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>@danielcox1602</v>
+        <v>@pear7777</v>
       </c>
       <c r="B611" t="str">
-        <v>Are these people leaders? From the other side of the globe, i can see how you ended up with biden</v>
+        <v>I DON'T CARE it went up with 30%</v>
       </c>
       <c r="C611" t="str">
         <v>Unknown</v>
       </c>
       <c r="D611">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E611" t="str">
         <v/>
@@ -11233,16 +11275,16 @@
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>@pear7777</v>
+        <v>@danielcox1602</v>
       </c>
       <c r="B612" t="str">
-        <v>I DON'T CARE it went up with 30%</v>
+        <v>Are these people leaders? From the other side of the globe, i can see how you ended up with biden</v>
       </c>
       <c r="C612" t="str">
         <v>Unknown</v>
       </c>
       <c r="D612">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E612" t="str">
         <v/>
@@ -11521,7 +11563,7 @@
         <v/>
       </c>
     </row>
-    <row r="629">
+    <row r="629" xml:space="preserve">
       <c r="A629" t="str">
         <v>@khvediri</v>
       </c>
@@ -11534,8 +11576,10 @@
       <c r="D629">
         <v>2</v>
       </c>
-      <c r="E629" t="str">
-        <v/>
+      <c r="E629" t="str" xml:space="preserve">
+        <v xml:space="preserve">More like over 150 years, but somewhat rapid yes (although history is full of similar abrupt fall and rises in CO2, says the known data).
+What is also correct is that CO2 was at an all time low before the industrial revolution (280ppm), lower than the past 2 billion years and at its lowest point close to the critical level where plants can survive (around 200ppm). Today we have many crops that are resilient to low CO2 levels because of this CO2 drought, and there is absolutely no reason to want CO2 levels to go back to pre industrial levels, because that WILL (fact) reduce the amount of food we can produce by up to 40%.
+The other thing is that there is a mountain of evidence that CO2 can not be a significant driver of warming. The CO2 theory is entirely deduction based and also on cherry picked and fabricated data, and even if we ignore that obvious data manipulation, if you use deduction as proof you would in all other science categories, have a very weak theory in the first place, and when you add all the ways this deduction theory is proven wrong, it gets ridiculously unlikely that it can be true.</v>
       </c>
     </row>
     <row r="630">
@@ -11591,16 +11635,16 @@
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>@chudson5901</v>
+        <v>@jumboegg5845</v>
       </c>
       <c r="B633" t="str">
-        <v>lol， finding a solution is not job, even knowing the problem is not my job, my job is to cry and play dumb.</v>
+        <v>Good example of how little people know about basic science, including the guy asking the questions. Dont know who he is, but he goes on to say 0.04% is a "tiny" concentration and "plants start to die" at 0.02%. That tells me he doesnt know much about it either, just repeating something he read or heard somewhere.</v>
       </c>
       <c r="C633" t="str">
         <v>Unknown</v>
       </c>
       <c r="D633">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E633" t="str">
         <v/>
@@ -11608,45 +11652,45 @@
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>@jumboegg5845</v>
+        <v>@chudson5901</v>
       </c>
       <c r="B634" t="str">
-        <v>Good example of how little people know about basic science, including the guy asking the questions. Dont know who he is, but he goes on to say 0.04% is a "tiny" concentration and "plants start to die" at 0.02%. That tells me he doesnt know much about it either, just repeating something he read or heard somewhere.</v>
+        <v>lol， finding a solution is not job, even knowing the problem is not my job, my job is to cry and play dumb.</v>
       </c>
       <c r="C634" t="str">
         <v>Unknown</v>
       </c>
       <c r="D634">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E634" t="str">
         <v/>
       </c>
     </row>
-    <row r="635" xml:space="preserve">
+    <row r="635">
       <c r="A635" t="str">
+        <v>@bbritton223</v>
+      </c>
+      <c r="B635" t="str">
+        <v>at 400 parts per million it is up from 180 parts per million since industrial revolution, not clear that the increase is due to humans and not natural cycles. my backyard loves it i will need a new lawnmower soon.</v>
+      </c>
+      <c r="C635" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D635">
+        <v>0</v>
+      </c>
+      <c r="E635" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="636" xml:space="preserve">
+      <c r="A636" t="str">
         <v>@gfconstantino</v>
       </c>
-      <c r="B635" t="str" xml:space="preserve">
+      <c r="B636" t="str" xml:space="preserve">
         <v xml:space="preserve">Conversion: 1% = 10000 ppm.
 So 0,043% = (0,043 x 10000) ppm = 430 ppm.</v>
-      </c>
-      <c r="C635" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D635">
-        <v>0</v>
-      </c>
-      <c r="E635" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" t="str">
-        <v>@bbritton223</v>
-      </c>
-      <c r="B636" t="str">
-        <v>at 400 parts per million it is up from 180 parts per million since industrial revolution, not clear that the increase is due to humans and not natural cycles. my backyard loves it i will need a new lawnmower soon.</v>
       </c>
       <c r="C636" t="str">
         <v>Unknown</v>
@@ -11807,10 +11851,10 @@
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>@eh2179</v>
+        <v>@Thrillhouse1</v>
       </c>
       <c r="B645" t="str">
-        <v>Cow farts</v>
+        <v>so called "experts", and they don't even know! They guessed more than 125x what it actually is!</v>
       </c>
       <c r="C645" t="str">
         <v>Unknown</v>
@@ -11824,10 +11868,10 @@
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>@Thrillhouse1</v>
+        <v>@eh2179</v>
       </c>
       <c r="B646" t="str">
-        <v>so called "experts", and they don't even know! They guessed more than 125x what it actually is!</v>
+        <v>Cow farts</v>
       </c>
       <c r="C646" t="str">
         <v>Unknown</v>
@@ -12053,33 +12097,33 @@
         <v/>
       </c>
     </row>
-    <row r="658">
+    <row r="658" xml:space="preserve">
       <c r="A658" t="str">
-        <v>@Serrafimo_Spang</v>
-      </c>
-      <c r="B658" t="str">
-        <v>What % of our Congress showed up for work that day? From the opening it appears less than the % of C02 in our atmosphere. Must have been Donor Lobbyists Lunch Day, a Congressional Holiday.</v>
-      </c>
-      <c r="C658" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D658">
-        <v>0</v>
-      </c>
-      <c r="E658" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="659" xml:space="preserve">
-      <c r="A659" t="str">
         <v>@Quiestre</v>
       </c>
-      <c r="B659" t="str" xml:space="preserve">
+      <c r="B658" t="str" xml:space="preserve">
         <v xml:space="preserve">The small% of the atmosphere makes it just more significant in contrast to our actions
 If it was 5% then human activity would barely influence the amount in the atmosphere
 But at such low levels any increase will have more dramatic effects
 Also CO2 isn't the only green house gas</v>
       </c>
+      <c r="C658" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D658">
+        <v>0</v>
+      </c>
+      <c r="E658" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="str">
+        <v>@Serrafimo_Spang</v>
+      </c>
+      <c r="B659" t="str">
+        <v>What % of our Congress showed up for work that day? From the opening it appears less than the % of C02 in our atmosphere. Must have been Donor Lobbyists Lunch Day, a Congressional Holiday.</v>
+      </c>
       <c r="C659" t="str">
         <v>Unknown</v>
       </c>
@@ -12212,10 +12256,10 @@
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>@danbaker1277</v>
+        <v>@randyfender6122</v>
       </c>
       <c r="B667" t="str">
-        <v>We need global warming to keep the plants alive!</v>
+        <v>So instead of a short truck ride for materials, the new regs will force the state to buy those materials from out of the country, and ship them 10 times as far. What genius thinks this will help anything?</v>
       </c>
       <c r="C667" t="str">
         <v>Unknown</v>
@@ -12229,10 +12273,10 @@
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>@randyfender6122</v>
+        <v>@danbaker1277</v>
       </c>
       <c r="B668" t="str">
-        <v>So instead of a short truck ride for materials, the new regs will force the state to buy those materials from out of the country, and ship them 10 times as far. What genius thinks this will help anything?</v>
+        <v>We need global warming to keep the plants alive!</v>
       </c>
       <c r="C668" t="str">
         <v>Unknown</v>
@@ -12563,10 +12607,10 @@
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>@robchalmers6278</v>
+        <v>@solartrix</v>
       </c>
       <c r="B687" t="str">
-        <v>These people should know this if they have contemplated what 400 parts per million means. Also LaMalfa knows although tiny in percentage terms co2 is important as in his words "plants start to die off if co2 levels fall below 200 parts per million" Not exactly true but he acknowledges it's importance..</v>
+        <v>0.04 percent is the same as a blood alcohol content of point zero four.  going from .04 to .08 means you might want to think twice about driving home.  going from 0.04 to 0.08 CO2 content in the earth's atmosphere would melt all the ice and snow, flood all the coastlines and make a big chunk of the planet impossible to live on most of the year.  Seriously.  Little changes can have HUGE impacts.</v>
       </c>
       <c r="C687" t="str">
         <v>Unknown</v>
@@ -12580,10 +12624,10 @@
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>@solartrix</v>
+        <v>@robchalmers6278</v>
       </c>
       <c r="B688" t="str">
-        <v>0.04 percent is the same as a blood alcohol content of point zero four.  going from .04 to .08 means you might want to think twice about driving home.  going from 0.04 to 0.08 CO2 content in the earth's atmosphere would melt all the ice and snow, flood all the coastlines and make a big chunk of the planet impossible to live on most of the year.  Seriously.  Little changes can have HUGE impacts.</v>
+        <v>These people should know this if they have contemplated what 400 parts per million means. Also LaMalfa knows although tiny in percentage terms co2 is important as in his words "plants start to die off if co2 levels fall below 200 parts per million" Not exactly true but he acknowledges it's importance..</v>
       </c>
       <c r="C688" t="str">
         <v>Unknown</v>
@@ -12643,7 +12687,7 @@
         <v>1</v>
       </c>
       <c r="E691" t="str">
-        <v>Ok. Are we also supposed to regress back to pre-industrial technological levels too?</v>
+        <v/>
       </c>
     </row>
     <row r="692">
@@ -12714,37 +12758,37 @@
         <v>The blanket on your bed takes up a fraction of the atmosphere in your bedroom yet does an amazing job of trapping your body heat, even when the blanket is full of little holes. You don't need solid, hole-less blankets piled bed to ceiling to keep you warm. It's important to understand how CO2 molecules behave in the atmosphere. They carry on like crazed pinballs, constantly colliding with one another and exchanging heat in all directions. It's that heat exchange that fills the gaps between the molecules that creates the greenhouse effect.</v>
       </c>
     </row>
-    <row r="696" xml:space="preserve">
+    <row r="696">
       <c r="A696" t="str">
+        <v>@nolonger9112</v>
+      </c>
+      <c r="B696" t="str">
+        <v>Well just keep complain about too much co2 then. When tech about harvest co2 and turn it to plastic and glucose be a mass there will not enough co2 to mine.</v>
+      </c>
+      <c r="C696" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D696">
+        <v>0</v>
+      </c>
+      <c r="E696" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="697" xml:space="preserve">
+      <c r="A697" t="str">
         <v>@kw350</v>
       </c>
-      <c r="B696" t="str" xml:space="preserve">
+      <c r="B697" t="str" xml:space="preserve">
         <v xml:space="preserve">What's the point of this stupid question? Yes, there is a very tiny amount of CO2 in the cocktail that we call air. Its now about 425ppm. So 0.0425% It used to be half of that for tens of thousands of years. It took as less than a hundred years to get where we are now.
 Just to put that in perspective: you can easily live with about 0.000001% of cyanide in your blood. As soon as that reaches 0.000003%, you die. 
 So again: what is the point of that horrendously stupid question?</v>
       </c>
-      <c r="C696" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D696">
+      <c r="C697" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D697">
         <v>1</v>
-      </c>
-      <c r="E696" t="str">
-        <v>please tell me when these climate scientists have ever been right? Tell me one prediction they have made that is accurate? According to them we are dead and beyond saving 100 times over, we were supposed to die in a new Ice Age, then global warming, and then climate change. If they were right, why rebrand the image over 3 times?</v>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" t="str">
-        <v>@nolonger9112</v>
-      </c>
-      <c r="B697" t="str">
-        <v>Well just keep complain about too much co2 then. When tech about harvest co2 and turn it to plastic and glucose be a mass there will not enough co2 to mine.</v>
-      </c>
-      <c r="C697" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D697">
-        <v>0</v>
       </c>
       <c r="E697" t="str">
         <v/>
@@ -12859,10 +12903,10 @@
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>@LennartGustafsson-y8k</v>
+        <v>@calypsocostelo2482</v>
       </c>
       <c r="B704" t="str">
-        <v>Yes the haba hababs tribe is lost .</v>
+        <v>These are the same people who promoted vaccination.</v>
       </c>
       <c r="C704" t="str">
         <v>Unknown</v>
@@ -12876,10 +12920,10 @@
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>@calypsocostelo2482</v>
+        <v>@LennartGustafsson-y8k</v>
       </c>
       <c r="B705" t="str">
-        <v>These are the same people who promoted vaccination.</v>
+        <v>Yes the haba hababs tribe is lost .</v>
       </c>
       <c r="C705" t="str">
         <v>Unknown</v>
@@ -12905,7 +12949,7 @@
         <v>0</v>
       </c>
       <c r="E706" t="str">
-        <v/>
+        <v>It was 0.0317% when I was born and world population was just over 3bn (8bn today).  I think there might be some causal link here - I await my Nobel Prize...</v>
       </c>
     </row>
     <row r="707">
@@ -12942,30 +12986,30 @@
         <v/>
       </c>
     </row>
-    <row r="709">
+    <row r="709" xml:space="preserve">
       <c r="A709" t="str">
-        <v>@bennievanderschyff4370</v>
-      </c>
-      <c r="B709" t="str">
-        <v>Stunning ignorance!!!!</v>
-      </c>
-      <c r="C709" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D709">
-        <v>0</v>
-      </c>
-      <c r="E709" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="710" xml:space="preserve">
-      <c r="A710" t="str">
         <v>@shakycameratheater</v>
       </c>
-      <c r="B710" t="str" xml:space="preserve">
+      <c r="B709" t="str" xml:space="preserve">
         <v xml:space="preserve">Thought it was 80% nitrogen 20% Oxygen.  Google says 79% Nitrogen 20% Oxygen and 1 % everything else. And of that 1%,  0.04 is Carbon Dioxide
 Composition of atmosphere google chrome.</v>
+      </c>
+      <c r="C709" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D709">
+        <v>0</v>
+      </c>
+      <c r="E709" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="str">
+        <v>@bennievanderschyff4370</v>
+      </c>
+      <c r="B710" t="str">
+        <v>Stunning ignorance!!!!</v>
       </c>
       <c r="C710" t="str">
         <v>Unknown</v>
@@ -12991,15 +13035,15 @@
         <v>0</v>
       </c>
       <c r="E711" t="str">
-        <v/>
+        <v>That congressman's argument had no common sense. It was more comedy than reason.</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>@rays6202</v>
+        <v>@rogerrudyk8514</v>
       </c>
       <c r="B712" t="str">
-        <v>HERES AN IDEA WHY NOT GET NASA IN THERE TO EXPLAINE IT TO YOU ALL</v>
+        <v>Carbon dioxide from volcanic eruptions gas molecules reflect into space,hance global COOLING,happening in years</v>
       </c>
       <c r="C712" t="str">
         <v>Unknown</v>
@@ -13013,10 +13057,10 @@
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>@rogerrudyk8514</v>
+        <v>@brazil7028</v>
       </c>
       <c r="B713" t="str">
-        <v>Carbon dioxide from volcanic eruptions gas molecules reflect into space,hance global COOLING,happening in years</v>
+        <v>Why don't you ask them what the level of CO2 was during the time of the dinosaurs and back during the times when the earth was almost entirely covered in living breathing plants and animals? Spoiler, almost FOUR TIMES HIGHER than it is NOW. So how could it be so high during the time when the earth was more alive and healthier than it is now?</v>
       </c>
       <c r="C713" t="str">
         <v>Unknown</v>
@@ -13030,10 +13074,10 @@
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>@brazil7028</v>
+        <v>@rays6202</v>
       </c>
       <c r="B714" t="str">
-        <v>Why don't you ask them what the level of CO2 was during the time of the dinosaurs and back during the times when the earth was almost entirely covered in living breathing plants and animals? Spoiler, almost FOUR TIMES HIGHER than it is NOW. So how could it be so high during the time when the earth was more alive and healthier than it is now?</v>
+        <v>HERES AN IDEA WHY NOT GET NASA IN THERE TO EXPLAINE IT TO YOU ALL</v>
       </c>
       <c r="C714" t="str">
         <v>Unknown</v>
@@ -13224,7 +13268,7 @@
         <v>0</v>
       </c>
       <c r="E724" t="str">
-        <v>No it isn't. | Hogwash on the "lowest" part of your comment.  It is the highest.</v>
+        <v/>
       </c>
     </row>
     <row r="725" xml:space="preserve">
@@ -13259,7 +13303,7 @@
         <v>0</v>
       </c>
       <c r="E726" t="str">
-        <v/>
+        <v>Isotopes hold your answer.</v>
       </c>
     </row>
     <row r="727">
@@ -13580,66 +13624,66 @@
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>@Zephyr-c2j</v>
+        <v>@jksinorbit</v>
       </c>
       <c r="B745" t="str">
-        <v>Someone should seal this room, and increase the co2 level in the room from 438ppm to 1000ppm…. And let them discuss it for a few hours</v>
+        <v>The question is how much of a rise in CO2 will affect temperature not how little there is in terms of overall percentage. It might just take .001 increase over time to alter temperature in a deleterious way.</v>
       </c>
       <c r="C745" t="str">
         <v>Unknown</v>
       </c>
       <c r="D745">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E745" t="str">
-        <v/>
+        <v>or it might not</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>@lydiagracehill2307</v>
+        <v>@Zephyr-c2j</v>
       </c>
       <c r="B746" t="str">
-        <v>Climate change is real!</v>
+        <v>Someone should seal this room, and increase the co2 level in the room from 438ppm to 1000ppm…. And let them discuss it for a few hours</v>
       </c>
       <c r="C746" t="str">
         <v>Unknown</v>
       </c>
       <c r="D746">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E746" t="str">
         <v/>
       </c>
     </row>
-    <row r="747">
+    <row r="747" xml:space="preserve">
       <c r="A747" t="str">
-        <v>@jksinorbit</v>
-      </c>
-      <c r="B747" t="str">
-        <v>The question is how much of a rise in CO2 will affect temperature not how little there is in terms of overall percentage. It might just take .001 increase over time to alter temperature in a deleterious way.</v>
-      </c>
-      <c r="C747" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D747">
-        <v>0</v>
-      </c>
-      <c r="E747" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="748" xml:space="preserve">
-      <c r="A748" t="str">
         <v>@failure_4_sale</v>
       </c>
-      <c r="B748" t="str" xml:space="preserve">
+      <c r="B747" t="str" xml:space="preserve">
         <v xml:space="preserve">its actually not even .04 percent, the .04 percent he is referring to is actually the total COMBINED amount of gases like c02, methane, n02 and ozone... that's .04 percent. so really carbons number would be closer to less than 0.01 percent, roughly as there is multiple gases that fall into that .04 percent.
 I love hearing people say "we need to go electric" as this man points out, states are doing "rolling blackouts" when the temps hit 95 degrees because they don't generate enough power to sustain everyone's homes that being said, one electric vehicle equals approx. a half of an avg homes daily power use to charge and keep it running... so for every 2 electric vehicles on the road, its like another house was built... California wants everyone all electric by like 2030 or bs, I'm still waiting for them to explain where all this power is going to come from? there is roughly 27 mil drivers in Cali, so that's like building an additional 13.5 million houses... how THE F**K... do they planning on making all that power? 
 here is the VERY low end of what they'd have to build, roughly, 14, 361 wind turbines which all have to be made, and then replaced every 20 years so AND those have to be maintained at nearly 50 grand a year EACH,  or roughly 13-15 nuclear power plants, but that's not an option since California doesn't believe in nuclear, or roughly 35,500 acres of solar panels which also need to be made, or roughly 1800 coal fired plants and these folks are just the BARE MINIMUM they'd need to build... that's just to power the cars, this doesn't account for population growth or new homes that are built.... but it gives you a really great insight into how brilliant some of these politicians are when it comes to "where is all this power going to come from" even more hilarious? This is assuming everyone only drives 12,500 miles a year... which we all know just isn't true..so that just shows you how much more these are VERY lowball numbers for needed infrastructure JUST to power the cars... and they expect people to buy into "All electric" lmao, yeah, explain to me where its all going to come from then ill consider it
 Already see on the news of people waiting hours to charge their cars.. Electric cars are not nearly close to efficient enough to fully take over, not even close, not even close to close at our current pace, Plus, this doesn't even take account the absolutely environmentally damaging process of mining the needed lithium which oh by the way,  we need to import 100 percent of because the us mined like 3 percent of the worlds lithium. We have one large lithium mine in this country and that's it... hope they don't find any by you to power your new electric cars, EMINENT DOMAIN, BITCHES LEAVE
  Now this is just the numbers for Cali, now do all those numbers times 8 and that covers the whole country, just to power the cars AND THE REAL KICKER? The fucking batteries cant even efficiently be recycled since its not just one single battery per car, its thousands of lithium cells per car battery that have to be broken down....INDIVIDUALLY. its so inefficient, actually,  that ONLY FIVE PERCENT of the nearly 600,000 electric car batteries that needed trashed in 2020, we recycled, the rest? The other 570,000 batteries that weren't recycled? buried in the ground in a dump somewhere hope those chemicals don't leach into your ground water.... so yeah, go electric... ya know... for the environment and stuff... or something like that, now vote for me...to get F***ed super hard with no lube...</v>
       </c>
+      <c r="C747" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D747">
+        <v>0</v>
+      </c>
+      <c r="E747" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="str">
+        <v>@lydiagracehill2307</v>
+      </c>
+      <c r="B748" t="str">
+        <v>Climate change is real!</v>
+      </c>
       <c r="C748" t="str">
         <v>Unknown</v>
       </c>
@@ -13650,11 +13694,28 @@
         <v/>
       </c>
     </row>
-    <row r="749" xml:space="preserve">
+    <row r="749">
       <c r="A749" t="str">
+        <v>@cmwHisArtist</v>
+      </c>
+      <c r="B749" t="str">
+        <v>Am I blind, or did no one who makes the laws that could ruin our lives show up for this panel discussion so that they could claim ignorance?</v>
+      </c>
+      <c r="C749" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D749">
+        <v>0</v>
+      </c>
+      <c r="E749" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="750" xml:space="preserve">
+      <c r="A750" t="str">
         <v>@lrvogt1257</v>
       </c>
-      <c r="B749" t="str" xml:space="preserve">
+      <c r="B750" t="str" xml:space="preserve">
         <v xml:space="preserve">The natural high for CO2 during the period between glaciations is 280 ppm. Industry is pushing that past 420 ppm which 150% of what is natural and this is why the climate is warming 50 times faster than it did when the glaciers receded and civilization began. This is all contrary to natural cycles. 
 —“MET Office UK, Causes of climate change” —"Columbia Climate School, How Exactly Does Carbon Dioxide Cause Global Warming?"
 —“MIT, How do greenhouse gases trap heat in the atmosphere?
@@ -13662,23 +13723,6 @@
 —NASA: Watching the Land Temperature Bell Curve Heat Up (this. shows how a small increase in average produces a large number of extremely hot days)
 —YouTube Sabine Hossenfelder, I Misunderstood the Greenhouse Effect. Here's How It Works.</v>
       </c>
-      <c r="C749" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D749">
-        <v>0</v>
-      </c>
-      <c r="E749" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="750">
-      <c r="A750" t="str">
-        <v>@cmwHisArtist</v>
-      </c>
-      <c r="B750" t="str">
-        <v>Am I blind, or did no one who makes the laws that could ruin our lives show up for this panel discussion so that they could claim ignorance?</v>
-      </c>
       <c r="C750" t="str">
         <v>Unknown</v>
       </c>
@@ -13825,7 +13869,7 @@
         <v>0</v>
       </c>
       <c r="E758" t="str">
-        <v/>
+        <v>Correct. What's your point?</v>
       </c>
     </row>
     <row r="759" xml:space="preserve">
@@ -13987,7 +14031,7 @@
         <v>2</v>
       </c>
       <c r="E767" t="str">
-        <v/>
+        <v>please tell me when these climate scientists have ever been right? Tell me one prediction they have made that is accurate? According to them we are dead and beyond saving 100 times over, we were supposed to die in a new Ice Age, then global warming, and then climate change. If they were right, why rebrand the image over 3 times?</v>
       </c>
     </row>
     <row r="768">
@@ -14007,28 +14051,11 @@
         <v/>
       </c>
     </row>
-    <row r="769">
+    <row r="769" xml:space="preserve">
       <c r="A769" t="str">
-        <v>@lcruz1136</v>
-      </c>
-      <c r="B769" t="str">
-        <v>Are the panelist climate experts? No. so it is okay for they not to know, but Doug LaMalfa says it is a small increase, but it is not it is a 33% increase, that matters a lot.</v>
-      </c>
-      <c r="C769" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D769">
-        <v>0</v>
-      </c>
-      <c r="E769" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="770" xml:space="preserve">
-      <c r="A770" t="str">
         <v>@donkloos9078</v>
       </c>
-      <c r="B770" t="str" xml:space="preserve">
+      <c r="B769" t="str" xml:space="preserve">
         <v xml:space="preserve">The CO2 Greenhouse Effect_x000d_
 _x000d_
 There's a common belief that increasing CO2 levels in the atmosphere leads to more global warming._x000d_
@@ -14042,6 +14069,23 @@
 Given these points, the focus on increasing CO2 levels and their catastrophic potential is greatly overemphasized. Instead, redirecting efforts to other effects CO2 might have, and investing in nuclear energy development would be a more effective use of resources._x000d_
 Sincerely, Don Kloos, Chemist.</v>
       </c>
+      <c r="C769" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D769">
+        <v>0</v>
+      </c>
+      <c r="E769" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="str">
+        <v>@lcruz1136</v>
+      </c>
+      <c r="B770" t="str">
+        <v>Are the panelist climate experts? No. so it is okay for they not to know, but Doug LaMalfa says it is a small increase, but it is not it is a 33% increase, that matters a lot.</v>
+      </c>
       <c r="C770" t="str">
         <v>Unknown</v>
       </c>
@@ -14088,28 +14132,9 @@
     </row>
     <row r="773" xml:space="preserve">
       <c r="A773" t="str">
-        <v>@pau_6524</v>
+        <v>@Kharnellius</v>
       </c>
       <c r="B773" t="str" xml:space="preserve">
-        <v xml:space="preserve">How much does it matter if the % of CO2 in the atmosphere is a big or small number?... 
-How much arsenic are you going to take? Even though the quantity is very small, that does not mean it is not lethal.
-I understand the man's disagreement, but it makes no sense that his argument is based on the fact that the % of CO2 in the atmosphere is small.</v>
-      </c>
-      <c r="C773" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D773">
-        <v>3</v>
-      </c>
-      <c r="E773" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="774" xml:space="preserve">
-      <c r="A774" t="str">
-        <v>@Kharnellius</v>
-      </c>
-      <c r="B774" t="str" xml:space="preserve">
         <v xml:space="preserve">I’m confused.  We’re mocking them for not knowing how little CO2 makes up the atmosphere but not mocking the other guy for making it sound like it being a super small percentage somehow makes it better?!
 It’s the opposite.  If it’s only 0.04% then it takes a much smaller percentage to affect a bigger change. 
 75 years ago it was bout 0.03% or 300 ppm (parts per million) aka for every cube of 1 million gallons of air... 
@@ -14119,11 +14144,30 @@
 But that's assuming CO2 is 4%.  It's not.  It's a little over 0.04% (currently).  So now were going from 300 jugs to 400 jugs or in other words about a 33% increase!  Much higher change since it is already at a very small number.  This is what is concerning.  Now, I'm no alarmist, however, it does show a larger increase in a short time necessitating our attention and finding ways to mitigate and eventually stop/reverse this trend.
 But let's stop pretending those people are idiots when many of you don't even realize what you're championing.</v>
       </c>
+      <c r="C773" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D773">
+        <v>0</v>
+      </c>
+      <c r="E773" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="774" xml:space="preserve">
+      <c r="A774" t="str">
+        <v>@pau_6524</v>
+      </c>
+      <c r="B774" t="str" xml:space="preserve">
+        <v xml:space="preserve">How much does it matter if the % of CO2 in the atmosphere is a big or small number?... 
+How much arsenic are you going to take? Even though the quantity is very small, that does not mean it is not lethal.
+I understand the man's disagreement, but it makes no sense that his argument is based on the fact that the % of CO2 in the atmosphere is small.</v>
+      </c>
       <c r="C774" t="str">
         <v>Unknown</v>
       </c>
       <c r="D774">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E774" t="str">
         <v/>
@@ -14191,28 +14235,11 @@
         <v/>
       </c>
     </row>
-    <row r="778">
+    <row r="778" xml:space="preserve">
       <c r="A778" t="str">
-        <v>@GeorgeSmiley77</v>
-      </c>
-      <c r="B778" t="str">
-        <v>Most people know the concentration of CO2 as 400ppm, 400 Parts Per Million. But only a tiny, tiny, miniscule, eensie weensie fraction of them can convert 400ppm to a percentage in their heads within a second or two. I am one of those few. And I only have grade 12... almost.</v>
-      </c>
-      <c r="C778" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D778">
-        <v>1</v>
-      </c>
-      <c r="E778" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="779" xml:space="preserve">
-      <c r="A779" t="str">
         <v>@lrvogt1257</v>
       </c>
-      <c r="B779" t="str" xml:space="preserve">
+      <c r="B778" t="str" xml:space="preserve">
         <v xml:space="preserve">A few facts. None of this is speculative or controversial 
 —It's been known in physics for well over a century that CO2 absorbs and re-radiates infrared, AKA heat 
 —With no CO2, Earth's average temperature would be ~0 F instead of ~57 F. 
@@ -14228,11 +14255,28 @@
 —Warmer oceans means more energy is available to tropical storms. 
      These are just some of the basic changes to climate and weather. Beyond this is how it affects agriculture and all living things that can’t adapt fast enough to this rapid change.</v>
       </c>
+      <c r="C778" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D778">
+        <v>0</v>
+      </c>
+      <c r="E778" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="str">
+        <v>@GeorgeSmiley77</v>
+      </c>
+      <c r="B779" t="str">
+        <v>Most people know the concentration of CO2 as 400ppm, 400 Parts Per Million. But only a tiny, tiny, miniscule, eensie weensie fraction of them can convert 400ppm to a percentage in their heads within a second or two. I am one of those few. And I only have grade 12... almost.</v>
+      </c>
       <c r="C779" t="str">
         <v>Unknown</v>
       </c>
       <c r="D779">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E779" t="str">
         <v/>
@@ -14529,10 +14573,10 @@
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>@berniefynn6623</v>
+        <v>@GessteinTravels</v>
       </c>
       <c r="B797" t="str">
-        <v>0.00004% METHANE 0.000007%</v>
+        <v>We’re at .04% and .02% plant life cannot survive but at .2% plant life actually thrives and will grow faster.  In PPM thats 400PPM, 200PPM and 2000PPM respectively.</v>
       </c>
       <c r="C797" t="str">
         <v>Unknown</v>
@@ -14541,15 +14585,15 @@
         <v>0</v>
       </c>
       <c r="E797" t="str">
-        <v/>
+        <v>That’s irrelevant and is used as a strawman argument by prominent denier sites. The land and ocean cannot absorb all the extra CO2 we are emitting. About 40% of the additional CO2 we are emitting is absorbed. The rest remains in the atmosphere, consequently, atmospheric CO2 is at its highest level in millions of years. (A natural change of 100ppm normally takes 5,000 to 20,000 years. The recent increase of has taken just 120 years). CO2 is a greenhouse gas, and the simple truth is greenhouse gases allow short wavelength solar radiation to pass through the atmosphere unimpeded. As the Sun warms up Earth’s surface, longer wavelength thermal radiation is reflected back into the atmosphere. Some of this thermal radiation passes into space, some of the radiation is absorbed and some is reflected back to Earth. More CO2 means more thermal radiation is reflected back to Earth and this causes the temperature on Earth to rise. It is all explained through science.</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>@GessteinTravels</v>
+        <v>@berniefynn6623</v>
       </c>
       <c r="B798" t="str">
-        <v>We’re at .04% and .02% plant life cannot survive but at .2% plant life actually thrives and will grow faster.  In PPM thats 400PPM, 200PPM and 2000PPM respectively.</v>
+        <v>0.00004% METHANE 0.000007%</v>
       </c>
       <c r="C798" t="str">
         <v>Unknown</v>
@@ -14558,7 +14602,7 @@
         <v>0</v>
       </c>
       <c r="E798" t="str">
-        <v>That’s irrelevant and is used as a strawman argument by prominent denier sites. The land and ocean cannot absorb all the extra CO2 we are emitting. About 40% of the additional CO2 we are emitting is absorbed. The rest remains in the atmosphere, consequently, atmospheric CO2 is at its highest level in millions of years. (A natural change of 100ppm normally takes 5,000 to 20,000 years. The recent increase of has taken just 120 years). CO2 is a greenhouse gas, and the simple truth is greenhouse gases allow short wavelength solar radiation to pass through the atmosphere unimpeded. As the Sun warms up Earth’s surface, longer wavelength thermal radiation is reflected back into the atmosphere. Some of this thermal radiation passes into space, some of the radiation is absorbed and some is reflected back to Earth. More CO2 means more thermal radiation is reflected back to Earth and this causes the temperature on Earth to rise. It is all explained through science.</v>
+        <v/>
       </c>
     </row>
     <row r="799">
@@ -14595,7 +14639,7 @@
         <v/>
       </c>
     </row>
-    <row r="801">
+    <row r="801" xml:space="preserve">
       <c r="A801" t="str">
         <v>@listeningto8371</v>
       </c>
@@ -14608,8 +14652,12 @@
       <c r="D801">
         <v>0</v>
       </c>
-      <c r="E801" t="str">
-        <v/>
+      <c r="E801" t="str" xml:space="preserve">
+        <v xml:space="preserve">.03 to .032
+Redo your maths | @garreysellars5525  300 ppm to 420 ppm since 1960. It is indeed a big increase. | @melanp4698 
+  percent by volume USA parliamentary document
+,.042 to .044 percent atmospheric volume is quite small in respect
+Like pissing in the ocean and hopefully won't warm the water enough to melt the ice cap</v>
       </c>
     </row>
     <row r="802">
@@ -14815,7 +14863,7 @@
         <v>0</v>
       </c>
       <c r="E813" t="str">
-        <v>Your comment is Flat-Earther levels of divorced from reality. | @mathboy8188  thx</v>
+        <v/>
       </c>
     </row>
     <row r="814" xml:space="preserve">
@@ -14856,30 +14904,30 @@
         <v/>
       </c>
     </row>
-    <row r="816">
+    <row r="816" xml:space="preserve">
       <c r="A816" t="str">
-        <v>@arturhawk98</v>
-      </c>
-      <c r="B816" t="str">
-        <v>What ingorance...</v>
-      </c>
-      <c r="C816" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D816">
-        <v>0</v>
-      </c>
-      <c r="E816" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="817" xml:space="preserve">
-      <c r="A817" t="str">
         <v>@michaelrch</v>
       </c>
-      <c r="B817" t="str" xml:space="preserve">
+      <c r="B816" t="str" xml:space="preserve">
         <v xml:space="preserve">1:30 LaMalfa is a rice farmer. Rice unfortunately creates a lot of methane (a powerful GHG) due to how it's grown in water. 
 Climate is already hurting agriculture in CA. And it will get much worse. The irony of this line of questioning is that climate change will probably put him out of business one day.</v>
+      </c>
+      <c r="C816" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D816">
+        <v>0</v>
+      </c>
+      <c r="E816" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="str">
+        <v>@arturhawk98</v>
+      </c>
+      <c r="B817" t="str">
+        <v>What ingorance...</v>
       </c>
       <c r="C817" t="str">
         <v>Unknown</v>
@@ -14924,7 +14972,7 @@
         <v>4</v>
       </c>
       <c r="E819" t="str">
-        <v/>
+        <v>I was a meteorology minor and life long climate/meteorology enthusiast so this has been known to me for years and forget that the following is not known by others.   This happened from 1999-2013.  Global average temperatures did not rise, they fell compared to the previous 10 years, while co2 emissions went up, and at the highest stage of co2 emission rise, temps went down further.  So the two dont have a causal correlation.  1980-1999 they were incidentally correlated.</v>
       </c>
     </row>
     <row r="820">
@@ -15192,7 +15240,7 @@
         <v>0</v>
       </c>
       <c r="E834" t="str">
-        <v/>
+        <v>ohhh nooo what are we gonna do??? Tax and regulate. Best to make billionaires and politicians richer lol</v>
       </c>
     </row>
     <row r="835">
@@ -15234,7 +15282,7 @@
         <v/>
       </c>
     </row>
-    <row r="837" xml:space="preserve">
+    <row r="837">
       <c r="A837" t="str">
         <v>@paulroberts5677</v>
       </c>
@@ -15247,10 +15295,8 @@
       <c r="D837">
         <v>1</v>
       </c>
-      <c r="E837" t="str" xml:space="preserve">
-        <v xml:space="preserve">Very good for plants and crops | @charlieboy2587  Is it though? That's like saying if eating an apple is good for you, then eating 20 pounds of apples must be VERY good for you.
-Certainly more co2 is better for plants, but that causes them to grow faster. This means they need more water, nutrients etc. In turn that means higher co2 will devastate crops faster in a drought etc.
-Everything is a balance when it comes to science.</v>
+      <c r="E837" t="str">
+        <v/>
       </c>
     </row>
     <row r="838">
@@ -15302,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="E840" t="str">
-        <v/>
+        <v>Yeah he forgets that while .03% -&gt; .04% is a tiny increase, objectively speaking, it is still a 33% increase for that specific area, which is huge.</v>
       </c>
     </row>
     <row r="841">
@@ -15967,9 +16013,8 @@
       <c r="D878">
         <v>0</v>
       </c>
-      <c r="E878" t="str" xml:space="preserve">
-        <v xml:space="preserve">Well, CO2 isn't dropping so... | @Optimistprime.   thats good news for the planet. | "Plant life requires a minimum of 330 ppm" Hilariously wrong on a Trump U level, not even Prager U teaches that. The PEAK for the past 1,000,000 years prior to 1900 was 300ppm. Not the average, but the peak. The highest level.
-Your claim is that there was no plant life prior to 1911. Do you have proof? I'd love to see this proof.</v>
+      <c r="E878" t="str">
+        <v/>
       </c>
     </row>
     <row r="879">
@@ -15986,7 +16031,7 @@
         <v>0</v>
       </c>
       <c r="E879" t="str">
-        <v/>
+        <v>@Dan-mm1yl  read again. | Current 12-month avg is 424 ppm. Going up by about 3.5 ppm/year | @edilee5909  trend will continue until nuclear power is the new base power. Wind and solar are too wasteful as these require energy storage facilities that can eliminate up to 70% of the energy produced by wind and solar.</v>
       </c>
     </row>
     <row r="880">
@@ -16024,7 +16069,7 @@
         <v/>
       </c>
     </row>
-    <row r="882" xml:space="preserve">
+    <row r="882">
       <c r="A882" t="str">
         <v>@cathiharper</v>
       </c>
@@ -16037,14 +16082,8 @@
       <c r="D882">
         <v>0</v>
       </c>
-      <c r="E882" t="str" xml:space="preserve">
-        <v xml:space="preserve">You too are out of your depth. Your last sentence states "incredibly high".
-No ! CO2 is in short supply for all plants. Please do a Wiki (or some other
-credible source) to improve your knowledge. | @brianterence3211  To say that Wiki is a credible source is not only laughable, but also quite concerning. When I do my research, I tend to focus on more reputable sources such as NASA, NOAA, EPA or The Intergovernmental Panel on Climate Change (IPCC). I am quite happy to supply you with links or text associated with my statement. Would you please share with me your research? | @cathiharper  Research ? I sent a couple of links but they were 
-deleted. Was it you that did the job or a friend ?
-Opinion by most academics is that 2000 - 3000 ppm of CO2
-in the atmosphere would be ideal for most plants. It's currently 
-around 400 ppm. | @brianterence3211  at this point it's clear that you are just a TROLL and not willing to have any type of meaningful conversation or debate. "Opinion by most academics" is not fact nor does it substantiate any scientific study.</v>
+      <c r="E882" t="str">
+        <v/>
       </c>
     </row>
     <row r="883" xml:space="preserve">
@@ -16105,7 +16144,7 @@
         <v>0</v>
       </c>
       <c r="E885" t="str">
-        <v>Just false</v>
+        <v/>
       </c>
     </row>
     <row r="886">
@@ -16139,7 +16178,7 @@
         <v>0</v>
       </c>
       <c r="E887" t="str">
-        <v/>
+        <v>.04%</v>
       </c>
     </row>
     <row r="888" xml:space="preserve">
@@ -16217,10 +16256,10 @@
         <v>0</v>
       </c>
       <c r="E891" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="892" xml:space="preserve">
+        <v>Having to drive the same car for about 200k km (not 8-10 years) is only an issue because modern society is plagued by consumerism and shortlived technology. A generator that uses coal or oil is still more efficient than a car engine, so even if you're using fossile fuels to generate electricity, an EV is still worth it. Most developed countries also get the majority of their electricity from nuclear and renewables, not fossil fuels. There's also a limit to how much CO2 a plant, or even the ocean, can absorb.</v>
+      </c>
+    </row>
+    <row r="892">
       <c r="A892" t="str">
         <v>@mmypainting</v>
       </c>
@@ -16233,9 +16272,8 @@
       <c r="D892">
         <v>0</v>
       </c>
-      <c r="E892" t="str" xml:space="preserve">
-        <v xml:space="preserve">They're not driving the bus. They're working the administrative and regulatory process based on what those who are driving the bus, the climate scientists, have found. They didn't know that factoid because they didn't need to know it to do their job.
-However, if you're just a farmer, kudos to you for knowing it. | mmypainting  Clearly, you don't - you're an order of magnitude too high...</v>
+      <c r="E892" t="str">
+        <v/>
       </c>
     </row>
     <row r="893" xml:space="preserve">
@@ -16275,39 +16313,39 @@
         <v/>
       </c>
     </row>
-    <row r="895" xml:space="preserve">
+    <row r="895">
       <c r="A895" t="str">
+        <v>@MrCrecker</v>
+      </c>
+      <c r="B895" t="str">
+        <v>Це просто розгром усіх "зелених" і викриття схем збагачення окремої купки людей за рахунок тупості усього людства.</v>
+      </c>
+      <c r="C895" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D895">
+        <v>0</v>
+      </c>
+      <c r="E895" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="896" xml:space="preserve">
+      <c r="A896" t="str">
         <v>@marileedent8499</v>
       </c>
-      <c r="B895" t="str">
+      <c r="B896" t="str">
         <v>They are illiterate</v>
       </c>
-      <c r="C895" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D895">
-        <v>0</v>
-      </c>
-      <c r="E895" t="str" xml:space="preserve">
+      <c r="C896" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D896">
+        <v>0</v>
+      </c>
+      <c r="E896" t="str" xml:space="preserve">
         <v xml:space="preserve">[] They are illiterate ...
 As is the questioner.</v>
-      </c>
-    </row>
-    <row r="896">
-      <c r="A896" t="str">
-        <v>@MrCrecker</v>
-      </c>
-      <c r="B896" t="str">
-        <v>Це просто розгром усіх "зелених" і викриття схем збагачення окремої купки людей за рахунок тупості усього людства.</v>
-      </c>
-      <c r="C896" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D896">
-        <v>0</v>
-      </c>
-      <c r="E896" t="str">
-        <v/>
       </c>
     </row>
     <row r="897" xml:space="preserve">
@@ -16347,7 +16385,7 @@
         <v>0.04% can also be thought of as one twenty fifth of one percent, or 1/2500.  It's 4/10000 as a fraction.  The 'experts' guessed 7/100!</v>
       </c>
     </row>
-    <row r="899">
+    <row r="899" xml:space="preserve">
       <c r="A899" t="str">
         <v>@oreo753</v>
       </c>
@@ -16360,11 +16398,12 @@
       <c r="D899">
         <v>0</v>
       </c>
-      <c r="E899" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="900" xml:space="preserve">
+      <c r="E899" t="str" xml:space="preserve">
+        <v xml:space="preserve">Too funny. The moon and Earth are roughly the same distance from the sun, but they very different climates. Why? | @milankovitch8697  Are you genuinely asking that?? The moon’s gravity is one sixth of the Earth’s gravity thus it is unable to hold its own atmosphere due to the low escape velocity  needed by the gas molecules to fly off to space. A highschooler knows this already. | @oreo753  
+Nice try, I did not ask why they have different atmospheres, I asked why they have different climates. Care to try again again? | @milankovitch8697  the lunar climate alternates between extremes of hot and cold. However, Earth doesn't due to the presence of atmosphere. Moon doesn't have an atmosphere simply because of its weak gravity and thus its climate isn't the same as that of Earth. Is it clearer now? | Yup.</v>
+      </c>
+    </row>
+    <row r="900">
       <c r="A900" t="str">
         <v>@stephtraveler7378</v>
       </c>
@@ -16377,9 +16416,8 @@
       <c r="D900">
         <v>0</v>
       </c>
-      <c r="E900" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wrong question will get you wrong answer. You ask average of total opposite spectrum, between equator and pole, not to mention difference between day &amp; night, between low elevation and high elevation, which is not possible to get definitive answer.
-Now I ask, how you can calculate average earth temperature? Is it possible with all those variable?</v>
+      <c r="E900" t="str">
+        <v/>
       </c>
     </row>
     <row r="901">
@@ -16432,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="E903" t="str">
-        <v/>
+        <v>Yeah, but each cycle took 1000s of years, not 100 | @after_midnight9592  You could be correct. However, the history of the past 2,000 years alone provides examples of rapid climate change at different times.</v>
       </c>
     </row>
     <row r="904">
@@ -16500,7 +16538,7 @@
         <v>0</v>
       </c>
       <c r="E907" t="str">
-        <v/>
+        <v>Truth? He literally lied by omitting the fact that the 0.04% is still a huge increase from pre-industrial levels. | The politician made a basic factual statement while the so-called experts made it like a guessing game. Are they making regulatory policies based on guesses too? | @rockprime1136  They're making regulatory policies based on the fact that we need less carbondioxide in the atmosphere.</v>
       </c>
     </row>
     <row r="908">
@@ -16517,7 +16555,7 @@
         <v>0</v>
       </c>
       <c r="E908" t="str">
-        <v/>
+        <v>Why? They are policians who have experts at their side who know this. Why should they know themselves?</v>
       </c>
     </row>
     <row r="909" xml:space="preserve">
@@ -16607,8 +16645,14 @@
       <c r="D913">
         <v>0</v>
       </c>
-      <c r="E913" t="str">
-        <v/>
+      <c r="E913" t="str" xml:space="preserve">
+        <v xml:space="preserve">sadly, they have no understanding of the way things work.
+Oh sweet sweet irony... | Amount of co2 in atmosphere roughly 2e15 kg and humans breathe out about 3e12 kg per year, so your calculations probably incorrect. Also humans breathe out carbon that was just captured by plants, and it does not change carbon balance, while burning fossil fuels adds carbon that was removed from atmosphere millions of years ago, and adds it at a significant rate, like 1000x of natural co2 fluctuations | hiya - nice to meet you. 
+one thing i do not understand is why so many people call petroleum 'fossil fuel', when it has been demonstrated that long-chain hydrocarbons are produced by chemical reaction under heat and pressure from hydrogen and carbon, regardless of the source of the elements. hydrogen and carbon are 2 abundant elements - carbon needs to complete its electron orbits and hydrogen is obliging. voila, petroleum.
+methane, on the other hand, is largely produced by decomposition of vegetable matter, and cattle farts. (accelerated digestive decomposition)
+i dont know where you got your numbers, and you probably dont know how i got mine, but that doesnt mean we have to argue and 'win the argument', which is just childish. discussing our differences and comparing perspectives is the more mature, responsible procedure. 
+have a nice day.
+ @JumpingJack-w2l | @garywoodard5759   it is called fossil fuels because of the way vast majority of oil and gas reserves were formed, which supported by geological and geochemical evidences. Anyway, it is carbon that not present in atmosphere and now is releasing in it in large quantities, while humans breathe out carbon they ate, and food produced by plants, so that amount of co2 was extracted just recently from atmosphere so it does not matter. Numbers are: humans breathing out abt 3 Gt of co2 per year, global co2 emissions abt 50 Gt of co2 per year, atmosphere content about 2000 Gt. It is easy to find a source for this numbers or check by calculations (little harder for emissions, but doable) | @garywoodard5759  'Fossil' also has the meaning: 'belonging to a past epoch'. | @JumpingJack-w2l " Also humans breathe out carbon that was just captured by plants, and it does not change carbon balance".  True, but energy was expended growing, harvesting, transporting, selling, and cooking them.</v>
       </c>
     </row>
     <row r="914" xml:space="preserve">
@@ -16648,7 +16692,7 @@
         <v/>
       </c>
     </row>
-    <row r="916">
+    <row r="916" xml:space="preserve">
       <c r="A916" t="str">
         <v>@pascalbercker7487</v>
       </c>
@@ -16661,8 +16705,9 @@
       <c r="D916">
         <v>0</v>
       </c>
-      <c r="E916" t="str">
-        <v/>
+      <c r="E916" t="str" xml:space="preserve">
+        <v xml:space="preserve">Yeah, and here you are, one of that so called "16 000 climate science experts! "
+BRAVO BRAVO</v>
       </c>
     </row>
     <row r="917">
@@ -16679,7 +16724,7 @@
         <v>0</v>
       </c>
       <c r="E917" t="str">
-        <v/>
+        <v>Like so many people who don't understand orders of magnitude, you are one out on your percentages. | @thedubwhisperer2157 You are quite right, divide my answers by 10. So we need to be at 0.02 percent, not the current in excess of 0.04 percent. Otherwise, what I wrote is correct. BTW, I do understand orders of magnitude, by I was clearly "sloppy" with my mental arithmetic.  Thanks for pointing that out :)</v>
       </c>
     </row>
     <row r="918">
@@ -16819,31 +16864,31 @@
         <v/>
       </c>
     </row>
-    <row r="926">
+    <row r="926" xml:space="preserve">
       <c r="A926" t="str">
-        <v>@ACowGF</v>
-      </c>
-      <c r="B926" t="str">
-        <v>The question is stupid. This is like asking your car mechanic how to manufacture a tire. I guarantee your mechanic doesn't know how tires are made but I guarantee he knows how to fix them. Their job is reducing emissions from cars not environmental studies.</v>
-      </c>
-      <c r="C926" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="D926">
-        <v>0</v>
-      </c>
-      <c r="E926" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="927" xml:space="preserve">
-      <c r="A927" t="str">
         <v>@Greebstreebling</v>
       </c>
-      <c r="B927" t="str" xml:space="preserve">
+      <c r="B926" t="str" xml:space="preserve">
         <v xml:space="preserve">The sun is approximately 93 Million miles away from the earth. So applying similar logic, the sun can't possibly have any impact on the Earth can it? 
 Nonsense logic has been used to misrepresent the problem we face. Just because the percentage of CO2 in our atmosphere is low, that does NOT mean its impact is low. High school science :)</v>
       </c>
+      <c r="C926" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="D926">
+        <v>0</v>
+      </c>
+      <c r="E926" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="str">
+        <v>@ACowGF</v>
+      </c>
+      <c r="B927" t="str">
+        <v>The question is stupid. This is like asking your car mechanic how to manufacture a tire. I guarantee your mechanic doesn't know how tires are made but I guarantee he knows how to fix them. Their job is reducing emissions from cars not environmental studies.</v>
+      </c>
       <c r="C927" t="str">
         <v>Unknown</v>
       </c>
@@ -16854,7 +16899,7 @@
         <v/>
       </c>
     </row>
-    <row r="928">
+    <row r="928" xml:space="preserve">
       <c r="A928" t="str">
         <v>@resonant_theories</v>
       </c>
@@ -16867,8 +16912,14 @@
       <c r="D928">
         <v>0</v>
       </c>
-      <c r="E928" t="str">
-        <v/>
+      <c r="E928" t="str" xml:space="preserve">
+        <v xml:space="preserve">and here is the answer  (in short) from the modern search engines.. called AI.. 
+Concentration (ppm)	Context/Effect
+420-425 ppm	Current Global Atmospheric Average
+600-900 ppm	Typical Urban/Metropolitan Air
+&lt; 1,000 ppm	Recommended maximum for good indoor air quality (e.g., offices, classrooms)
+5,000 ppm	OSHA Permissible Exposure Limit (PEL) for an 8-hour workday in the US
+30,000 ppm	ACGIH Ceiling Exposure Limit (not to be exceeded for a 10-minute period) | in highly industrialized areas/localities, the concentration can exceed 1000ppm which is 0.1% to answer the question of the speaker. Of course human activity does not only release CO2 but also H2O, which is another green house gas. Combustion does that, and if you look around, what is mostly used is combustion engines. LLM answer.. "Conclusion: The H2O from combustion does locally increase the concentration of water vapor, contributing to higher local humidity, fog, and smog formation.".. "Quantitative Output: For most hydrocarbon fuels, the molar ratio of H2O to CO2 produced is often around 1:1 to 2:1 (for natural gas CH4(aka natural farts), it is 2 H2O for every 1 CO2. This means that for every molecule of CO2 measured at 1000 ppm from combustion, there are 1 to 2 molecules of H2O released alongside it." And guess what technology was adopted the past few years all over the globe, "because it was cleaner in carbon footprint"! Increased (or lowered) humidity, kind of hides problems for the respiratory system. There is a narrow zone that is the ideal for avoiding any health risks.</v>
       </c>
     </row>
     <row r="929" xml:space="preserve">
@@ -16887,7 +16938,7 @@
         <v>0</v>
       </c>
       <c r="E929" t="str">
-        <v/>
+        <v>@rudolfgernd8760 Yes, no excuse for your ignorance</v>
       </c>
     </row>
     <row r="930">
@@ -16938,7 +16989,7 @@
         <v>0</v>
       </c>
       <c r="E932" t="str">
-        <v/>
+        <v>@phoenixfelon9566 Earth has been a greenhouse planet for most of it's existence. Like 85% or so</v>
       </c>
     </row>
     <row r="933">
@@ -17040,10 +17091,10 @@
         <v>0</v>
       </c>
       <c r="E938" t="str">
-        <v>No. It's about 0.04% once converted from ppmv.</v>
-      </c>
-    </row>
-    <row r="939">
+        <v/>
+      </c>
+    </row>
+    <row r="939" xml:space="preserve">
       <c r="A939" t="str">
         <v>@Craig-fl8jj</v>
       </c>
@@ -17056,8 +17107,9 @@
       <c r="D939">
         <v>0</v>
       </c>
-      <c r="E939" t="str">
-        <v/>
+      <c r="E939" t="str" xml:space="preserve">
+        <v xml:space="preserve">What do you mean?
+It's easily measurable. | @TomH2681  lol no. You can't just take a few samples and average them | @Craig-fl8jj  There are other methods that detect CO2 in large volumes. | @kensmith5694  then cite 3 sources that agree on how much co2 is in the atmosphere</v>
       </c>
     </row>
     <row r="940">
@@ -17142,7 +17194,7 @@
         <v>1</v>
       </c>
       <c r="E944" t="str">
-        <v/>
+        <v>It’s not climate change its climate engineering | @JB-xb8wm You do love ignorance.</v>
       </c>
     </row>
     <row r="945">
@@ -17255,7 +17307,7 @@
         <v>0</v>
       </c>
       <c r="E950" t="str">
-        <v/>
+        <v>Flunk your 5th grade math I see. | @mrunning10  No he didnt | @melanp4698  You flunked it too I see.  "percentage of co2 in our atmosphere" = 100*(425/1000000) = 0.04%  Back to conspiracy denial school for the BOTH of you. | @mrunning10  I didnt say his equation was correct, i said he didnt flunk 5th grade math. | @melanp4698  Appears from both of your answers, you BOTH flunked 5th grade math. | @mrunning10  It took you 3 weeks to come up with that? That's more embarassing than flunking 5th grade math. | So YOU changed your answer.  I remember YOU typing "0,0004%" | Still flunking your 5th grade math I see.</v>
       </c>
     </row>
     <row r="951">
@@ -17289,7 +17341,7 @@
         <v>0</v>
       </c>
       <c r="E952" t="str">
-        <v/>
+        <v>Did you look stacks ?</v>
       </c>
     </row>
     <row r="953">
@@ -17402,7 +17454,7 @@
         <v>0</v>
       </c>
       <c r="E958" t="str">
-        <v>OK, so WHY aren't we better  than this?</v>
+        <v/>
       </c>
     </row>
     <row r="959">
